--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,81 +492,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.097200000000001</v>
+        <v>7.1922</v>
       </c>
       <c r="C2" t="n">
-        <v>3.643740000000001</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.358874113940586</v>
+        <v>2.4841</v>
       </c>
       <c r="E2" t="n">
-        <v>41.8603</v>
+        <v>7.1922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.880492424203339</v>
+        <v>2.4185</v>
       </c>
       <c r="G2" t="n">
-        <v>40.97980332796763</v>
+        <v>4.7737</v>
       </c>
       <c r="H2" t="n">
-        <v>0.880492424203339</v>
+        <v>2.4185</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8382579403271224</v>
+        <v>1.9603</v>
       </c>
       <c r="J2" t="n">
-        <v>40.97980332796763</v>
+        <v>4.7737</v>
       </c>
       <c r="K2" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L2" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>41.8181</v>
+        <v>6.734</v>
       </c>
       <c r="N2" t="n">
-        <v>276</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.095</v>
+        <v>6.9491</v>
       </c>
       <c r="C3" t="n">
-        <v>3.19275</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.63277994168892</v>
+        <v>2.3859</v>
       </c>
       <c r="E3" t="n">
-        <v>32.8113</v>
+        <v>6.9491</v>
       </c>
       <c r="F3" t="n">
-        <v>4.052166907190368</v>
+        <v>3.7781</v>
       </c>
       <c r="G3" t="n">
-        <v>28.75910951191484</v>
+        <v>3.171</v>
       </c>
       <c r="H3" t="n">
-        <v>4.052166907190368</v>
+        <v>3.7781</v>
       </c>
       <c r="I3" t="n">
-        <v>3.559305822047592</v>
+        <v>3.0623</v>
       </c>
       <c r="J3" t="n">
-        <v>28.75910951191484</v>
+        <v>3.171</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -587,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>32.3184</v>
+        <v>6.2333</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -596,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9999</v>
+        <v>5.6345</v>
       </c>
       <c r="C4" t="n">
-        <v>3.149955</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.570543023442364</v>
+        <v>1.8549</v>
       </c>
       <c r="E4" t="n">
-        <v>32.0356</v>
+        <v>5.6345</v>
       </c>
       <c r="F4" t="n">
-        <v>4.288499461156606</v>
+        <v>2.1097</v>
       </c>
       <c r="G4" t="n">
-        <v>27.74714330329874</v>
+        <v>3.5248</v>
       </c>
       <c r="H4" t="n">
-        <v>4.288499461156606</v>
+        <v>2.1097</v>
       </c>
       <c r="I4" t="n">
-        <v>4.082793476225208</v>
+        <v>1.71</v>
       </c>
       <c r="J4" t="n">
-        <v>27.74714330329874</v>
+        <v>3.5248</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>31.8299</v>
+        <v>5.2348</v>
       </c>
       <c r="N4" t="n">
-        <v>276</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7168</v>
+        <v>5.1144</v>
       </c>
       <c r="C5" t="n">
-        <v>3.02256</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.391367965090831</v>
+        <v>1.6447</v>
       </c>
       <c r="E5" t="n">
-        <v>29.8027</v>
+        <v>5.1144</v>
       </c>
       <c r="F5" t="n">
-        <v>4.663973920204955</v>
+        <v>3.3995</v>
       </c>
       <c r="G5" t="n">
-        <v>25.13868223040901</v>
+        <v>1.7149</v>
       </c>
       <c r="H5" t="n">
-        <v>4.663973920204955</v>
+        <v>3.3995</v>
       </c>
       <c r="I5" t="n">
-        <v>4.096699348342945</v>
+        <v>2.7554</v>
       </c>
       <c r="J5" t="n">
-        <v>25.13868223040901</v>
+        <v>1.7149</v>
       </c>
       <c r="K5" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="L5" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>29.2354</v>
+        <v>4.4703</v>
       </c>
       <c r="N5" t="n">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6">
@@ -692,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.6525</v>
+        <v>4.965</v>
       </c>
       <c r="C6" t="n">
-        <v>2.993625</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2.351964383088868</v>
+        <v>1.5844</v>
       </c>
       <c r="E6" t="n">
-        <v>29.3116</v>
+        <v>4.965</v>
       </c>
       <c r="F6" t="n">
-        <v>3.52154049792925</v>
+        <v>3.1878</v>
       </c>
       <c r="G6" t="n">
-        <v>25.79004467462952</v>
+        <v>1.7772</v>
       </c>
       <c r="H6" t="n">
-        <v>3.52154049792925</v>
+        <v>3.1878</v>
       </c>
       <c r="I6" t="n">
-        <v>3.352623149760348</v>
+        <v>2.5838</v>
       </c>
       <c r="J6" t="n">
-        <v>25.79004467462952</v>
+        <v>1.7772</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -725,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>29.1427</v>
+        <v>4.361</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -734,90 +722,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.015</v>
+        <v>4.3579</v>
       </c>
       <c r="C7" t="n">
-        <v>2.70675</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985118224545206</v>
+        <v>1.3391</v>
       </c>
       <c r="E7" t="n">
-        <v>24.7397</v>
+        <v>4.3579</v>
       </c>
       <c r="F7" t="n">
-        <v>5.88028025151824</v>
+        <v>4.4536</v>
       </c>
       <c r="G7" t="n">
-        <v>18.85944894452413</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>5.88028025151824</v>
+        <v>5.3574</v>
       </c>
       <c r="I7" t="n">
-        <v>5.165067533956119</v>
+        <v>4.3423</v>
       </c>
       <c r="J7" t="n">
-        <v>18.85944894452413</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>103</v>
+        <v>219</v>
       </c>
       <c r="L7" t="n">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>24.0245</v>
+        <v>4.2466</v>
       </c>
       <c r="N7" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0487</v>
+        <v>3.9571</v>
       </c>
       <c r="C8" t="n">
-        <v>1.821915</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.087842486710404</v>
+        <v>1.1772</v>
       </c>
       <c r="E8" t="n">
-        <v>13.5573</v>
+        <v>3.9571</v>
       </c>
       <c r="F8" t="n">
-        <v>4.636983122376003</v>
+        <v>4.8663</v>
       </c>
       <c r="G8" t="n">
-        <v>8.920359808839347</v>
+        <v>-0.9092</v>
       </c>
       <c r="H8" t="n">
-        <v>4.636983122376003</v>
+        <v>7.5914</v>
       </c>
       <c r="I8" t="n">
-        <v>4.723818012308138</v>
+        <v>6.1531</v>
       </c>
       <c r="J8" t="n">
-        <v>8.920359808839347</v>
+        <v>-0.9092</v>
       </c>
       <c r="K8" t="n">
-        <v>136</v>
+        <v>238</v>
       </c>
       <c r="L8" t="n">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>13.6442</v>
+        <v>5.2439</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -826,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9598</v>
+        <v>3.7469</v>
       </c>
       <c r="C9" t="n">
-        <v>1.78191</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.054356098878364</v>
+        <v>1.0923</v>
       </c>
       <c r="E9" t="n">
-        <v>13.14</v>
+        <v>3.7469</v>
       </c>
       <c r="F9" t="n">
-        <v>4.797122094980319</v>
+        <v>4.1793</v>
       </c>
       <c r="G9" t="n">
-        <v>8.342893466774143</v>
+        <v>-0.4324</v>
       </c>
       <c r="H9" t="n">
-        <v>4.797122094980319</v>
+        <v>4.2536</v>
       </c>
       <c r="I9" t="n">
-        <v>4.567019063763438</v>
+        <v>3.4476</v>
       </c>
       <c r="J9" t="n">
-        <v>8.342893466774143</v>
+        <v>-0.4324</v>
       </c>
       <c r="K9" t="n">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>12.9099</v>
+        <v>3.0152</v>
       </c>
       <c r="N9" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9486</v>
+        <v>3.7146</v>
       </c>
       <c r="C10" t="n">
-        <v>1.77687</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1.05019231190438</v>
+        <v>1.0793</v>
       </c>
       <c r="E10" t="n">
-        <v>13.0881</v>
+        <v>3.7146</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.234624450700604</v>
+        <v>4.7146</v>
       </c>
       <c r="G10" t="n">
-        <v>15.3227484117974</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.234624450700604</v>
+        <v>6.4074</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.962829271261037</v>
+        <v>5.1934</v>
       </c>
       <c r="J10" t="n">
-        <v>15.3227484117974</v>
+        <v>-1</v>
       </c>
       <c r="K10" t="n">
-        <v>103</v>
+        <v>238</v>
       </c>
       <c r="L10" t="n">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>13.3599</v>
+        <v>4.1934</v>
       </c>
       <c r="N10" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8472</v>
+        <v>3.713</v>
       </c>
       <c r="C11" t="n">
-        <v>1.73124</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1.012742245625005</v>
+        <v>1.0786</v>
       </c>
       <c r="E11" t="n">
-        <v>12.6214</v>
+        <v>3.713</v>
       </c>
       <c r="F11" t="n">
-        <v>2.491900437702778</v>
+        <v>3.3744</v>
       </c>
       <c r="G11" t="n">
-        <v>10.12949842527657</v>
+        <v>0.3386</v>
       </c>
       <c r="H11" t="n">
-        <v>2.491900437702778</v>
+        <v>3.3744</v>
       </c>
       <c r="I11" t="n">
-        <v>2.188813032390169</v>
+        <v>2.7351</v>
       </c>
       <c r="J11" t="n">
-        <v>10.12949842527657</v>
+        <v>0.3386</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="L11" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="M11" t="n">
-        <v>12.3183</v>
+        <v>3.0737</v>
       </c>
       <c r="N11" t="n">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -968,40 +956,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.452</v>
+        <v>3.5604</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5534</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8731697942357652</v>
+        <v>1.017</v>
       </c>
       <c r="E12" t="n">
-        <v>10.882</v>
+        <v>3.5604</v>
       </c>
       <c r="F12" t="n">
-        <v>4.504103107544476</v>
+        <v>3.2854</v>
       </c>
       <c r="G12" t="n">
-        <v>6.377860487599043</v>
+        <v>0.275</v>
       </c>
       <c r="H12" t="n">
-        <v>4.504103107544476</v>
+        <v>3.2854</v>
       </c>
       <c r="I12" t="n">
-        <v>4.588449607685758</v>
+        <v>2.6629</v>
       </c>
       <c r="J12" t="n">
-        <v>6.377860487599043</v>
+        <v>0.275</v>
       </c>
       <c r="K12" t="n">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="L12" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>10.9663</v>
+        <v>2.9379</v>
       </c>
       <c r="N12" t="n">
         <v>280</v>
@@ -1014,40 +1002,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3221</v>
+        <v>3.2217</v>
       </c>
       <c r="C13" t="n">
-        <v>1.494945</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8294467204916125</v>
+        <v>0.8801</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3371</v>
+        <v>3.2217</v>
       </c>
       <c r="F13" t="n">
-        <v>2.826565983653224</v>
+        <v>2.7233</v>
       </c>
       <c r="G13" t="n">
-        <v>7.510494546940199</v>
+        <v>0.4984</v>
       </c>
       <c r="H13" t="n">
-        <v>2.826565983653224</v>
+        <v>2.7233</v>
       </c>
       <c r="I13" t="n">
-        <v>2.879497930912648</v>
+        <v>2.2073</v>
       </c>
       <c r="J13" t="n">
-        <v>7.510494546940199</v>
+        <v>0.4984</v>
       </c>
       <c r="K13" t="n">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="L13" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>10.39</v>
+        <v>2.7057</v>
       </c>
       <c r="N13" t="n">
         <v>280</v>
@@ -1056,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9157</v>
+        <v>2.3451</v>
       </c>
       <c r="C14" t="n">
-        <v>1.312065</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6991438013068801</v>
+        <v>0.526</v>
       </c>
       <c r="E14" t="n">
-        <v>8.713100000000001</v>
+        <v>2.3451</v>
       </c>
       <c r="F14" t="n">
-        <v>5.349066127189363</v>
+        <v>0.7517</v>
       </c>
       <c r="G14" t="n">
-        <v>3.364081583389212</v>
+        <v>1.5934</v>
       </c>
       <c r="H14" t="n">
-        <v>5.349066127189363</v>
+        <v>0.7517</v>
       </c>
       <c r="I14" t="n">
-        <v>6.210526215088773</v>
+        <v>0.6093</v>
       </c>
       <c r="J14" t="n">
-        <v>3.364081583389212</v>
+        <v>1.5934</v>
       </c>
       <c r="K14" t="n">
+        <v>121</v>
+      </c>
+      <c r="L14" t="n">
         <v>155</v>
       </c>
-      <c r="L14" t="n">
-        <v>125</v>
-      </c>
       <c r="M14" t="n">
-        <v>9.5746</v>
+        <v>2.2027</v>
       </c>
       <c r="N14" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8692</v>
+        <v>1.9095</v>
       </c>
       <c r="C15" t="n">
-        <v>1.29114</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6848553527379022</v>
+        <v>0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>8.5351</v>
+        <v>1.9095</v>
       </c>
       <c r="F15" t="n">
-        <v>6.561039979583193</v>
+        <v>0.1444</v>
       </c>
       <c r="G15" t="n">
-        <v>1.974036549210187</v>
+        <v>1.7651</v>
       </c>
       <c r="H15" t="n">
-        <v>6.561039979583193</v>
+        <v>0.1444</v>
       </c>
       <c r="I15" t="n">
-        <v>7.61768686768086</v>
+        <v>0.117</v>
       </c>
       <c r="J15" t="n">
-        <v>1.974036549210187</v>
+        <v>1.7651</v>
       </c>
       <c r="K15" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>9.591699999999999</v>
+        <v>1.8821</v>
       </c>
       <c r="N15" t="n">
-        <v>280</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.588</v>
+        <v>1.6281</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1646</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6008699579939507</v>
+        <v>0.2364</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4884</v>
+        <v>1.6281</v>
       </c>
       <c r="F16" t="n">
-        <v>3.121247801106515</v>
+        <v>-0.7024</v>
       </c>
       <c r="G16" t="n">
-        <v>4.367152566691919</v>
+        <v>2.3305</v>
       </c>
       <c r="H16" t="n">
-        <v>3.121247801106515</v>
+        <v>-0.7024</v>
       </c>
       <c r="I16" t="n">
-        <v>3.17969813446057</v>
+        <v>-0.5693</v>
       </c>
       <c r="J16" t="n">
-        <v>4.367152566691919</v>
+        <v>2.3305</v>
       </c>
       <c r="K16" t="n">
+        <v>103</v>
+      </c>
+      <c r="L16" t="n">
         <v>136</v>
       </c>
-      <c r="L16" t="n">
-        <v>144</v>
-      </c>
       <c r="M16" t="n">
-        <v>7.5469</v>
+        <v>1.7612</v>
       </c>
       <c r="N16" t="n">
-        <v>280</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>flayy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5681</v>
+        <v>1.628</v>
       </c>
       <c r="C17" t="n">
-        <v>1.155645</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.595091260322051</v>
+        <v>0.2363</v>
       </c>
       <c r="E17" t="n">
-        <v>7.4164</v>
+        <v>1.628</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4715221647992662</v>
+        <v>1.628</v>
       </c>
       <c r="G17" t="n">
-        <v>7.887904950097617</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4715221647992662</v>
+        <v>1.628</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.547460191339972</v>
+        <v>1.628</v>
       </c>
       <c r="J17" t="n">
-        <v>7.887904950097617</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L17" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7.3404</v>
+        <v>1.628</v>
       </c>
       <c r="N17" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
@@ -1244,40 +1232,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5581</v>
+        <v>1.5909</v>
       </c>
       <c r="C18" t="n">
-        <v>1.151145</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5921753581075464</v>
+        <v>0.2213</v>
       </c>
       <c r="E18" t="n">
-        <v>7.38</v>
+        <v>1.5909</v>
       </c>
       <c r="F18" t="n">
-        <v>2.843037810788762</v>
+        <v>1.1574</v>
       </c>
       <c r="G18" t="n">
-        <v>4.537005259193386</v>
+        <v>0.4335</v>
       </c>
       <c r="H18" t="n">
-        <v>2.843037810788762</v>
+        <v>1.1574</v>
       </c>
       <c r="I18" t="n">
-        <v>3.300905323387701</v>
+        <v>0.9381</v>
       </c>
       <c r="J18" t="n">
-        <v>4.537005259193386</v>
+        <v>0.4335</v>
       </c>
       <c r="K18" t="n">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="L18" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>7.8379</v>
+        <v>1.3716</v>
       </c>
       <c r="N18" t="n">
         <v>280</v>
@@ -1286,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0873</v>
+        <v>1.328</v>
       </c>
       <c r="C19" t="n">
-        <v>0.939285</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4615798852996825</v>
+        <v>0.1151</v>
       </c>
       <c r="E19" t="n">
-        <v>5.7525</v>
+        <v>1.328</v>
       </c>
       <c r="F19" t="n">
-        <v>5.752484271948407</v>
+        <v>1.328</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.752484271948407</v>
+        <v>1.328</v>
       </c>
       <c r="I19" t="n">
-        <v>6.635824553408648</v>
+        <v>1.328</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>6.6358</v>
+        <v>1.328</v>
       </c>
       <c r="N19" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>flayy</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8073</v>
+        <v>1.2665</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8132849999999999</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3890299294556868</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>4.8483</v>
+        <v>1.2665</v>
       </c>
       <c r="F20" t="n">
-        <v>4.848323381895376</v>
+        <v>2.4833</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1.2168</v>
       </c>
       <c r="H20" t="n">
-        <v>4.848323381895376</v>
+        <v>2.4833</v>
       </c>
       <c r="I20" t="n">
-        <v>5.665456536147406</v>
+        <v>2.0128</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.2168</v>
       </c>
       <c r="K20" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6655</v>
+        <v>0.7959999999999998</v>
       </c>
       <c r="N20" t="n">
-        <v>156</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>spooke</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4096</v>
+        <v>1.1676</v>
       </c>
       <c r="C21" t="n">
-        <v>0.63432</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2921322724469444</v>
+        <v>0.0503</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6407</v>
+        <v>1.1676</v>
       </c>
       <c r="F21" t="n">
-        <v>3.640726894952392</v>
+        <v>1.1676</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.640726894952392</v>
+        <v>1.1676</v>
       </c>
       <c r="I21" t="n">
-        <v>3.480385771681282</v>
+        <v>1.1676</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4804</v>
+        <v>1.1676</v>
       </c>
       <c r="N21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>spooke</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4023</v>
+        <v>0.9159</v>
       </c>
       <c r="C22" t="n">
-        <v>0.631035</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2904070258443832</v>
+        <v>-0.0514</v>
       </c>
       <c r="E22" t="n">
-        <v>3.6192</v>
+        <v>0.9159</v>
       </c>
       <c r="F22" t="n">
-        <v>3.619225841153174</v>
+        <v>0.9159</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.619225841153174</v>
+        <v>0.9159</v>
       </c>
       <c r="I22" t="n">
-        <v>3.445622830802605</v>
+        <v>0.9159</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4456</v>
+        <v>0.9159</v>
       </c>
       <c r="N22" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1474,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3509</v>
+        <v>0.9004</v>
       </c>
       <c r="C23" t="n">
-        <v>0.607905</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2784194198406043</v>
+        <v>-0.0576</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4698</v>
+        <v>0.9004</v>
       </c>
       <c r="F23" t="n">
-        <v>3.469829133906537</v>
+        <v>0.9004</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.469829133906537</v>
+        <v>0.9004</v>
       </c>
       <c r="I23" t="n">
-        <v>3.303392219083794</v>
+        <v>0.9004</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1507,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3034</v>
+        <v>0.9004</v>
       </c>
       <c r="N23" t="n">
         <v>121</v>
@@ -1516,231 +1504,231 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.259</v>
+        <v>0.6766</v>
       </c>
       <c r="C24" t="n">
-        <v>0.56655</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2572341404387073</v>
+        <v>-0.148</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2058</v>
+        <v>0.6766</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5772987047752096</v>
+        <v>0.6766</v>
       </c>
       <c r="G24" t="n">
-        <v>3.783104230986793</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5772987047752096</v>
+        <v>0.6766</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5881095419432847</v>
+        <v>0.6766</v>
       </c>
       <c r="J24" t="n">
-        <v>3.783104230986793</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="L24" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.195</v>
+        <v>0.6766</v>
       </c>
       <c r="N24" t="n">
-        <v>280</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hfah</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.239</v>
+        <v>0.4943</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5575500000000001</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2526645069782011</v>
+        <v>-0.2217</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1489</v>
+        <v>0.4943</v>
       </c>
       <c r="F25" t="n">
-        <v>3.148856024191875</v>
+        <v>0.4943</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.148856024191875</v>
+        <v>0.4943</v>
       </c>
       <c r="I25" t="n">
-        <v>3.679562095684888</v>
+        <v>0.4943</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6796</v>
+        <v>0.4943</v>
       </c>
       <c r="N25" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1458</v>
+        <v>0.1095</v>
       </c>
       <c r="C26" t="n">
-        <v>0.51561</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.231608850853265</v>
+        <v>-0.3771</v>
       </c>
       <c r="E26" t="n">
-        <v>2.8864</v>
+        <v>0.1095</v>
       </c>
       <c r="F26" t="n">
-        <v>2.886447859209536</v>
+        <v>0.1095</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.886447859209536</v>
+        <v>0.1095</v>
       </c>
       <c r="I26" t="n">
-        <v>3.329685170923359</v>
+        <v>0.1095</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3297</v>
+        <v>0.1095</v>
       </c>
       <c r="N26" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0389</v>
+        <v>0.0596</v>
       </c>
       <c r="C27" t="n">
-        <v>0.467505</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2079014901697255</v>
+        <v>-0.3973</v>
       </c>
       <c r="E27" t="n">
-        <v>2.591</v>
+        <v>0.0596</v>
       </c>
       <c r="F27" t="n">
-        <v>2.590992567926801</v>
+        <v>-0.0572</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1168</v>
       </c>
       <c r="H27" t="n">
-        <v>2.590992567926801</v>
+        <v>-0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>2.476882756695295</v>
+        <v>-0.0464</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.1168</v>
       </c>
       <c r="K27" t="n">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M27" t="n">
-        <v>2.4769</v>
+        <v>0.0704</v>
       </c>
       <c r="N27" t="n">
-        <v>122</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>hfah</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8512</v>
+        <v>0.0314</v>
       </c>
       <c r="C28" t="n">
-        <v>0.38304</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1673808187111992</v>
+        <v>-0.4087</v>
       </c>
       <c r="E28" t="n">
-        <v>2.086</v>
+        <v>0.0314</v>
       </c>
       <c r="F28" t="n">
-        <v>2.08599975373035</v>
+        <v>0.0314</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.08599975373035</v>
+        <v>0.0314</v>
       </c>
       <c r="I28" t="n">
-        <v>1.994130313009568</v>
+        <v>0.0314</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9941</v>
+        <v>0.0314</v>
       </c>
       <c r="N28" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
@@ -1750,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8283</v>
+        <v>-0.0697</v>
       </c>
       <c r="C29" t="n">
-        <v>0.372735</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1625326627445257</v>
+        <v>-0.4495</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0256</v>
+        <v>-0.0697</v>
       </c>
       <c r="F29" t="n">
-        <v>2.02557913785335</v>
+        <v>-0.0697</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.02557913785335</v>
+        <v>-0.0697</v>
       </c>
       <c r="I29" t="n">
-        <v>2.366968880188184</v>
+        <v>-0.0697</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1783,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.367</v>
+        <v>-0.0697</v>
       </c>
       <c r="N29" t="n">
         <v>156</v>
@@ -1792,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6806</v>
+        <v>-0.278</v>
       </c>
       <c r="C30" t="n">
-        <v>0.30627</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1317275756381406</v>
+        <v>-0.5337</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6417</v>
+        <v>-0.278</v>
       </c>
       <c r="F30" t="n">
-        <v>1.641667739806987</v>
+        <v>-0.278</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.641667739806987</v>
+        <v>-0.278</v>
       </c>
       <c r="I30" t="n">
-        <v>1.569367109456618</v>
+        <v>-0.278</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1829,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5694</v>
+        <v>-0.278</v>
       </c>
       <c r="N30" t="n">
         <v>122</v>
@@ -1838,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5237000000000001</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.235665</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09990271862166497</v>
+        <v>-0.6333</v>
       </c>
       <c r="E31" t="n">
-        <v>1.245</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1.245047359944847</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.245047359944847</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1.190214273591662</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1902</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1884,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5124</v>
+        <v>-0.5871</v>
       </c>
       <c r="C32" t="n">
-        <v>0.23058</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0976324892703658</v>
+        <v>-0.6585</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2168</v>
+        <v>-0.5871</v>
       </c>
       <c r="F32" t="n">
-        <v>1.216754405565812</v>
+        <v>-0.5871</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.216754405565812</v>
+        <v>-0.5871</v>
       </c>
       <c r="I32" t="n">
-        <v>1.158390479982147</v>
+        <v>-0.5871</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1584</v>
+        <v>-0.5871</v>
       </c>
       <c r="N32" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
@@ -1934,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4294</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.19323</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08120814002572417</v>
+        <v>-0.7079</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0121</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.012064353603416</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.012064353603416</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9635187733701377</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1967,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9635</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>121</v>
@@ -1976,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4096</v>
+        <v>-0.7254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.18432</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0773148860473309</v>
+        <v>-0.7144</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9635</v>
+        <v>-0.7254</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9635442967494066</v>
+        <v>-0.7254</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9635442967494066</v>
+        <v>-0.7254</v>
       </c>
       <c r="I34" t="n">
-        <v>1.111504282392574</v>
+        <v>-0.7254</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1115</v>
+        <v>-0.7254</v>
       </c>
       <c r="N34" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>urban0</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4064</v>
+        <v>-0.9346</v>
       </c>
       <c r="C35" t="n">
-        <v>0.18288</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07669113087932426</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9558</v>
+        <v>-0.9346</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9557706872231269</v>
+        <v>-0.9346</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9557706872231269</v>
+        <v>-0.9346</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9099253391323596</v>
+        <v>-0.9346</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9099</v>
+        <v>-0.9346</v>
       </c>
       <c r="N35" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>urban0</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3507</v>
+        <v>-1.0152</v>
       </c>
       <c r="C36" t="n">
-        <v>0.157815</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.06583360715259548</v>
+        <v>-0.8315</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8205</v>
+        <v>-1.0152</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8204577404083777</v>
+        <v>-1.0152</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8204577404083777</v>
+        <v>-1.0152</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9464456331302634</v>
+        <v>-1.0152</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9464</v>
+        <v>-1.0152</v>
       </c>
       <c r="N36" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
@@ -2118,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3492</v>
+        <v>-1.1356</v>
       </c>
       <c r="C37" t="n">
-        <v>0.15714</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06555910945603589</v>
+        <v>-0.8801</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8169999999999999</v>
+        <v>-1.1356</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8170367861327816</v>
+        <v>-1.1356</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8170367861327816</v>
+        <v>-1.1356</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9547396152562841</v>
+        <v>-1.1356</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2151,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9547</v>
+        <v>-1.1356</v>
       </c>
       <c r="N37" t="n">
         <v>156</v>
@@ -2160,136 +2148,136 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.0646</v>
+        <v>-1.2686</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.02907</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.01181308691765714</v>
+        <v>-0.9338</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1472</v>
+        <v>-1.2686</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1472217461401343</v>
+        <v>-0.2686</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1472217461401343</v>
+        <v>-0.2686</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1720343999839772</v>
+        <v>-0.2177</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.172</v>
+        <v>-1.2177</v>
       </c>
       <c r="N38" t="n">
-        <v>156</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>levi</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3852</v>
+        <v>-1.6462</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.17334</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.07254367805474198</v>
+        <v>-1.0864</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9041</v>
+        <v>-1.6462</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9040826524930874</v>
+        <v>-1.6462</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9040826524930874</v>
+        <v>-1.6462</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.042911823849704</v>
+        <v>-1.6462</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0429</v>
+        <v>-1.6462</v>
       </c>
       <c r="N39" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.5695</v>
+        <v>-1.8892</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.256275</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1090986604116826</v>
+        <v>-1.1846</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3597</v>
+        <v>-1.8892</v>
       </c>
       <c r="F40" t="n">
-        <v>1.230056603179893</v>
+        <v>-1.9158</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.589709283238471</v>
+        <v>0.0266</v>
       </c>
       <c r="H40" t="n">
-        <v>1.230056603179893</v>
+        <v>-1.9158</v>
       </c>
       <c r="I40" t="n">
-        <v>1.428155606688265</v>
+        <v>-1.5528</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.589709283238471</v>
+        <v>0.0266</v>
       </c>
       <c r="K40" t="n">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="L40" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1616</v>
+        <v>-1.5262</v>
       </c>
       <c r="N40" t="n">
         <v>280</v>
@@ -2298,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>levi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.0731</v>
+        <v>-2.7609</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.832895</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.097129693307567</v>
+        <v>-1.5367</v>
       </c>
       <c r="E41" t="n">
-        <v>-13.6731</v>
+        <v>-2.7609</v>
       </c>
       <c r="F41" t="n">
-        <v>2.680750420013416</v>
+        <v>-2.7609</v>
       </c>
       <c r="G41" t="n">
-        <v>-16.35383606788945</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.680750420013416</v>
+        <v>-2.7609</v>
       </c>
       <c r="I41" t="n">
-        <v>2.552163157615721</v>
+        <v>-2.7609</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.35383606788945</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="L41" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-13.8017</v>
+        <v>-2.7609</v>
       </c>
       <c r="N41" t="n">
-        <v>276</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2282681065399513</v>
+        <v>0.3946</v>
       </c>
       <c r="J2" t="n">
-        <v>4.337094024259074</v>
+        <v>7.4974</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.165152314460529</v>
+        <v>0.2111</v>
       </c>
       <c r="J3" t="n">
-        <v>3.137893974750051</v>
+        <v>4.0109</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0641936071799814</v>
+        <v>-0.1808</v>
       </c>
       <c r="J4" t="n">
-        <v>1.219678536419647</v>
+        <v>-3.4352</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01813597260788483</v>
+        <v>-0.4746</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3445834795498117</v>
+        <v>-9.0174</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2417554459975623</v>
+        <v>-0.9804</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.593353473953683</v>
+        <v>-18.6276</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.049292112535478</v>
+        <v>1.2479</v>
       </c>
       <c r="J7" t="n">
-        <v>19.93655013817408</v>
+        <v>23.7101</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4874856812400186</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>9.262227943560353</v>
+        <v>14.7763</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2129922465366409</v>
+        <v>0.4728</v>
       </c>
       <c r="J9" t="n">
-        <v>4.046852684196176</v>
+        <v>8.9832</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09004307445589178</v>
+        <v>0.1506</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.710818414661944</v>
+        <v>2.8614</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4176935558241373</v>
+        <v>-0.3339</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.936177560658608</v>
+        <v>-6.3441</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3024622202181378</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>6.654168844799033</v>
+        <v>13.4728</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1597397131774073</v>
+        <v>0.2651</v>
       </c>
       <c r="J13" t="n">
-        <v>3.51427368990296</v>
+        <v>5.8322</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06731085497437721</v>
+        <v>-0.1706</v>
       </c>
       <c r="J14" t="n">
-        <v>1.480838809436299</v>
+        <v>-3.7532</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>0.005588395007624647</v>
+        <v>-0.3519</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1229446901677422</v>
+        <v>-7.7418</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05779968233888498</v>
+        <v>-0.5053</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.27159301145547</v>
+        <v>-11.1166</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.344419267393317</v>
+        <v>0.4514</v>
       </c>
       <c r="J17" t="n">
-        <v>7.577223882652975</v>
+        <v>9.9308</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.241639862873687</v>
+        <v>0.3381</v>
       </c>
       <c r="J18" t="n">
-        <v>5.316076983221114</v>
+        <v>7.4382</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1466411154460307</v>
+        <v>0.2078</v>
       </c>
       <c r="J19" t="n">
-        <v>3.226104539812675</v>
+        <v>4.5716</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07754837784114105</v>
+        <v>0.0619</v>
       </c>
       <c r="J20" t="n">
-        <v>1.706064312505103</v>
+        <v>1.3618</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1823614256455345</v>
+        <v>-0.359</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.011951364201758</v>
+        <v>-7.898</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4852778950463161</v>
+        <v>1.1737</v>
       </c>
       <c r="J22" t="n">
-        <v>10.19083579597264</v>
+        <v>24.6477</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2671718789475188</v>
+        <v>0.758</v>
       </c>
       <c r="J23" t="n">
-        <v>5.610609457897894</v>
+        <v>15.918</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1581304070233867</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>3.32073854749112</v>
+        <v>10.5315</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08590224124426897</v>
+        <v>-0.3683</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.803947066129648</v>
+        <v>-7.7343</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.85</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1778965935227503</v>
+        <v>-0.5893</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.735828463977757</v>
+        <v>-12.3753</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3323579705818597</v>
+        <v>0.652</v>
       </c>
       <c r="J27" t="n">
-        <v>6.979517382219053</v>
+        <v>13.692</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1542154754733711</v>
+        <v>0.2708</v>
       </c>
       <c r="J28" t="n">
-        <v>3.238524984940793</v>
+        <v>5.6868</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1073797100314056</v>
+        <v>0.1269</v>
       </c>
       <c r="J29" t="n">
-        <v>2.254973910659519</v>
+        <v>2.6649</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0147041290941036</v>
+        <v>-0.3289</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3087867109761755</v>
+        <v>-6.9069</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1307059356285866</v>
+        <v>-0.5745</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.744824648200319</v>
+        <v>-12.0645</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4632328718031753</v>
+        <v>1.2168</v>
       </c>
       <c r="J32" t="n">
-        <v>8.338191692457155</v>
+        <v>21.9024</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3046018855168963</v>
+        <v>0.9227</v>
       </c>
       <c r="J33" t="n">
-        <v>5.482833939304133</v>
+        <v>16.6086</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.157064383396302</v>
+        <v>0.5344</v>
       </c>
       <c r="J34" t="n">
-        <v>2.827158901133437</v>
+        <v>9.619199999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1367019511816361</v>
+        <v>0.4815</v>
       </c>
       <c r="J35" t="n">
-        <v>2.460635121269449</v>
+        <v>8.667</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1353843298835589</v>
+        <v>-0.3121</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.43691793790406</v>
+        <v>-5.6178</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2894081409590661</v>
+        <v>0.5072</v>
       </c>
       <c r="J37" t="n">
-        <v>5.20934653726319</v>
+        <v>9.1296</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.14329019910442</v>
+        <v>0.1404</v>
       </c>
       <c r="J38" t="n">
-        <v>2.579223583879561</v>
+        <v>2.5272</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07569102892725654</v>
+        <v>-0.1274</v>
       </c>
       <c r="J39" t="n">
-        <v>1.362438520690618</v>
+        <v>-2.2932</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.05831339873218437</v>
+        <v>-0.5099</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.049641177179319</v>
+        <v>-9.1782</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1534996577774678</v>
+        <v>-0.7013</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.76299383999442</v>
+        <v>-12.6234</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>2.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9960325238747514</v>
+        <v>2.179</v>
       </c>
       <c r="J42" t="n">
-        <v>13.94445533424652</v>
+        <v>30.506</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.53</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2481455362220901</v>
+        <v>1.0607</v>
       </c>
       <c r="J43" t="n">
-        <v>3.474037507109262</v>
+        <v>14.8498</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1286266633694474</v>
+        <v>0.835</v>
       </c>
       <c r="J44" t="n">
-        <v>1.800773287172264</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.09499987519088683</v>
+        <v>0.7732</v>
       </c>
       <c r="J45" t="n">
-        <v>1.329998252672416</v>
+        <v>10.8248</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07250842175842898</v>
+        <v>0.7318</v>
       </c>
       <c r="J46" t="n">
-        <v>1.015117904618006</v>
+        <v>10.2452</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5140367507535489</v>
+        <v>0.9388</v>
       </c>
       <c r="J47" t="n">
-        <v>7.196514510549685</v>
+        <v>13.1432</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.08511914088956056</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.191667972453848</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.48</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09738058754183333</v>
+        <v>-0.7202</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.363328225585667</v>
+        <v>-10.0828</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1467128125019481</v>
+        <v>-0.8244</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.053979375027273</v>
+        <v>-11.5416</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2078509673289551</v>
+        <v>-0.9474</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.909913542605372</v>
+        <v>-13.2636</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.103472657948568</v>
+        <v>0.6022</v>
       </c>
       <c r="J52" t="n">
-        <v>3.104179738457039</v>
+        <v>18.066</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0545184902760327</v>
+        <v>0.3785</v>
       </c>
       <c r="J53" t="n">
-        <v>1.635554708280981</v>
+        <v>11.355</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.02175177060364292</v>
+        <v>0.1576</v>
       </c>
       <c r="J54" t="n">
-        <v>0.6525531181092877</v>
+        <v>4.728</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.003230208553180954</v>
+        <v>-0.0796</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.09690625659542862</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.05703102023031806</v>
+        <v>-0.4035</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.710930606909542</v>
+        <v>-12.105</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0496623089103744</v>
+        <v>0.5743</v>
       </c>
       <c r="J57" t="n">
-        <v>1.489869267311232</v>
+        <v>17.229</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.04559955367796106</v>
+        <v>0.523</v>
       </c>
       <c r="J58" t="n">
-        <v>1.367986610338832</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01000225091129601</v>
+        <v>-0.1899</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3000675273388802</v>
+        <v>-5.697</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.72</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01024479397075293</v>
+        <v>-0.4924</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.3073438191225878</v>
+        <v>-14.772</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.01430493940194697</v>
+        <v>-0.5447</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.429148182058409</v>
+        <v>-16.341</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.06489698380074417</v>
+        <v>0.6359</v>
       </c>
       <c r="J62" t="n">
-        <v>1.492630627417116</v>
+        <v>14.6257</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>0.007402076085425976</v>
+        <v>-0.1049</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1702477499647974</v>
+        <v>-2.4127</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>0.004692198430828642</v>
+        <v>-0.1465</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1079205639090588</v>
+        <v>-3.3695</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0005118762173198822</v>
+        <v>-0.2024</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01177315299835729</v>
+        <v>-4.6552</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0009023573008531995</v>
+        <v>-0.2198</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.02075421791962359</v>
+        <v>-5.0554</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>2.07</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1922576908183684</v>
+        <v>2.0593</v>
       </c>
       <c r="J67" t="n">
-        <v>4.421926888822473</v>
+        <v>47.3639</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.03920771491910372</v>
+        <v>0.715</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9017774431393856</v>
+        <v>16.445</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.007535421461384605</v>
+        <v>-0.1109</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.1733146936118459</v>
+        <v>-2.5507</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.84</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.03995522447206294</v>
+        <v>-0.6242</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.9189701628574477</v>
+        <v>-14.3566</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0738166283362818</v>
+        <v>-1.0132</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.697782451734482</v>
+        <v>-23.3036</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09327211333602847</v>
+        <v>0.8665</v>
       </c>
       <c r="J72" t="n">
-        <v>2.798163400080854</v>
+        <v>25.995</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.01469302177583874</v>
+        <v>0.0509</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4407906532751622</v>
+        <v>1.527</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.000164505144165359</v>
+        <v>-0.2114</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.004935154324960771</v>
+        <v>-6.342</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.003033242158491253</v>
+        <v>-0.2453</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.0909972647547376</v>
+        <v>-7.359</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.01026189694337049</v>
+        <v>-0.324</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.3078569083011146</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.04821214066027435</v>
+        <v>0.7023</v>
       </c>
       <c r="J77" t="n">
-        <v>1.44636421980823</v>
+        <v>21.069</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0361276297828754</v>
+        <v>0.5495</v>
       </c>
       <c r="J78" t="n">
-        <v>1.083828893486262</v>
+        <v>16.485</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02136677145390481</v>
+        <v>0.3164</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6410031436171443</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>0.001760072818062678</v>
+        <v>-0.2038</v>
       </c>
       <c r="J80" t="n">
-        <v>0.05280218454188034</v>
+        <v>-6.114</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.01843421511755924</v>
+        <v>-0.5121</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.5530264535267773</v>
+        <v>-15.363</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.85</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8708677018620425</v>
+        <v>1.8003</v>
       </c>
       <c r="J82" t="n">
-        <v>19.15908944096494</v>
+        <v>39.6066</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3606266102291502</v>
+        <v>1.0093</v>
       </c>
       <c r="J83" t="n">
-        <v>7.933785425041305</v>
+        <v>22.2046</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.09789751978559506</v>
+        <v>-0.186</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.153745435283092</v>
+        <v>-4.092</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1218801760841891</v>
+        <v>-0.265</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.681363873852161</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2599453609321036</v>
+        <v>-0.611</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.718797940506279</v>
+        <v>-13.442</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1283911514915864</v>
+        <v>0.2426</v>
       </c>
       <c r="J87" t="n">
-        <v>2.824605332814901</v>
+        <v>5.3372</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.09152247573720096</v>
+        <v>0.0299</v>
       </c>
       <c r="J88" t="n">
-        <v>2.013494466218421</v>
+        <v>0.6578000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>0.04194798116540843</v>
+        <v>-0.2616</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9228555856389855</v>
+        <v>-5.7552</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>0.007988764672464871</v>
+        <v>-0.4066</v>
       </c>
       <c r="J90" t="n">
-        <v>0.1757528227942272</v>
+        <v>-8.9452</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.02434124633497275</v>
+        <v>-0.5194</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.5355074193694006</v>
+        <v>-11.4268</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2796833270314004</v>
+        <v>0.5987</v>
       </c>
       <c r="J92" t="n">
-        <v>4.474933232502406</v>
+        <v>9.5792</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.06</v>
       </c>
       <c r="I93" t="n">
-        <v>0.121485372745971</v>
+        <v>0.2002</v>
       </c>
       <c r="J93" t="n">
-        <v>1.943765963935536</v>
+        <v>3.2032</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.88</v>
       </c>
       <c r="I94" t="n">
-        <v>0.02354370848832441</v>
+        <v>-0.2141</v>
       </c>
       <c r="J94" t="n">
-        <v>0.3766993358131905</v>
+        <v>-3.4256</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>0.003742561751217205</v>
+        <v>-0.2871</v>
       </c>
       <c r="J95" t="n">
-        <v>0.05988098801947528</v>
+        <v>-4.5936</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2880913735028773</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.609461976046036</v>
+        <v>-15.088</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.67</v>
       </c>
       <c r="I97" t="n">
-        <v>0.420709240321978</v>
+        <v>0.8605</v>
       </c>
       <c r="J97" t="n">
-        <v>6.731347845151649</v>
+        <v>13.768</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1297471223626137</v>
+        <v>0.3889</v>
       </c>
       <c r="J98" t="n">
-        <v>2.075953957801819</v>
+        <v>6.2224</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1297471223626137</v>
+        <v>0.3889</v>
       </c>
       <c r="J99" t="n">
-        <v>2.075953957801819</v>
+        <v>6.2224</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07782592247872855</v>
+        <v>0.2881</v>
       </c>
       <c r="J100" t="n">
-        <v>1.245214759659657</v>
+        <v>4.6096</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.03649371254365359</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.5838994006984575</v>
+        <v>1.2368</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.41</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4111158302807967</v>
+        <v>1.0544</v>
       </c>
       <c r="J102" t="n">
-        <v>9.455664096458325</v>
+        <v>24.2512</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3514351087037898</v>
+        <v>0.9467</v>
       </c>
       <c r="J103" t="n">
-        <v>8.083007500187165</v>
+        <v>21.7741</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.08</v>
       </c>
       <c r="I104" t="n">
-        <v>0.04669154968116641</v>
+        <v>0.194</v>
       </c>
       <c r="J104" t="n">
-        <v>1.073905642666827</v>
+        <v>4.462</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.05954066908480903</v>
+        <v>-0.1689</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.369435388950608</v>
+        <v>-3.8847</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.05954066908480903</v>
+        <v>-0.1689</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.369435388950608</v>
+        <v>-3.8847</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1516072751807111</v>
+        <v>0.3464</v>
       </c>
       <c r="J107" t="n">
-        <v>3.486967329156355</v>
+        <v>7.9672</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>0.06084145778739929</v>
+        <v>-0.1331</v>
       </c>
       <c r="J108" t="n">
-        <v>1.399353529110184</v>
+        <v>-3.0613</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>0.03484298530271675</v>
+        <v>-0.2914</v>
       </c>
       <c r="J109" t="n">
-        <v>0.8013886619624851</v>
+        <v>-6.7022</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>0.02716529805439319</v>
+        <v>-0.3239</v>
       </c>
       <c r="J110" t="n">
-        <v>0.6248018552510434</v>
+        <v>-7.4497</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I111" t="n">
-        <v>0.003245562707428012</v>
+        <v>-0.4147</v>
       </c>
       <c r="J111" t="n">
-        <v>0.07464794227084429</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2665787248407045</v>
+        <v>0.9661</v>
       </c>
       <c r="J112" t="n">
-        <v>6.397889396176907</v>
+        <v>23.1864</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2248904309937088</v>
+        <v>0.8546</v>
       </c>
       <c r="J113" t="n">
-        <v>5.39737034384901</v>
+        <v>20.5104</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2166495660985285</v>
+        <v>0.8316</v>
       </c>
       <c r="J114" t="n">
-        <v>5.199589586364683</v>
+        <v>19.9584</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0850554831529661</v>
+        <v>0.3431</v>
       </c>
       <c r="J115" t="n">
-        <v>2.041331595671187</v>
+        <v>8.234400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.89</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1256330684770234</v>
+        <v>-0.5069</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.015193643448562</v>
+        <v>-12.1656</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1676953357885672</v>
+        <v>0.3245</v>
       </c>
       <c r="J117" t="n">
-        <v>4.024688058925613</v>
+        <v>7.788</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1121235180678528</v>
+        <v>0.0805</v>
       </c>
       <c r="J118" t="n">
-        <v>2.690964433628467</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>0.004217900012518705</v>
+        <v>-0.4231</v>
       </c>
       <c r="J119" t="n">
-        <v>0.1012296003004489</v>
+        <v>-10.1544</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.004690871290315923</v>
+        <v>-0.4525</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.1125809109675822</v>
+        <v>-10.86</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.06384058244967659</v>
+        <v>-0.6287</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.532173978792238</v>
+        <v>-15.0888</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4786190625418089</v>
+        <v>1.6674</v>
       </c>
       <c r="J122" t="n">
-        <v>8.61514312575256</v>
+        <v>30.0132</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2904935830838604</v>
+        <v>1.2405</v>
       </c>
       <c r="J123" t="n">
-        <v>5.228884495509488</v>
+        <v>22.329</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1518681732120209</v>
+        <v>0.8052</v>
       </c>
       <c r="J124" t="n">
-        <v>2.733627117816376</v>
+        <v>14.4936</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>1.28</v>
       </c>
       <c r="I125" t="n">
-        <v>0.08008367946073819</v>
+        <v>0.599</v>
       </c>
       <c r="J125" t="n">
-        <v>1.441506230293288</v>
+        <v>10.782</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>1.06</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1059286445650925</v>
+        <v>0.0463</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.906715602171664</v>
+        <v>0.8334</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1742741665066068</v>
+        <v>0.353</v>
       </c>
       <c r="J127" t="n">
-        <v>3.136934997118922</v>
+        <v>6.354</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.84</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0465700702484081</v>
+        <v>-0.2077</v>
       </c>
       <c r="J128" t="n">
-        <v>0.8382612644713457</v>
+        <v>-3.7386</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.01485786901620582</v>
+        <v>-0.4861</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.2674416422917049</v>
+        <v>-8.7498</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0457233271952493</v>
+        <v>-0.5849</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.8230198895144873</v>
+        <v>-10.5282</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.05916534321744997</v>
+        <v>-0.6251</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.064976177914099</v>
+        <v>-11.2518</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>2.2</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1079924286267631</v>
+        <v>2.0593</v>
       </c>
       <c r="J132" t="n">
-        <v>1.619886429401446</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>2.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.09522686038231706</v>
+        <v>2.0208</v>
       </c>
       <c r="J133" t="n">
-        <v>1.428402905734756</v>
+        <v>30.312</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>0.02692061072636947</v>
+        <v>0.9253</v>
       </c>
       <c r="J134" t="n">
-        <v>0.4038091608955421</v>
+        <v>13.8795</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.01029740503193376</v>
+        <v>0.6331</v>
       </c>
       <c r="J135" t="n">
-        <v>0.1544610754790064</v>
+        <v>9.496499999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.04954890892274928</v>
+        <v>-0.7952</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.7432336338412392</v>
+        <v>-11.928</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>0.91</v>
       </c>
       <c r="I137" t="n">
-        <v>0.024440296796042</v>
+        <v>-0.0361</v>
       </c>
       <c r="J137" t="n">
-        <v>0.3666044519406301</v>
+        <v>-0.5415</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.89</v>
       </c>
       <c r="I138" t="n">
-        <v>0.02243573971893496</v>
+        <v>-0.0707</v>
       </c>
       <c r="J138" t="n">
-        <v>0.3365360957840244</v>
+        <v>-1.0605</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.009393056047065172</v>
+        <v>-0.645</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.1408958407059776</v>
+        <v>-9.675000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.01422747954594477</v>
+        <v>-0.7131</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.2134121931891715</v>
+        <v>-10.6965</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.01715118960884901</v>
+        <v>-0.7526</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.2572678441327351</v>
+        <v>-11.289</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.04507667653153256</v>
+        <v>0.7347</v>
       </c>
       <c r="J142" t="n">
-        <v>0.7663035010360536</v>
+        <v>12.4899</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>0.01786745215217111</v>
+        <v>-0.0113</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3037466865869088</v>
+        <v>-0.1921</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0111117060999667</v>
+        <v>-0.2703</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1888990036994339</v>
+        <v>-4.5951</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0002650194636386431</v>
+        <v>-0.5556</v>
       </c>
       <c r="J145" t="n">
-        <v>0.004505330881856933</v>
+        <v>-9.4452</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.39</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.01489168688448431</v>
+        <v>-0.8727</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.2531586770362333</v>
+        <v>-14.8359</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1192909044826133</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>2.027945376204425</v>
+        <v>16.7518</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.72</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1018851004813054</v>
+        <v>0.893</v>
       </c>
       <c r="J148" t="n">
-        <v>1.732046708182192</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.009187398965769047</v>
+        <v>0.2824</v>
       </c>
       <c r="J149" t="n">
-        <v>0.1561857824180738</v>
+        <v>4.8008</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.007153948021366414</v>
+        <v>0.2688</v>
       </c>
       <c r="J150" t="n">
-        <v>0.121617116363229</v>
+        <v>4.5696</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.04362964693825341</v>
+        <v>-0.1803</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.7417039979503081</v>
+        <v>-3.0651</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>0.08440130278074254</v>
+        <v>1.8263</v>
       </c>
       <c r="J152" t="n">
-        <v>1.603624752834108</v>
+        <v>34.6997</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.7</v>
       </c>
       <c r="I153" t="n">
-        <v>0.06252805924201855</v>
+        <v>1.4898</v>
       </c>
       <c r="J153" t="n">
-        <v>1.188033125598353</v>
+        <v>28.3062</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.3</v>
       </c>
       <c r="I154" t="n">
-        <v>0.01840792870518796</v>
+        <v>0.628</v>
       </c>
       <c r="J154" t="n">
-        <v>0.3497506453985713</v>
+        <v>11.932</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I155" t="n">
-        <v>0.01480472369816802</v>
+        <v>0.5607</v>
       </c>
       <c r="J155" t="n">
-        <v>0.2812897502651923</v>
+        <v>10.6533</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>1.11</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.004544159739881929</v>
+        <v>0.1758</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.08633903505775666</v>
+        <v>3.3402</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>0.83</v>
       </c>
       <c r="I157" t="n">
-        <v>0.01467791886913399</v>
+        <v>-0.194</v>
       </c>
       <c r="J157" t="n">
-        <v>0.2788804585135458</v>
+        <v>-3.686</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.82</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0136946285681352</v>
+        <v>-0.2102</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2601979427945687</v>
+        <v>-3.9938</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0009400857213873286</v>
+        <v>-0.4733</v>
       </c>
       <c r="J159" t="n">
-        <v>0.01786162870635924</v>
+        <v>-8.992699999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0008282282211035906</v>
+        <v>-0.5048</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.01573633620096822</v>
+        <v>-9.591200000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.009398653926051253</v>
+        <v>-0.6341</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.1785744245949738</v>
+        <v>-12.0479</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.04252074163498792</v>
+        <v>0.9378</v>
       </c>
       <c r="J162" t="n">
-        <v>0.8504148326997584</v>
+        <v>18.756</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.36</v>
       </c>
       <c r="I163" t="n">
-        <v>0.04128109521918494</v>
+        <v>0.9157</v>
       </c>
       <c r="J163" t="n">
-        <v>0.8256219043836988</v>
+        <v>18.314</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.25</v>
       </c>
       <c r="I164" t="n">
-        <v>0.02831141011608302</v>
+        <v>0.6523</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5662282023216604</v>
+        <v>13.046</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.02471177283347064</v>
+        <v>0.5288</v>
       </c>
       <c r="J165" t="n">
-        <v>0.4942354566694128</v>
+        <v>10.576</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.009358836529303263</v>
+        <v>-0.3976</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.1871767305860653</v>
+        <v>-7.952</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.19</v>
       </c>
       <c r="I167" t="n">
-        <v>0.04954563488940744</v>
+        <v>0.4074</v>
       </c>
       <c r="J167" t="n">
-        <v>0.9909126977881488</v>
+        <v>8.148</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>0.01822628862466167</v>
+        <v>-0.0279</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3645257724932334</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>0.009487417809456168</v>
+        <v>-0.1718</v>
       </c>
       <c r="J169" t="n">
-        <v>0.1897483561891234</v>
+        <v>-3.436</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.74</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.01115986167964686</v>
+        <v>-0.4422</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.2231972335929372</v>
+        <v>-8.843999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.02114443920167127</v>
+        <v>-0.5381</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.4228887840334253</v>
+        <v>-10.762</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>0.07895948488748351</v>
+        <v>1.4585</v>
       </c>
       <c r="J172" t="n">
-        <v>1.895027637299604</v>
+        <v>35.004</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.03063916400964205</v>
+        <v>0.621</v>
       </c>
       <c r="J173" t="n">
-        <v>0.7353399362314091</v>
+        <v>14.904</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.02260102547339184</v>
+        <v>0.4283</v>
       </c>
       <c r="J174" t="n">
-        <v>0.5424246113614041</v>
+        <v>10.2792</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.01068835306505747</v>
+        <v>-0.5836</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.2565204735613794</v>
+        <v>-14.0064</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.01824352855851579</v>
+        <v>-0.732</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.437844685404379</v>
+        <v>-17.568</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.03422745975454276</v>
+        <v>0.3098</v>
       </c>
       <c r="J177" t="n">
-        <v>0.8214590341090263</v>
+        <v>7.4352</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.01615323903050429</v>
+        <v>0.0418</v>
       </c>
       <c r="J178" t="n">
-        <v>0.3876777367321029</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.01516520185780491</v>
+        <v>0.0029</v>
       </c>
       <c r="J179" t="n">
-        <v>0.3639648445873179</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>0.01078513053111715</v>
+        <v>-0.1136</v>
       </c>
       <c r="J180" t="n">
-        <v>0.2588431327468116</v>
+        <v>-2.7264</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.001518311086963577</v>
+        <v>-0.277</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.03643946608712584</v>
+        <v>-6.648</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.02892814214924807</v>
+        <v>0.2924</v>
       </c>
       <c r="J182" t="n">
-        <v>0.5496347008357132</v>
+        <v>5.5556</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.79</v>
       </c>
       <c r="I183" t="n">
-        <v>0.01157283644206765</v>
+        <v>-0.3177</v>
       </c>
       <c r="J183" t="n">
-        <v>0.2198838923992853</v>
+        <v>-6.0363</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>0.01157283644206765</v>
+        <v>-0.3177</v>
       </c>
       <c r="J184" t="n">
-        <v>0.2198838923992853</v>
+        <v>-6.0363</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>0.006873894683450558</v>
+        <v>-0.4667</v>
       </c>
       <c r="J185" t="n">
-        <v>0.1306039989855606</v>
+        <v>-8.8673</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0003770047783317465</v>
+        <v>-0.6188</v>
       </c>
       <c r="J186" t="n">
-        <v>0.007163090788303184</v>
+        <v>-11.7572</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>0.06278458648057575</v>
+        <v>1.3335</v>
       </c>
       <c r="J187" t="n">
-        <v>1.192907143130939</v>
+        <v>25.3365</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.51</v>
       </c>
       <c r="I188" t="n">
-        <v>0.05242315079227675</v>
+        <v>1.1755</v>
       </c>
       <c r="J188" t="n">
-        <v>0.9960398650532581</v>
+        <v>22.3345</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0319720946911573</v>
+        <v>0.7927</v>
       </c>
       <c r="J189" t="n">
-        <v>0.6074697991319886</v>
+        <v>15.0613</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.01678026966457363</v>
+        <v>0.4641</v>
       </c>
       <c r="J190" t="n">
-        <v>0.318825123626899</v>
+        <v>8.8179</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>1.04</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.005756830759234919</v>
+        <v>0.0031</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.1093797844254635</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>0.08179204412335081</v>
+        <v>0.9998</v>
       </c>
       <c r="J192" t="n">
-        <v>1.472256794220315</v>
+        <v>17.9964</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>0.05136393307474066</v>
+        <v>0.7238</v>
       </c>
       <c r="J193" t="n">
-        <v>0.9245507953453318</v>
+        <v>13.0284</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.37</v>
       </c>
       <c r="I194" t="n">
-        <v>0.03037718405105212</v>
+        <v>0.4809</v>
       </c>
       <c r="J194" t="n">
-        <v>0.5467893129189382</v>
+        <v>8.6562</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.005809019766927832</v>
+        <v>0.0327</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.104562355804701</v>
+        <v>0.5886</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.007026200005218183</v>
+        <v>0.0149</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.1264716000939273</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.04143579087297919</v>
+        <v>0.5935</v>
       </c>
       <c r="J197" t="n">
-        <v>0.7458442357136255</v>
+        <v>10.683</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>0.01406803460109831</v>
+        <v>-0.1564</v>
       </c>
       <c r="J198" t="n">
-        <v>0.2532246228197697</v>
+        <v>-2.8152</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>0.009403315176021453</v>
+        <v>-0.3296</v>
       </c>
       <c r="J199" t="n">
-        <v>0.1692596731683862</v>
+        <v>-5.9328</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>0.007020650288444296</v>
+        <v>-0.3936</v>
       </c>
       <c r="J200" t="n">
-        <v>0.1263717051919973</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.42</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0146925712982442</v>
+        <v>-0.8358</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.2644662833683956</v>
+        <v>-15.0444</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.03628024406318074</v>
+        <v>0.6132</v>
       </c>
       <c r="J202" t="n">
-        <v>0.8707258575163378</v>
+        <v>14.7168</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.23</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0259012200199334</v>
+        <v>0.3914</v>
       </c>
       <c r="J203" t="n">
-        <v>0.6216292804784017</v>
+        <v>9.393599999999999</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0201702805906623</v>
+        <v>0.2366</v>
       </c>
       <c r="J204" t="n">
-        <v>0.4840867341758951</v>
+        <v>5.6784</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.93</v>
       </c>
       <c r="I205" t="n">
-        <v>0.009603671148941685</v>
+        <v>-0.204</v>
       </c>
       <c r="J205" t="n">
-        <v>0.2304881075746004</v>
+        <v>-4.896</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>0.002886428611591108</v>
+        <v>-0.376</v>
       </c>
       <c r="J206" t="n">
-        <v>0.06927428667818658</v>
+        <v>-9.023999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.43</v>
       </c>
       <c r="I207" t="n">
-        <v>0.06871567532198203</v>
+        <v>1.1795</v>
       </c>
       <c r="J207" t="n">
-        <v>1.649176207727569</v>
+        <v>28.308</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0305560552215413</v>
+        <v>0.5029</v>
       </c>
       <c r="J208" t="n">
-        <v>0.7333453253169913</v>
+        <v>12.0696</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.01497735552525471</v>
+        <v>-0.0184</v>
       </c>
       <c r="J209" t="n">
-        <v>0.3594565326061132</v>
+        <v>-0.4416</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.9</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0029139201145813</v>
+        <v>-0.403</v>
       </c>
       <c r="J210" t="n">
-        <v>0.06993408274995119</v>
+        <v>-9.672000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.03785182125704688</v>
+        <v>-1.1477</v>
       </c>
       <c r="J211" t="n">
-        <v>-0.9084437101691251</v>
+        <v>-27.5448</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.04507321933437802</v>
+        <v>0.417</v>
       </c>
       <c r="J212" t="n">
-        <v>0.7662447286844264</v>
+        <v>7.089</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>0.02467913387866518</v>
+        <v>0.0145</v>
       </c>
       <c r="J213" t="n">
-        <v>0.4195452759373081</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.001946455915205446</v>
+        <v>-0.4971</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.03308975055849258</v>
+        <v>-8.450699999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.002931907629529922</v>
+        <v>-0.5113</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.04984242970200868</v>
+        <v>-8.6921</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.02086505448158325</v>
+        <v>-0.7461</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.3547059261869153</v>
+        <v>-12.6837</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1505724983702929</v>
+        <v>1.1101</v>
       </c>
       <c r="J217" t="n">
-        <v>2.559732472294979</v>
+        <v>18.8717</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0653370090886255</v>
+        <v>0.6187</v>
       </c>
       <c r="J218" t="n">
-        <v>1.110729154506633</v>
+        <v>10.5179</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.01987583692214449</v>
+        <v>0.2509</v>
       </c>
       <c r="J219" t="n">
-        <v>0.3378892276764563</v>
+        <v>4.2653</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.01604381080121424</v>
+        <v>0.2215</v>
       </c>
       <c r="J220" t="n">
-        <v>0.2727447836206421</v>
+        <v>3.7655</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.06985755375911049</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-1.187578413904878</v>
+        <v>-9.0746</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1175515253486671</v>
+        <v>1.6902</v>
       </c>
       <c r="J222" t="n">
-        <v>2.233478981624674</v>
+        <v>32.1138</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>0.06458805657789467</v>
+        <v>1.183</v>
       </c>
       <c r="J223" t="n">
-        <v>1.227173074979999</v>
+        <v>22.477</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>1.32</v>
       </c>
       <c r="I224" t="n">
-        <v>0.02780324893401876</v>
+        <v>0.6931</v>
       </c>
       <c r="J224" t="n">
-        <v>0.5282617297463564</v>
+        <v>13.1689</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.003800273119402037</v>
+        <v>0.4145</v>
       </c>
       <c r="J225" t="n">
-        <v>0.0722051892686387</v>
+        <v>7.8755</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0002770690840439606</v>
+        <v>0.3662</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.005264312596835252</v>
+        <v>6.9578</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.04270417410324619</v>
+        <v>0.4124</v>
       </c>
       <c r="J227" t="n">
-        <v>0.8113793079616777</v>
+        <v>7.8356</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>0.02210778472307125</v>
+        <v>-0.0161</v>
       </c>
       <c r="J228" t="n">
-        <v>0.4200479097383538</v>
+        <v>-0.3059</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>0.006614957462109283</v>
+        <v>-0.3159</v>
       </c>
       <c r="J229" t="n">
-        <v>0.1256841917800764</v>
+        <v>-6.0021</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.54</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.01480509486029943</v>
+        <v>-0.6786</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.2812968023456892</v>
+        <v>-12.8934</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.02523242351842562</v>
+        <v>-0.8144</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.4794160468500868</v>
+        <v>-15.4736</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.05605128430362118</v>
+        <v>0.8107</v>
       </c>
       <c r="J232" t="n">
-        <v>1.345230823286908</v>
+        <v>19.4568</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.03807419426625495</v>
+        <v>0.59</v>
       </c>
       <c r="J233" t="n">
-        <v>0.9137806623901188</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0288948537985198</v>
+        <v>0.4515</v>
       </c>
       <c r="J234" t="n">
-        <v>0.6934764911644751</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.13</v>
       </c>
       <c r="I235" t="n">
-        <v>0.02578904090777875</v>
+        <v>0.3875</v>
       </c>
       <c r="J235" t="n">
-        <v>0.6189369817866901</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.02505032880764841</v>
+        <v>-0.5603</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.6012078913835619</v>
+        <v>-13.4472</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.22</v>
       </c>
       <c r="I237" t="n">
-        <v>0.04112868752481291</v>
+        <v>0.4368</v>
       </c>
       <c r="J237" t="n">
-        <v>0.9870885005955099</v>
+        <v>10.4832</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.03067754394355952</v>
+        <v>0.2712</v>
       </c>
       <c r="J238" t="n">
-        <v>0.7362610546454285</v>
+        <v>6.5088</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>0.00774571943467805</v>
+        <v>-0.2874</v>
       </c>
       <c r="J239" t="n">
-        <v>0.1858972664322732</v>
+        <v>-6.8976</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.002930998103095266</v>
+        <v>-0.4517</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.07034395447428637</v>
+        <v>-10.8408</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.003915951077993404</v>
+        <v>-0.4655</v>
       </c>
       <c r="J241" t="n">
-        <v>-0.0939828258718417</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.43</v>
       </c>
       <c r="I242" t="n">
-        <v>0.04826156586386783</v>
+        <v>0.6143</v>
       </c>
       <c r="J242" t="n">
-        <v>0.9652313172773566</v>
+        <v>12.286</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.03212080907160689</v>
+        <v>0.4483</v>
       </c>
       <c r="J243" t="n">
-        <v>0.6424161814321377</v>
+        <v>8.965999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.02069061542780766</v>
+        <v>0.2733</v>
       </c>
       <c r="J244" t="n">
-        <v>0.4138123085561532</v>
+        <v>5.466</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.17</v>
       </c>
       <c r="I245" t="n">
-        <v>0.01846639567986781</v>
+        <v>0.2418</v>
       </c>
       <c r="J245" t="n">
-        <v>0.3693279135973562</v>
+        <v>4.836</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>1.01</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.001059692388664647</v>
+        <v>-0.0415</v>
       </c>
       <c r="J246" t="n">
-        <v>-0.02119384777329293</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.48</v>
       </c>
       <c r="I247" t="n">
-        <v>0.04791476581026627</v>
+        <v>0.7461</v>
       </c>
       <c r="J247" t="n">
-        <v>0.9582953162053254</v>
+        <v>14.922</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.01570593451456093</v>
+        <v>0.0133</v>
       </c>
       <c r="J248" t="n">
-        <v>0.3141186902912186</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>0.01477328998090897</v>
+        <v>-0.0575</v>
       </c>
       <c r="J249" t="n">
-        <v>0.2954657996181793</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>0.007198945698861776</v>
+        <v>-0.2889</v>
       </c>
       <c r="J250" t="n">
-        <v>0.1439789139772355</v>
+        <v>-5.778</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.01072085642933752</v>
+        <v>-0.6435</v>
       </c>
       <c r="J251" t="n">
-        <v>-0.2144171285867504</v>
+        <v>-12.87</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.61</v>
       </c>
       <c r="I252" t="n">
-        <v>0.05454019764926007</v>
+        <v>0.9105</v>
       </c>
       <c r="J252" t="n">
-        <v>1.145344150634461</v>
+        <v>19.1205</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>0.01442619338500944</v>
+        <v>-0.1145</v>
       </c>
       <c r="J253" t="n">
-        <v>0.3029500610851983</v>
+        <v>-2.4045</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>0.01256583144240691</v>
+        <v>-0.2025</v>
       </c>
       <c r="J254" t="n">
-        <v>0.2638824602905452</v>
+        <v>-4.2525</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>0.00662792763558584</v>
+        <v>-0.3664</v>
       </c>
       <c r="J255" t="n">
-        <v>0.1391864803473026</v>
+        <v>-7.6944</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.42</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.01653592713223214</v>
+        <v>-0.8475</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.3472544697768749</v>
+        <v>-17.7975</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.62</v>
       </c>
       <c r="I257" t="n">
-        <v>0.07533661378018711</v>
+        <v>1.4303</v>
       </c>
       <c r="J257" t="n">
-        <v>1.582068889383929</v>
+        <v>30.0363</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.6</v>
       </c>
       <c r="I258" t="n">
-        <v>0.07263932460519583</v>
+        <v>1.3924</v>
       </c>
       <c r="J258" t="n">
-        <v>1.525425816709112</v>
+        <v>29.2404</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.01928024430404338</v>
+        <v>0.4552</v>
       </c>
       <c r="J259" t="n">
-        <v>0.404885130384911</v>
+        <v>9.559200000000001</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.008447314861185461</v>
+        <v>0.241</v>
       </c>
       <c r="J260" t="n">
-        <v>0.1773936120848947</v>
+        <v>5.061</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.04166046545214176</v>
+        <v>-0.8783</v>
       </c>
       <c r="J261" t="n">
-        <v>-0.874869774494977</v>
+        <v>-18.4443</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>0.05198652177450433</v>
+        <v>0.9054</v>
       </c>
       <c r="J262" t="n">
-        <v>1.819528262107652</v>
+        <v>31.689</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.02872050869815703</v>
+        <v>0.4531</v>
       </c>
       <c r="J263" t="n">
-        <v>1.005217804435496</v>
+        <v>15.8585</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>0.009328003560007623</v>
+        <v>-0.2059</v>
       </c>
       <c r="J264" t="n">
-        <v>0.3264801246002668</v>
+        <v>-7.2065</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.73</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.002602343900364384</v>
+        <v>-0.4884</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.09108203651275343</v>
+        <v>-17.094</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.006919775786243729</v>
+        <v>-0.5782</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.2421921525185305</v>
+        <v>-20.237</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>2.04</v>
       </c>
       <c r="I267" t="n">
-        <v>0.130405894380665</v>
+        <v>2.0593</v>
       </c>
       <c r="J267" t="n">
-        <v>4.564206303323274</v>
+        <v>72.07550000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.02088968999669139</v>
+        <v>0.4904</v>
       </c>
       <c r="J268" t="n">
-        <v>0.7311391498841985</v>
+        <v>17.164</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.01358940177981525</v>
+        <v>0.3207</v>
       </c>
       <c r="J269" t="n">
-        <v>0.4756290622935339</v>
+        <v>11.2245</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.83</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.02712531202784186</v>
+        <v>-0.6581</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.9493859209744649</v>
+        <v>-23.0335</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.02850189772988268</v>
+        <v>-0.6825</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.9975664205458937</v>
+        <v>-23.8875</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1010305586636357</v>
+        <v>1.0816</v>
       </c>
       <c r="J272" t="n">
-        <v>3.435038994563615</v>
+        <v>36.7744</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.04416567024850901</v>
+        <v>0.6236</v>
       </c>
       <c r="J273" t="n">
-        <v>1.501632788449306</v>
+        <v>21.2024</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.02937869890115215</v>
+        <v>0.4549</v>
       </c>
       <c r="J274" t="n">
-        <v>0.9988757626391732</v>
+        <v>15.4666</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.15</v>
       </c>
       <c r="I275" t="n">
-        <v>0.02766877730934023</v>
+        <v>0.4158</v>
       </c>
       <c r="J275" t="n">
-        <v>0.9407384285175677</v>
+        <v>14.1372</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.06217921551826516</v>
+        <v>-0.6697</v>
       </c>
       <c r="J276" t="n">
-        <v>-2.114093327621016</v>
+        <v>-22.7698</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.06493840026128052</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>2.207905608883538</v>
+        <v>24.0788</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.02177894324292182</v>
+        <v>0.133</v>
       </c>
       <c r="J278" t="n">
-        <v>0.7404840702593418</v>
+        <v>4.522</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>0.01170573968958895</v>
+        <v>-0.1566</v>
       </c>
       <c r="J279" t="n">
-        <v>0.3979951494460242</v>
+        <v>-5.3244</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.7</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.01309781616865494</v>
+        <v>-0.5122</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.445325749734268</v>
+        <v>-17.4148</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.01530281268265135</v>
+        <v>-0.5384</v>
       </c>
       <c r="J281" t="n">
-        <v>-0.5202956312101458</v>
+        <v>-18.3056</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.37</v>
       </c>
       <c r="I282" t="n">
-        <v>0.08627377951263386</v>
+        <v>0.9792</v>
       </c>
       <c r="J282" t="n">
-        <v>2.070570708303213</v>
+        <v>23.5008</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0805013648239933</v>
+        <v>0.9354</v>
       </c>
       <c r="J283" t="n">
-        <v>1.932032755775839</v>
+        <v>22.4496</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.06322496221802398</v>
+        <v>0.7994</v>
       </c>
       <c r="J284" t="n">
-        <v>1.517399093232576</v>
+        <v>19.1856</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.9</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.03965646647360889</v>
+        <v>-0.4591</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.9517551953666133</v>
+        <v>-11.0184</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.06264813028971626</v>
+        <v>-0.6675</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.50355512695319</v>
+        <v>-16.02</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.02905631952360331</v>
+        <v>0.2942</v>
       </c>
       <c r="J287" t="n">
-        <v>0.6973516685664793</v>
+        <v>7.0608</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.02802812340455059</v>
+        <v>0.2783</v>
       </c>
       <c r="J288" t="n">
-        <v>0.672674961709214</v>
+        <v>6.6792</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>0.01452980455139179</v>
+        <v>-0.0391</v>
       </c>
       <c r="J289" t="n">
-        <v>0.348715309233403</v>
+        <v>-0.9384</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>0.00773654746444964</v>
+        <v>-0.192</v>
       </c>
       <c r="J290" t="n">
-        <v>0.1856771391467913</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.00429478087571231</v>
+        <v>-0.3686</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.1030747410170954</v>
+        <v>-8.846399999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>0.0657718512240736</v>
+        <v>1.3037</v>
       </c>
       <c r="J292" t="n">
-        <v>1.578524429377766</v>
+        <v>31.2888</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.25</v>
       </c>
       <c r="I293" t="n">
-        <v>0.03194816379711732</v>
+        <v>0.6978</v>
       </c>
       <c r="J293" t="n">
-        <v>0.7667559311308156</v>
+        <v>16.7472</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.02412213060669005</v>
+        <v>0.5139</v>
       </c>
       <c r="J294" t="n">
-        <v>0.5789311345605612</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>0.003633355278410414</v>
+        <v>-0.1649</v>
       </c>
       <c r="J295" t="n">
-        <v>0.08720052668184994</v>
+        <v>-3.9576</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.01538929408517792</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.3693430580442701</v>
+        <v>-15.4968</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.39</v>
       </c>
       <c r="I297" t="n">
-        <v>0.05477533834016503</v>
+        <v>0.6418</v>
       </c>
       <c r="J297" t="n">
-        <v>1.314608120163961</v>
+        <v>15.4032</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>0.01563644662685214</v>
+        <v>-0.0189</v>
       </c>
       <c r="J298" t="n">
-        <v>0.3752747190444514</v>
+        <v>-0.4536</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>0.98</v>
       </c>
       <c r="I299" t="n">
-        <v>0.01490257301427865</v>
+        <v>-0.0477</v>
       </c>
       <c r="J299" t="n">
-        <v>0.3576617523426877</v>
+        <v>-1.1448</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>0.01093356983721759</v>
+        <v>-0.1649</v>
       </c>
       <c r="J300" t="n">
-        <v>0.2624056760932222</v>
+        <v>-3.9576</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.02312934420719776</v>
+        <v>-0.6545</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.5551042609727462</v>
+        <v>-15.708</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.75</v>
       </c>
       <c r="I302" t="n">
-        <v>0.07885102209379188</v>
+        <v>1.6464</v>
       </c>
       <c r="J302" t="n">
-        <v>1.577020441875838</v>
+        <v>32.928</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>1.56</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0565552477216069</v>
+        <v>1.2919</v>
       </c>
       <c r="J303" t="n">
-        <v>1.131104954432138</v>
+        <v>25.838</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.02608433997641171</v>
+        <v>0.6834</v>
       </c>
       <c r="J304" t="n">
-        <v>0.5216867995282343</v>
+        <v>13.668</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>1.23</v>
       </c>
       <c r="I305" t="n">
-        <v>0.0196863395044706</v>
+        <v>0.5301</v>
       </c>
       <c r="J305" t="n">
-        <v>0.393726790089412</v>
+        <v>10.602</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.04503054879039826</v>
+        <v>-1.0161</v>
       </c>
       <c r="J306" t="n">
-        <v>-0.9006109758079652</v>
+        <v>-20.322</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.78</v>
       </c>
       <c r="I307" t="n">
-        <v>0.09283246116399931</v>
+        <v>1.0992</v>
       </c>
       <c r="J307" t="n">
-        <v>1.856649223279986</v>
+        <v>21.984</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I308" t="n">
-        <v>0.005063014175743735</v>
+        <v>-0.2813</v>
       </c>
       <c r="J308" t="n">
-        <v>0.1012602835148747</v>
+        <v>-5.626</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>0.74</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.005782419114403445</v>
+        <v>-0.4476</v>
       </c>
       <c r="J309" t="n">
-        <v>-0.1156483822880689</v>
+        <v>-8.952</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.01583950976005265</v>
+        <v>-0.5814</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.316790195201053</v>
+        <v>-11.628</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.02377368355459734</v>
+        <v>-0.6813</v>
       </c>
       <c r="J311" t="n">
-        <v>-0.4754736710919468</v>
+        <v>-13.626</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.18</v>
       </c>
       <c r="I312" t="n">
-        <v>0.03161332552534155</v>
+        <v>0.3853</v>
       </c>
       <c r="J312" t="n">
-        <v>0.7271064870828557</v>
+        <v>8.8619</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>0.01762152862256099</v>
+        <v>-0.0592</v>
       </c>
       <c r="J313" t="n">
-        <v>0.4052951583189028</v>
+        <v>-1.3616</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>0.01703394752132868</v>
+        <v>-0.0805</v>
       </c>
       <c r="J314" t="n">
-        <v>0.3917807929905595</v>
+        <v>-1.8515</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>0.01042066442794291</v>
+        <v>-0.3138</v>
       </c>
       <c r="J315" t="n">
-        <v>0.2396752818426869</v>
+        <v>-7.2174</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.001390920839354767</v>
+        <v>-0.5686</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.03199117930515963</v>
+        <v>-13.0778</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.05480802991939208</v>
+        <v>0.4741</v>
       </c>
       <c r="J317" t="n">
-        <v>1.260584688146018</v>
+        <v>10.9043</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.25</v>
       </c>
       <c r="I318" t="n">
-        <v>0.04509087092886978</v>
+        <v>0.4059</v>
       </c>
       <c r="J318" t="n">
-        <v>1.037090031364005</v>
+        <v>9.335699999999999</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I319" t="n">
-        <v>0.04127647310483637</v>
+        <v>0.3774</v>
       </c>
       <c r="J319" t="n">
-        <v>0.9493588814112365</v>
+        <v>8.680199999999999</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.008739092079300728</v>
+        <v>0.0439</v>
       </c>
       <c r="J320" t="n">
-        <v>0.2009991178239167</v>
+        <v>1.0097</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.01978286628980268</v>
+        <v>-0.279</v>
       </c>
       <c r="J321" t="n">
-        <v>-0.4550059246654617</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="322">
@@ -15241,10 +15229,10 @@
         <v>1.75</v>
       </c>
       <c r="I322" t="n">
-        <v>0.07186259989406826</v>
+        <v>1.5769</v>
       </c>
       <c r="J322" t="n">
-        <v>1.221664198199161</v>
+        <v>26.8073</v>
       </c>
     </row>
     <row r="323">
@@ -15281,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0452707530720885</v>
+        <v>1.1741</v>
       </c>
       <c r="J323" t="n">
-        <v>0.7696028022255045</v>
+        <v>19.9597</v>
       </c>
     </row>
     <row r="324">
@@ -15321,10 +15309,10 @@
         <v>1.4</v>
       </c>
       <c r="I324" t="n">
-        <v>0.03024000641243948</v>
+        <v>0.8451</v>
       </c>
       <c r="J324" t="n">
-        <v>0.5140801090114712</v>
+        <v>14.3667</v>
       </c>
     </row>
     <row r="325">
@@ -15361,10 +15349,10 @@
         <v>1.39</v>
       </c>
       <c r="I325" t="n">
-        <v>0.02902687705402762</v>
+        <v>0.823</v>
       </c>
       <c r="J325" t="n">
-        <v>0.4934569099184695</v>
+        <v>13.991</v>
       </c>
     </row>
     <row r="326">
@@ -15401,10 +15389,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.009716873442523409</v>
+        <v>0.4892</v>
       </c>
       <c r="J326" t="n">
-        <v>0.165186848522898</v>
+        <v>8.3164</v>
       </c>
     </row>
     <row r="327">
@@ -15441,10 +15429,10 @@
         <v>1.04</v>
       </c>
       <c r="I327" t="n">
-        <v>0.03566489276742288</v>
+        <v>0.2431</v>
       </c>
       <c r="J327" t="n">
-        <v>0.606303177046189</v>
+        <v>4.1327</v>
       </c>
     </row>
     <row r="328">
@@ -15481,10 +15469,10 @@
         <v>0.82</v>
       </c>
       <c r="I328" t="n">
-        <v>0.01428212672240658</v>
+        <v>-0.2062</v>
       </c>
       <c r="J328" t="n">
-        <v>0.2427961542809119</v>
+        <v>-3.5054</v>
       </c>
     </row>
     <row r="329">
@@ -15521,10 +15509,10 @@
         <v>0.7</v>
       </c>
       <c r="I329" t="n">
-        <v>0.003946241484299309</v>
+        <v>-0.4083</v>
       </c>
       <c r="J329" t="n">
-        <v>0.06708610523308825</v>
+        <v>-6.9411</v>
       </c>
     </row>
     <row r="330">
@@ -15561,10 +15549,10 @@
         <v>0.63</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.001541113787499826</v>
+        <v>-0.5315</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.02619893438749704</v>
+        <v>-9.035500000000001</v>
       </c>
     </row>
     <row r="331">
@@ -15601,10 +15589,10 @@
         <v>0.3</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.03241937672908966</v>
+        <v>-0.9563</v>
       </c>
       <c r="J331" t="n">
-        <v>-0.5511294043945243</v>
+        <v>-16.2571</v>
       </c>
     </row>
     <row r="332">
@@ -15641,10 +15629,10 @@
         <v>1.56</v>
       </c>
       <c r="I332" t="n">
-        <v>0.06953492256093485</v>
+        <v>1.3326</v>
       </c>
       <c r="J332" t="n">
-        <v>1.460233373779632</v>
+        <v>27.9846</v>
       </c>
     </row>
     <row r="333">
@@ -15681,10 +15669,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>0.06306730627031824</v>
+        <v>1.2343</v>
       </c>
       <c r="J333" t="n">
-        <v>1.324413431676683</v>
+        <v>25.9203</v>
       </c>
     </row>
     <row r="334">
@@ -15721,10 +15709,10 @@
         <v>1.28</v>
       </c>
       <c r="I334" t="n">
-        <v>0.03317354611088564</v>
+        <v>0.7342</v>
       </c>
       <c r="J334" t="n">
-        <v>0.6966444683285984</v>
+        <v>15.4182</v>
       </c>
     </row>
     <row r="335">
@@ -15761,10 +15749,10 @@
         <v>0.9</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.01369355871077152</v>
+        <v>-0.4809</v>
       </c>
       <c r="J335" t="n">
-        <v>-0.2875647329262018</v>
+        <v>-10.0989</v>
       </c>
     </row>
     <row r="336">
@@ -15801,10 +15789,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.02242622811504782</v>
+        <v>-0.6617</v>
       </c>
       <c r="J336" t="n">
-        <v>-0.4709507904160042</v>
+        <v>-13.8957</v>
       </c>
     </row>
     <row r="337">
@@ -15841,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.04172525915368525</v>
+        <v>0.4367</v>
       </c>
       <c r="J337" t="n">
-        <v>0.8762304422273901</v>
+        <v>9.1707</v>
       </c>
     </row>
     <row r="338">
@@ -15881,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>0.01752980992273858</v>
+        <v>-0.0487</v>
       </c>
       <c r="J338" t="n">
-        <v>0.3681260083775102</v>
+        <v>-1.0227</v>
       </c>
     </row>
     <row r="339">
@@ -15921,10 +15909,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>0.01115331999177042</v>
+        <v>-0.217</v>
       </c>
       <c r="J339" t="n">
-        <v>0.2342197198271788</v>
+        <v>-4.557</v>
       </c>
     </row>
     <row r="340">
@@ -15961,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>0.005993102498256212</v>
+        <v>-0.3216</v>
       </c>
       <c r="J340" t="n">
-        <v>0.1258551524633805</v>
+        <v>-6.7536</v>
       </c>
     </row>
     <row r="341">
@@ -16001,10 +15989,10 @@
         <v>0.59</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.01625103708268769</v>
+        <v>-0.6405</v>
       </c>
       <c r="J341" t="n">
-        <v>-0.3412717787364415</v>
+        <v>-13.4505</v>
       </c>
     </row>
     <row r="342">
@@ -16041,10 +16029,10 @@
         <v>1.7</v>
       </c>
       <c r="I342" t="n">
-        <v>0.07523177886770549</v>
+        <v>1.5337</v>
       </c>
       <c r="J342" t="n">
-        <v>1.203708461883288</v>
+        <v>24.5392</v>
       </c>
     </row>
     <row r="343">
@@ -16081,10 +16069,10 @@
         <v>1.51</v>
       </c>
       <c r="I343" t="n">
-        <v>0.05221052735348719</v>
+        <v>1.1687</v>
       </c>
       <c r="J343" t="n">
-        <v>0.835368437655795</v>
+        <v>18.6992</v>
       </c>
     </row>
     <row r="344">
@@ -16121,10 +16109,10 @@
         <v>1.22</v>
       </c>
       <c r="I344" t="n">
-        <v>0.01992717637061456</v>
+        <v>0.4825</v>
       </c>
       <c r="J344" t="n">
-        <v>0.318834821929833</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="345">
@@ -16161,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I345" t="n">
-        <v>0.0162202697220819</v>
+        <v>0.4095</v>
       </c>
       <c r="J345" t="n">
-        <v>0.2595243155533104</v>
+        <v>6.552</v>
       </c>
     </row>
     <row r="346">
@@ -16201,10 +16189,10 @@
         <v>1.14</v>
       </c>
       <c r="I346" t="n">
-        <v>0.009974800142083122</v>
+        <v>0.2837</v>
       </c>
       <c r="J346" t="n">
-        <v>0.15959680227333</v>
+        <v>4.5392</v>
       </c>
     </row>
     <row r="347">
@@ -16241,10 +16229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I347" t="n">
-        <v>0.01889957194878223</v>
+        <v>-0.2005</v>
       </c>
       <c r="J347" t="n">
-        <v>0.3023931511805156</v>
+        <v>-3.208</v>
       </c>
     </row>
     <row r="348">
@@ -16281,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>0.01748601479736046</v>
+        <v>-0.2164</v>
       </c>
       <c r="J348" t="n">
-        <v>0.2797762367577673</v>
+        <v>-3.4624</v>
       </c>
     </row>
     <row r="349">
@@ -16321,10 +16309,10 @@
         <v>0.7</v>
       </c>
       <c r="I349" t="n">
-        <v>0.003931977601365367</v>
+        <v>-0.3753</v>
       </c>
       <c r="J349" t="n">
-        <v>0.06291164162184587</v>
+        <v>-6.0048</v>
       </c>
     </row>
     <row r="350">
@@ -16361,10 +16349,10 @@
         <v>0.67</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0003875575153208348</v>
+        <v>-0.4269</v>
       </c>
       <c r="J350" t="n">
-        <v>0.006200920245133357</v>
+        <v>-6.8304</v>
       </c>
     </row>
     <row r="351">
@@ -16401,10 +16389,10 @@
         <v>0.3</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.04849617972320822</v>
+        <v>-0.9503</v>
       </c>
       <c r="J351" t="n">
-        <v>-0.7759388755713315</v>
+        <v>-15.2048</v>
       </c>
     </row>
     <row r="352">
@@ -16441,10 +16429,10 @@
         <v>1.5</v>
       </c>
       <c r="I352" t="n">
-        <v>0.04653437406623818</v>
+        <v>1.1413</v>
       </c>
       <c r="J352" t="n">
-        <v>0.8376187331922873</v>
+        <v>20.5434</v>
       </c>
     </row>
     <row r="353">
@@ -16481,10 +16469,10 @@
         <v>1.47</v>
       </c>
       <c r="I353" t="n">
-        <v>0.04290681302770442</v>
+        <v>1.0787</v>
       </c>
       <c r="J353" t="n">
-        <v>0.7723226344986797</v>
+        <v>19.4166</v>
       </c>
     </row>
     <row r="354">
@@ -16521,10 +16509,10 @@
         <v>1.41</v>
       </c>
       <c r="I354" t="n">
-        <v>0.03594336507840223</v>
+        <v>0.9469</v>
       </c>
       <c r="J354" t="n">
-        <v>0.6469805714112401</v>
+        <v>17.0442</v>
       </c>
     </row>
     <row r="355">
@@ -16561,10 +16549,10 @@
         <v>1.36</v>
       </c>
       <c r="I355" t="n">
-        <v>0.03121195697904764</v>
+        <v>0.8146</v>
       </c>
       <c r="J355" t="n">
-        <v>0.5618152256228576</v>
+        <v>14.6628</v>
       </c>
     </row>
     <row r="356">
@@ -16601,10 +16589,10 @@
         <v>1.09</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.00123746318306648</v>
+        <v>0.1455</v>
       </c>
       <c r="J356" t="n">
-        <v>-0.02227433729519664</v>
+        <v>2.619</v>
       </c>
     </row>
     <row r="357">
@@ -16641,10 +16629,10 @@
         <v>1.25</v>
       </c>
       <c r="I357" t="n">
-        <v>0.06499040918568712</v>
+        <v>0.5296</v>
       </c>
       <c r="J357" t="n">
-        <v>1.169827365342368</v>
+        <v>9.5328</v>
       </c>
     </row>
     <row r="358">
@@ -16681,10 +16669,10 @@
         <v>0.82</v>
       </c>
       <c r="I358" t="n">
-        <v>0.004625963768431171</v>
+        <v>-0.2601</v>
       </c>
       <c r="J358" t="n">
-        <v>0.08326734783176108</v>
+        <v>-4.6818</v>
       </c>
     </row>
     <row r="359">
@@ -16721,10 +16709,10 @@
         <v>0.75</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.003013067102312621</v>
+        <v>-0.3928</v>
       </c>
       <c r="J359" t="n">
-        <v>-0.05423520784162719</v>
+        <v>-7.0704</v>
       </c>
     </row>
     <row r="360">
@@ -16761,10 +16749,10 @@
         <v>0.61</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.02217197573341132</v>
+        <v>-0.5939</v>
       </c>
       <c r="J360" t="n">
-        <v>-0.3990955632014037</v>
+        <v>-10.6902</v>
       </c>
     </row>
     <row r="361">
@@ -16801,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.02919626282477165</v>
+        <v>-0.659</v>
       </c>
       <c r="J361" t="n">
-        <v>-0.5255327308458897</v>
+        <v>-11.862</v>
       </c>
     </row>
     <row r="362">
@@ -16841,10 +16829,10 @@
         <v>1.27</v>
       </c>
       <c r="I362" t="n">
-        <v>0.04365525437254193</v>
+        <v>0.7786</v>
       </c>
       <c r="J362" t="n">
-        <v>1.004070850568464</v>
+        <v>17.9078</v>
       </c>
     </row>
     <row r="363">
@@ -16881,10 +16869,10 @@
         <v>1.26</v>
       </c>
       <c r="I363" t="n">
-        <v>0.04226051973415735</v>
+        <v>0.7549</v>
       </c>
       <c r="J363" t="n">
-        <v>0.971991953885619</v>
+        <v>17.3627</v>
       </c>
     </row>
     <row r="364">
@@ -16921,10 +16909,10 @@
         <v>1.08</v>
       </c>
       <c r="I364" t="n">
-        <v>0.01979666468652982</v>
+        <v>0.2375</v>
       </c>
       <c r="J364" t="n">
-        <v>0.4553232877901858</v>
+        <v>5.4625</v>
       </c>
     </row>
     <row r="365">
@@ -16961,10 +16949,10 @@
         <v>1.08</v>
       </c>
       <c r="I365" t="n">
-        <v>0.01979666468652982</v>
+        <v>0.2375</v>
       </c>
       <c r="J365" t="n">
-        <v>0.4553232877901858</v>
+        <v>5.4625</v>
       </c>
     </row>
     <row r="366">
@@ -17001,10 +16989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.01597261997339878</v>
+        <v>-0.6782</v>
       </c>
       <c r="J366" t="n">
-        <v>-0.3673702593881718</v>
+        <v>-15.5986</v>
       </c>
     </row>
     <row r="367">
@@ -17041,10 +17029,10 @@
         <v>1.25</v>
       </c>
       <c r="I367" t="n">
-        <v>0.04632122466988861</v>
+        <v>0.4717</v>
       </c>
       <c r="J367" t="n">
-        <v>1.065388167407438</v>
+        <v>10.8491</v>
       </c>
     </row>
     <row r="368">
@@ -17081,10 +17069,10 @@
         <v>1.03</v>
       </c>
       <c r="I368" t="n">
-        <v>0.02271001816563457</v>
+        <v>0.1158</v>
       </c>
       <c r="J368" t="n">
-        <v>0.522330417809595</v>
+        <v>2.6634</v>
       </c>
     </row>
     <row r="369">
@@ -17121,10 +17109,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.02064594402969518</v>
+        <v>0.0672</v>
       </c>
       <c r="J369" t="n">
-        <v>0.4748567126829892</v>
+        <v>1.5456</v>
       </c>
     </row>
     <row r="370">
@@ -17161,10 +17149,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.001054695062667223</v>
+        <v>-0.3851</v>
       </c>
       <c r="J370" t="n">
-        <v>-0.02425798644134614</v>
+        <v>-8.8573</v>
       </c>
     </row>
     <row r="371">
@@ -17201,10 +17189,10 @@
         <v>0.66</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.01546915168710688</v>
+        <v>-0.5624</v>
       </c>
       <c r="J371" t="n">
-        <v>-0.3557904888034583</v>
+        <v>-12.9352</v>
       </c>
     </row>
     <row r="372">
@@ -17241,10 +17229,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.04961591874751221</v>
+        <v>0.8783</v>
       </c>
       <c r="J372" t="n">
-        <v>1.091550212445269</v>
+        <v>19.3226</v>
       </c>
     </row>
     <row r="373">
@@ -17281,10 +17269,10 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>0.04683654834118052</v>
+        <v>0.8327</v>
       </c>
       <c r="J373" t="n">
-        <v>1.030404063505971</v>
+        <v>18.3194</v>
       </c>
     </row>
     <row r="374">
@@ -17321,10 +17309,10 @@
         <v>1.17</v>
       </c>
       <c r="I374" t="n">
-        <v>0.02935659147760285</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J374" t="n">
-        <v>0.6458450125072627</v>
+        <v>11.1672</v>
       </c>
     </row>
     <row r="375">
@@ -17361,10 +17349,10 @@
         <v>0.98</v>
       </c>
       <c r="I375" t="n">
-        <v>0.005955786265498773</v>
+        <v>-0.1954</v>
       </c>
       <c r="J375" t="n">
-        <v>0.131027297840973</v>
+        <v>-4.2988</v>
       </c>
     </row>
     <row r="376">
@@ -17401,10 +17389,10 @@
         <v>0.87</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.008999732864111015</v>
+        <v>-0.5346</v>
       </c>
       <c r="J376" t="n">
-        <v>-0.1979941230104423</v>
+        <v>-11.7612</v>
       </c>
     </row>
     <row r="377">
@@ -17441,10 +17429,10 @@
         <v>1.24</v>
       </c>
       <c r="I377" t="n">
-        <v>0.05146946574738263</v>
+        <v>0.4868</v>
       </c>
       <c r="J377" t="n">
-        <v>1.132328246442418</v>
+        <v>10.7096</v>
       </c>
     </row>
     <row r="378">
@@ -17481,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I378" t="n">
-        <v>0.03218445295602876</v>
+        <v>0.2074</v>
       </c>
       <c r="J378" t="n">
-        <v>0.7080579650326326</v>
+        <v>4.5628</v>
       </c>
     </row>
     <row r="379">
@@ -17521,10 +17509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I379" t="n">
-        <v>0.007165138252550487</v>
+        <v>-0.3288</v>
       </c>
       <c r="J379" t="n">
-        <v>0.1576330415561107</v>
+        <v>-7.2336</v>
       </c>
     </row>
     <row r="380">
@@ -17561,10 +17549,10 @@
         <v>0.74</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.0002977327642876837</v>
+        <v>-0.4351</v>
       </c>
       <c r="J380" t="n">
-        <v>-0.006550120814329041</v>
+        <v>-9.5722</v>
       </c>
     </row>
     <row r="381">
@@ -17601,10 +17589,10 @@
         <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.02658185774015826</v>
+        <v>-0.7466</v>
       </c>
       <c r="J381" t="n">
-        <v>-0.5848008702834817</v>
+        <v>-16.4252</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.1922</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.5831</v>
       </c>
       <c r="D2" t="n">
         <v>2.4841</v>
@@ -545,7 +545,7 @@
         <v>6.9491</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.5296</v>
       </c>
       <c r="D3" t="n">
         <v>2.3859</v>
@@ -591,7 +591,7 @@
         <v>5.6345</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.2402</v>
       </c>
       <c r="D4" t="n">
         <v>1.8549</v>
@@ -637,7 +637,7 @@
         <v>5.1144</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.1258</v>
       </c>
       <c r="D5" t="n">
         <v>1.6447</v>
@@ -683,7 +683,7 @@
         <v>4.965</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.0929</v>
       </c>
       <c r="D6" t="n">
         <v>1.5844</v>
@@ -729,7 +729,7 @@
         <v>4.3579</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>1.3391</v>
@@ -775,7 +775,7 @@
         <v>3.9571</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.871</v>
       </c>
       <c r="D8" t="n">
         <v>1.1772</v>
@@ -821,7 +821,7 @@
         <v>3.7469</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.8247</v>
       </c>
       <c r="D9" t="n">
         <v>1.0923</v>
@@ -867,7 +867,7 @@
         <v>3.7146</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.8176</v>
       </c>
       <c r="D10" t="n">
         <v>1.0793</v>
@@ -913,7 +913,7 @@
         <v>3.713</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.8173</v>
       </c>
       <c r="D11" t="n">
         <v>1.0786</v>
@@ -959,7 +959,7 @@
         <v>3.5604</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.7837</v>
       </c>
       <c r="D12" t="n">
         <v>1.017</v>
@@ -1005,7 +1005,7 @@
         <v>3.2217</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.7091</v>
       </c>
       <c r="D13" t="n">
         <v>0.8801</v>
@@ -1051,7 +1051,7 @@
         <v>2.3451</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.5162</v>
       </c>
       <c r="D14" t="n">
         <v>0.526</v>
@@ -1097,7 +1097,7 @@
         <v>1.9095</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.4203</v>
       </c>
       <c r="D15" t="n">
         <v>0.35</v>
@@ -1143,7 +1143,7 @@
         <v>1.6281</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.3584</v>
       </c>
       <c r="D16" t="n">
         <v>0.2364</v>
@@ -1189,7 +1189,7 @@
         <v>1.628</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3583</v>
       </c>
       <c r="D17" t="n">
         <v>0.2363</v>
@@ -1235,7 +1235,7 @@
         <v>1.5909</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3502</v>
       </c>
       <c r="D18" t="n">
         <v>0.2213</v>
@@ -1281,7 +1281,7 @@
         <v>1.328</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.2923</v>
       </c>
       <c r="D19" t="n">
         <v>0.1151</v>
@@ -1327,7 +1327,7 @@
         <v>1.2665</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.2788</v>
       </c>
       <c r="D20" t="n">
         <v>0.09030000000000001</v>
@@ -1373,7 +1373,7 @@
         <v>1.1676</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="D21" t="n">
         <v>0.0503</v>
@@ -1419,7 +1419,7 @@
         <v>0.9159</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.2016</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0514</v>
@@ -1465,7 +1465,7 @@
         <v>0.9004</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="D23" t="n">
         <v>-0.0576</v>
@@ -1511,7 +1511,7 @@
         <v>0.6766</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1489</v>
       </c>
       <c r="D24" t="n">
         <v>-0.148</v>
@@ -1557,7 +1557,7 @@
         <v>0.4943</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2217</v>
@@ -1603,7 +1603,7 @@
         <v>0.1095</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0241</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3771</v>
@@ -1649,7 +1649,7 @@
         <v>0.0596</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0131</v>
       </c>
       <c r="D27" t="n">
         <v>-0.3973</v>
@@ -1695,7 +1695,7 @@
         <v>0.0314</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4087</v>
@@ -1741,7 +1741,7 @@
         <v>-0.0697</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0153</v>
       </c>
       <c r="D29" t="n">
         <v>-0.4495</v>
@@ -1787,7 +1787,7 @@
         <v>-0.278</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0612</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5337</v>
@@ -1833,7 +1833,7 @@
         <v>-0.5247000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1155</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6333</v>
@@ -1879,7 +1879,7 @@
         <v>-0.5871</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1292</v>
       </c>
       <c r="D32" t="n">
         <v>-0.6585</v>
@@ -1925,7 +1925,7 @@
         <v>-0.7092000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.1561</v>
       </c>
       <c r="D33" t="n">
         <v>-0.7079</v>
@@ -1971,7 +1971,7 @@
         <v>-0.7254</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1597</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7144</v>
@@ -2017,7 +2017,7 @@
         <v>-0.9346</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.2057</v>
       </c>
       <c r="D35" t="n">
         <v>-0.7989000000000001</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0152</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.2235</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8315</v>
@@ -2109,7 +2109,7 @@
         <v>-1.1356</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.25</v>
       </c>
       <c r="D37" t="n">
         <v>-0.8801</v>
@@ -2155,7 +2155,7 @@
         <v>-1.2686</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.2792</v>
       </c>
       <c r="D38" t="n">
         <v>-0.9338</v>
@@ -2201,7 +2201,7 @@
         <v>-1.6462</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.3624</v>
       </c>
       <c r="D39" t="n">
         <v>-1.0864</v>
@@ -2247,7 +2247,7 @@
         <v>-1.8892</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.4158</v>
       </c>
       <c r="D40" t="n">
         <v>-1.1846</v>
@@ -2293,7 +2293,7 @@
         <v>-2.7609</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.6077</v>
       </c>
       <c r="D41" t="n">
         <v>-1.5367</v>

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.5831</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4841</v>
+        <v>2.4215</v>
       </c>
       <c r="E2" t="n">
         <v>7.1922</v>
@@ -548,7 +548,7 @@
         <v>1.5296</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3859</v>
+        <v>2.3246</v>
       </c>
       <c r="E3" t="n">
         <v>6.9491</v>
@@ -594,7 +594,7 @@
         <v>1.2402</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8549</v>
+        <v>1.8009</v>
       </c>
       <c r="E4" t="n">
         <v>5.6345</v>
@@ -640,7 +640,7 @@
         <v>1.1258</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6447</v>
+        <v>1.5937</v>
       </c>
       <c r="E5" t="n">
         <v>5.1144</v>
@@ -686,7 +686,7 @@
         <v>1.0929</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5844</v>
+        <v>1.5341</v>
       </c>
       <c r="E6" t="n">
         <v>4.965</v>
@@ -732,7 +732,7 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3391</v>
+        <v>1.2923</v>
       </c>
       <c r="E7" t="n">
         <v>4.3579</v>
@@ -778,7 +778,7 @@
         <v>0.871</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1772</v>
+        <v>1.1326</v>
       </c>
       <c r="E8" t="n">
         <v>3.9571</v>
@@ -824,7 +824,7 @@
         <v>0.8247</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0923</v>
+        <v>1.0489</v>
       </c>
       <c r="E9" t="n">
         <v>3.7469</v>
@@ -870,7 +870,7 @@
         <v>0.8176</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0793</v>
+        <v>1.036</v>
       </c>
       <c r="E10" t="n">
         <v>3.7146</v>
@@ -916,7 +916,7 @@
         <v>0.8173</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0786</v>
+        <v>1.0353</v>
       </c>
       <c r="E11" t="n">
         <v>3.713</v>
@@ -962,7 +962,7 @@
         <v>0.7837</v>
       </c>
       <c r="D12" t="n">
-        <v>1.017</v>
+        <v>0.9746</v>
       </c>
       <c r="E12" t="n">
         <v>3.5604</v>
@@ -1008,7 +1008,7 @@
         <v>0.7091</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8801</v>
+        <v>0.8396</v>
       </c>
       <c r="E13" t="n">
         <v>3.2217</v>
@@ -1054,7 +1054,7 @@
         <v>0.5162</v>
       </c>
       <c r="D14" t="n">
-        <v>0.526</v>
+        <v>0.4904</v>
       </c>
       <c r="E14" t="n">
         <v>2.3451</v>
@@ -1100,7 +1100,7 @@
         <v>0.4203</v>
       </c>
       <c r="D15" t="n">
-        <v>0.35</v>
+        <v>0.3168</v>
       </c>
       <c r="E15" t="n">
         <v>1.9095</v>
@@ -1146,7 +1146,7 @@
         <v>0.3584</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2364</v>
+        <v>0.2047</v>
       </c>
       <c r="E16" t="n">
         <v>1.6281</v>
@@ -1192,7 +1192,7 @@
         <v>0.3583</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2363</v>
+        <v>0.2047</v>
       </c>
       <c r="E17" t="n">
         <v>1.628</v>
@@ -1238,7 +1238,7 @@
         <v>0.3502</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2213</v>
+        <v>0.1899</v>
       </c>
       <c r="E18" t="n">
         <v>1.5909</v>
@@ -1284,7 +1284,7 @@
         <v>0.2923</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1151</v>
+        <v>0.0852</v>
       </c>
       <c r="E19" t="n">
         <v>1.328</v>
@@ -1330,7 +1330,7 @@
         <v>0.2788</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0607</v>
       </c>
       <c r="E20" t="n">
         <v>1.2665</v>
@@ -1376,7 +1376,7 @@
         <v>0.257</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0503</v>
+        <v>0.0213</v>
       </c>
       <c r="E21" t="n">
         <v>1.1676</v>
@@ -1422,7 +1422,7 @@
         <v>0.2016</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0514</v>
+        <v>-0.079</v>
       </c>
       <c r="E22" t="n">
         <v>0.9159</v>
@@ -1468,7 +1468,7 @@
         <v>0.1982</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0576</v>
+        <v>-0.0852</v>
       </c>
       <c r="E23" t="n">
         <v>0.9004</v>
@@ -1514,7 +1514,7 @@
         <v>0.1489</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.148</v>
+        <v>-0.1744</v>
       </c>
       <c r="E24" t="n">
         <v>0.6766</v>
@@ -1560,7 +1560,7 @@
         <v>0.1088</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2217</v>
+        <v>-0.247</v>
       </c>
       <c r="E25" t="n">
         <v>0.4943</v>
@@ -1606,7 +1606,7 @@
         <v>0.0241</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3771</v>
+        <v>-0.4003</v>
       </c>
       <c r="E26" t="n">
         <v>0.1095</v>
@@ -1652,7 +1652,7 @@
         <v>0.0131</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3973</v>
+        <v>-0.4202</v>
       </c>
       <c r="E27" t="n">
         <v>0.0596</v>
@@ -1698,7 +1698,7 @@
         <v>0.0069</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4087</v>
+        <v>-0.4314</v>
       </c>
       <c r="E28" t="n">
         <v>0.0314</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0153</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4495</v>
+        <v>-0.4717</v>
       </c>
       <c r="E29" t="n">
         <v>-0.0697</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0612</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5337</v>
+        <v>-0.5547</v>
       </c>
       <c r="E30" t="n">
         <v>-0.278</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1155</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6333</v>
+        <v>-0.653</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5247000000000001</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1292</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6585</v>
+        <v>-0.6778</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5871</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1561</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7079</v>
+        <v>-0.7265</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7092000000000001</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1597</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7144</v>
+        <v>-0.7329</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7254</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2057</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.8163</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9346</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2235</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8315</v>
+        <v>-0.8484</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0152</v>
@@ -2112,7 +2112,7 @@
         <v>-0.25</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8801</v>
+        <v>-0.8963</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1356</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2792</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9338</v>
+        <v>-0.9493</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2686</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3624</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0864</v>
+        <v>-1.0998</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6462</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4158</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1846</v>
+        <v>-1.1966</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8892</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6077</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5367</v>
+        <v>-1.5439</v>
       </c>
       <c r="E41" t="n">
         <v>-2.7609</v>

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1922</v>
+        <v>7.0684</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5831</v>
+        <v>1.5559</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4215</v>
+        <v>2.553</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1922</v>
+        <v>7.0684</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4185</v>
+        <v>2.6486</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7737</v>
+        <v>4.4198</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4185</v>
+        <v>3.8455</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9603</v>
+        <v>1.9995</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7737</v>
+        <v>4.4198</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>6.734</v>
+        <v>6.419300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>239</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9491</v>
+        <v>6.2285</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5296</v>
+        <v>1.371</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3246</v>
+        <v>2.1738</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9491</v>
+        <v>6.2285</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7781</v>
+        <v>3.225</v>
       </c>
       <c r="G3" t="n">
-        <v>3.171</v>
+        <v>3.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7781</v>
+        <v>5.8765</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0623</v>
+        <v>3.0555</v>
       </c>
       <c r="J3" t="n">
-        <v>3.171</v>
+        <v>3.0035</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2333</v>
+        <v>6.058999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6345</v>
+        <v>5.7533</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2402</v>
+        <v>1.2664</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8009</v>
+        <v>1.9593</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6345</v>
+        <v>5.7533</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1097</v>
+        <v>2.5043</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5248</v>
+        <v>3.249</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1097</v>
+        <v>3.3372</v>
       </c>
       <c r="I4" t="n">
-        <v>1.71</v>
+        <v>1.7352</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5248</v>
+        <v>3.249</v>
       </c>
       <c r="K4" t="n">
         <v>103</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2348</v>
+        <v>4.9842</v>
       </c>
       <c r="N4" t="n">
         <v>239</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1144</v>
+        <v>5.455</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1258</v>
+        <v>1.2007</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5937</v>
+        <v>1.8246</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1144</v>
+        <v>5.455</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3995</v>
+        <v>3.136</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7149</v>
+        <v>2.319</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3995</v>
+        <v>5.563</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7554</v>
+        <v>2.8925</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7149</v>
+        <v>2.319</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4703</v>
+        <v>5.2115</v>
       </c>
       <c r="N5" t="n">
         <v>276</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.965</v>
+        <v>5.0247</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0929</v>
+        <v>1.106</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5341</v>
+        <v>1.6304</v>
       </c>
       <c r="E6" t="n">
-        <v>4.965</v>
+        <v>5.0247</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1878</v>
+        <v>3.2196</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7772</v>
+        <v>1.8051</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1878</v>
+        <v>5.8576</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5838</v>
+        <v>3.0457</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7772</v>
+        <v>1.8051</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.361</v>
+        <v>4.8508</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3579</v>
+        <v>4.3548</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9586</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2923</v>
+        <v>1.328</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3579</v>
+        <v>4.3548</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4536</v>
+        <v>4.2229</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1319</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3574</v>
+        <v>9.3926</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3423</v>
+        <v>4.8837</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1319</v>
       </c>
       <c r="K7" t="n">
         <v>219</v>
@@ -759,7 +759,7 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2466</v>
+        <v>5.0156</v>
       </c>
       <c r="N7" t="n">
         <v>280</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9571</v>
+        <v>3.8503</v>
       </c>
       <c r="C8" t="n">
-        <v>0.871</v>
+        <v>0.8475</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1326</v>
+        <v>1.1002</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9571</v>
+        <v>3.8503</v>
       </c>
       <c r="F8" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9092</v>
+        <v>-0.6015</v>
       </c>
       <c r="H8" t="n">
-        <v>7.5914</v>
+        <v>13.6829</v>
       </c>
       <c r="I8" t="n">
-        <v>6.1531</v>
+        <v>7.1145</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9092</v>
+        <v>-0.6015</v>
       </c>
       <c r="K8" t="n">
         <v>238</v>
@@ -805,7 +805,7 @@
         <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2439</v>
+        <v>6.513</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -814,44 +814,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7469</v>
+        <v>3.7372</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8247</v>
+        <v>0.8226</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0489</v>
+        <v>1.0491</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7469</v>
+        <v>3.7372</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1793</v>
+        <v>4.4518</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4324</v>
+        <v>-0.7146</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2536</v>
+        <v>10.862</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4476</v>
+        <v>5.6478</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4324</v>
+        <v>-0.7146</v>
       </c>
       <c r="K9" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0152</v>
+        <v>4.9332</v>
       </c>
       <c r="N9" t="n">
         <v>280</v>
@@ -860,127 +860,127 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7146</v>
+        <v>3.6393</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8176</v>
+        <v>0.8011</v>
       </c>
       <c r="D10" t="n">
-        <v>1.036</v>
+        <v>1.0049</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7146</v>
+        <v>3.6393</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7146</v>
+        <v>3.16</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0.4793</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4074</v>
+        <v>5.6474</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1934</v>
+        <v>2.9364</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>0.4793</v>
       </c>
       <c r="K10" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1934</v>
+        <v>3.4157</v>
       </c>
       <c r="N10" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.713</v>
+        <v>3.5446</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8173</v>
+        <v>0.7802</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0353</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.713</v>
+        <v>3.5446</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3744</v>
+        <v>3.7139</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3386</v>
+        <v>-0.1693</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3744</v>
+        <v>7.599</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7351</v>
+        <v>3.9511</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3386</v>
+        <v>-0.1693</v>
       </c>
       <c r="K11" t="n">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="L11" t="n">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0737</v>
+        <v>3.7818</v>
       </c>
       <c r="N11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5604</v>
+        <v>3.5391</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7837</v>
+        <v>0.779</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9746</v>
+        <v>0.9597</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5604</v>
+        <v>3.5391</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2854</v>
+        <v>3.0373</v>
       </c>
       <c r="G12" t="n">
-        <v>0.275</v>
+        <v>0.5018</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2854</v>
+        <v>5.2152</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6629</v>
+        <v>2.7116</v>
       </c>
       <c r="J12" t="n">
-        <v>0.275</v>
+        <v>0.5018</v>
       </c>
       <c r="K12" t="n">
         <v>219</v>
@@ -989,7 +989,7 @@
         <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9379</v>
+        <v>3.2134</v>
       </c>
       <c r="N12" t="n">
         <v>280</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2217</v>
+        <v>3.4614</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7091</v>
+        <v>0.7619</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8396</v>
+        <v>0.9246</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2217</v>
+        <v>3.4614</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7233</v>
+        <v>3.2438</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4984</v>
+        <v>0.2176</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7233</v>
+        <v>5.9427</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2073</v>
+        <v>3.09</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4984</v>
+        <v>0.2176</v>
       </c>
       <c r="K13" t="n">
         <v>219</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7057</v>
+        <v>3.3076</v>
       </c>
       <c r="N13" t="n">
         <v>280</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3451</v>
+        <v>3.0241</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5162</v>
+        <v>0.6656</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4904</v>
+        <v>0.7272</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3451</v>
+        <v>3.0241</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7517</v>
+        <v>1.4647</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5934</v>
+        <v>1.5594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7517</v>
+        <v>1.4647</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6093</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5934</v>
+        <v>1.5594</v>
       </c>
       <c r="K14" t="n">
         <v>121</v>
@@ -1081,7 +1081,7 @@
         <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2027</v>
+        <v>2.321</v>
       </c>
       <c r="N14" t="n">
         <v>276</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9095</v>
+        <v>2.9442</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4203</v>
+        <v>0.6481</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3168</v>
+        <v>0.6911</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9095</v>
+        <v>2.9442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1444</v>
+        <v>2.537</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7651</v>
+        <v>0.4072</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1444</v>
+        <v>3.4525</v>
       </c>
       <c r="I15" t="n">
-        <v>0.117</v>
+        <v>1.7951</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7651</v>
+        <v>0.4072</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>238</v>
       </c>
       <c r="L15" t="n">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8821</v>
+        <v>2.2023</v>
       </c>
       <c r="N15" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flayy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6281</v>
+        <v>2.8278</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3584</v>
+        <v>0.6224</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2047</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6281</v>
+        <v>2.8278</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7024</v>
+        <v>2.8278</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3305</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7024</v>
+        <v>2.8496</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5693</v>
+        <v>2.8496</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3305</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="L16" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7612</v>
+        <v>2.8496</v>
       </c>
       <c r="N16" t="n">
-        <v>239</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flayy</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3583</v>
+        <v>0.5407</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2047</v>
+        <v>0.4709</v>
       </c>
       <c r="E17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="F17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="I17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.628</v>
+        <v>2.4563</v>
       </c>
       <c r="N17" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5909</v>
+        <v>2.452</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3502</v>
+        <v>0.5397</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1899</v>
+        <v>0.4689</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5909</v>
+        <v>2.452</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1574</v>
+        <v>0.4537</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4335</v>
+        <v>1.9983</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1574</v>
+        <v>0.4537</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9381</v>
+        <v>0.2359</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4335</v>
+        <v>1.9983</v>
       </c>
       <c r="K18" t="n">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3716</v>
+        <v>2.2342</v>
       </c>
       <c r="N18" t="n">
-        <v>280</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>adamb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2923</v>
+        <v>0.4208</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0852</v>
+        <v>0.225</v>
       </c>
       <c r="E19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="F19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="I19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.328</v>
+        <v>1.9117</v>
       </c>
       <c r="N19" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2665</v>
+        <v>1.7228</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2788</v>
+        <v>0.3792</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0607</v>
+        <v>0.1397</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2665</v>
+        <v>1.7228</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4833</v>
+        <v>2.868</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2168</v>
+        <v>-1.1452</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4833</v>
+        <v>4.6189</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0128</v>
+        <v>2.4016</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2168</v>
+        <v>-1.1452</v>
       </c>
       <c r="K20" t="n">
         <v>121</v>
@@ -1357,7 +1357,7 @@
         <v>155</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7959999999999998</v>
+        <v>1.2564</v>
       </c>
       <c r="N20" t="n">
         <v>276</v>
@@ -1366,170 +1366,170 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>spooke</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1676</v>
+        <v>1.6876</v>
       </c>
       <c r="C21" t="n">
-        <v>0.257</v>
+        <v>0.3715</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0213</v>
+        <v>0.1239</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1676</v>
+        <v>1.6876</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1676</v>
+        <v>-0.7624</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1676</v>
+        <v>-0.7624</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1676</v>
+        <v>-0.3964</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="K21" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1676</v>
+        <v>2.0536</v>
       </c>
       <c r="N21" t="n">
-        <v>121</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>spooke</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2016</v>
+        <v>0.3351</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.079</v>
+        <v>0.0493</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9159</v>
+        <v>1.5225</v>
       </c>
       <c r="N22" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>adamb</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1982</v>
+        <v>0.308</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0852</v>
+        <v>-0.0063</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9004</v>
+        <v>1.3994</v>
       </c>
       <c r="N23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1489</v>
+        <v>0.2821</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1744</v>
+        <v>-0.0595</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6766</v>
+        <v>1.2814</v>
       </c>
       <c r="N24" t="n">
         <v>154</v>
@@ -1550,231 +1550,231 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4943</v>
+        <v>0.7881</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1088</v>
+        <v>0.1735</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.247</v>
+        <v>-0.2822</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4943</v>
+        <v>0.7881</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4943</v>
+        <v>0.6183</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1698</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4943</v>
+        <v>0.6183</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4943</v>
+        <v>0.3215</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1698</v>
       </c>
       <c r="K25" t="n">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4943</v>
+        <v>0.4913</v>
       </c>
       <c r="N25" t="n">
-        <v>154</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>hfah</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0241</v>
+        <v>0.1117</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4003</v>
+        <v>-0.4089</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1095</v>
+        <v>0.5075</v>
       </c>
       <c r="N26" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Qlocuu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0596</v>
+        <v>0.5049</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0131</v>
+        <v>0.1111</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4202</v>
+        <v>-0.4101</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0596</v>
+        <v>0.5049</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0572</v>
+        <v>0.5049</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1168</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0572</v>
+        <v>0.5049</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0464</v>
+        <v>0.5049</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1168</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0704</v>
+        <v>0.5049</v>
       </c>
       <c r="N27" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hfah</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0069</v>
+        <v>0.1056</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4314</v>
+        <v>-0.4214</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0314</v>
+        <v>0.4799</v>
       </c>
       <c r="N28" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Qlocuu</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0153</v>
+        <v>0.0806</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4717</v>
+        <v>-0.4727</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0697</v>
+        <v>0.3661</v>
       </c>
       <c r="N29" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0612</v>
+        <v>0.0401</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5547</v>
+        <v>-0.5558</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.278</v>
+        <v>0.1821</v>
       </c>
       <c r="N30" t="n">
         <v>122</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1155</v>
+        <v>0.0105</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.653</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5871</v>
+        <v>-0.2222</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1292</v>
+        <v>-0.0489</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6778</v>
+        <v>-0.7383</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5871</v>
+        <v>-0.2222</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5871</v>
+        <v>0.5869</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.8091</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5871</v>
+        <v>0.5869</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5871</v>
+        <v>0.3052</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.8091</v>
       </c>
       <c r="K32" t="n">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5871</v>
+        <v>-0.5039</v>
       </c>
       <c r="N32" t="n">
-        <v>122</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>Sobol</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1561</v>
+        <v>-0.0511</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7265</v>
+        <v>-0.7428</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2322</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1597</v>
+        <v>-0.0578</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7329</v>
+        <v>-0.7567</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7254</v>
+        <v>-0.2628</v>
       </c>
       <c r="N34" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2057</v>
+        <v>-0.0687</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8163</v>
+        <v>-0.7788</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9346</v>
+        <v>-0.3119</v>
       </c>
       <c r="N35" t="n">
         <v>154</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2235</v>
+        <v>-0.0707</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8484</v>
+        <v>-0.783</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0152</v>
+        <v>-0.3212</v>
       </c>
       <c r="N36" t="n">
         <v>121</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sobol</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.25</v>
+        <v>-0.0839</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8963</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1356</v>
+        <v>-0.381</v>
       </c>
       <c r="N37" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2686</v>
+        <v>-0.532</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2792</v>
+        <v>-0.1171</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9493</v>
+        <v>-0.8782</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2686</v>
+        <v>-0.532</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2686</v>
+        <v>-0.532</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2686</v>
+        <v>-0.532</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2177</v>
+        <v>-0.532</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L38" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2177</v>
+        <v>-0.532</v>
       </c>
       <c r="N38" t="n">
-        <v>280</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3624</v>
+        <v>-0.2188</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0998</v>
+        <v>-1.0867</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6462</v>
+        <v>-0.9939</v>
       </c>
       <c r="N39" t="n">
         <v>156</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8892</v>
+        <v>-1.7414</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4158</v>
+        <v>-0.3833</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1966</v>
+        <v>-1.4242</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8892</v>
+        <v>-1.7414</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9158</v>
+        <v>-1.8453</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0266</v>
+        <v>0.1039</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9158</v>
+        <v>-1.8453</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5528</v>
+        <v>-0.9594</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0266</v>
+        <v>0.1039</v>
       </c>
       <c r="K40" t="n">
         <v>219</v>
@@ -2277,7 +2277,7 @@
         <v>61</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5262</v>
+        <v>-0.8555</v>
       </c>
       <c r="N40" t="n">
         <v>280</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6077</v>
+        <v>-0.4647</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5439</v>
+        <v>-1.5911</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.7609</v>
+        <v>-2.1111</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3946</v>
+        <v>0.3376</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4974</v>
+        <v>6.4144</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2111</v>
+        <v>0.1529</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0109</v>
+        <v>2.9051</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1808</v>
+        <v>-0.1469</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.4352</v>
+        <v>-2.7911</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4746</v>
+        <v>-0.3125</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.0174</v>
+        <v>-5.9375</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9804</v>
+        <v>-0.6896</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.6276</v>
+        <v>-13.1024</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2479</v>
+        <v>1.1008</v>
       </c>
       <c r="J7" t="n">
-        <v>23.7101</v>
+        <v>20.9152</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7113</v>
       </c>
       <c r="J8" t="n">
-        <v>14.7763</v>
+        <v>13.5147</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4728</v>
+        <v>0.4661</v>
       </c>
       <c r="J9" t="n">
-        <v>8.9832</v>
+        <v>8.8559</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1506</v>
+        <v>0.1819</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8614</v>
+        <v>3.4561</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3339</v>
+        <v>-0.1959</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.3441</v>
+        <v>-3.7221</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5674</v>
       </c>
       <c r="J12" t="n">
-        <v>13.4728</v>
+        <v>12.4828</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2651</v>
+        <v>0.2213</v>
       </c>
       <c r="J13" t="n">
-        <v>5.8322</v>
+        <v>4.8686</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1706</v>
+        <v>-0.099</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.7532</v>
+        <v>-2.178</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3519</v>
+        <v>-0.2177</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.7418</v>
+        <v>-4.7894</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5053</v>
+        <v>-0.3256</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.1166</v>
+        <v>-7.1632</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4514</v>
+        <v>0.3821</v>
       </c>
       <c r="J17" t="n">
-        <v>9.9308</v>
+        <v>8.4062</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3381</v>
+        <v>0.2824</v>
       </c>
       <c r="J18" t="n">
-        <v>7.4382</v>
+        <v>6.2128</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2078</v>
+        <v>0.177</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5716</v>
+        <v>3.894</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0619</v>
+        <v>0.0738</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3618</v>
+        <v>1.6236</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.359</v>
+        <v>-0.2184</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.898</v>
+        <v>-4.8048</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1737</v>
+        <v>1.106</v>
       </c>
       <c r="J22" t="n">
-        <v>24.6477</v>
+        <v>23.226</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.758</v>
+        <v>0.7426</v>
       </c>
       <c r="J23" t="n">
-        <v>15.918</v>
+        <v>15.5946</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4981</v>
       </c>
       <c r="J24" t="n">
-        <v>10.5315</v>
+        <v>10.4601</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3683</v>
+        <v>-0.2974</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.7343</v>
+        <v>-6.2454</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.85</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5893</v>
+        <v>-0.5269</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3753</v>
+        <v>-11.0649</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.652</v>
+        <v>0.7967</v>
       </c>
       <c r="J27" t="n">
-        <v>13.692</v>
+        <v>16.7307</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2708</v>
+        <v>0.3015</v>
       </c>
       <c r="J28" t="n">
-        <v>5.6868</v>
+        <v>6.3315</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1269</v>
+        <v>0.1359</v>
       </c>
       <c r="J29" t="n">
-        <v>2.6649</v>
+        <v>2.8539</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3289</v>
+        <v>-0.2004</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.9069</v>
+        <v>-4.2084</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5745</v>
+        <v>-0.3758</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.0645</v>
+        <v>-7.8918</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2168</v>
+        <v>1.1421</v>
       </c>
       <c r="J32" t="n">
-        <v>21.9024</v>
+        <v>20.5578</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9227</v>
+        <v>0.9353</v>
       </c>
       <c r="J33" t="n">
-        <v>16.6086</v>
+        <v>16.8354</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5344</v>
+        <v>0.5995</v>
       </c>
       <c r="J34" t="n">
-        <v>9.619199999999999</v>
+        <v>10.791</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4815</v>
+        <v>0.5515</v>
       </c>
       <c r="J35" t="n">
-        <v>8.667</v>
+        <v>9.927</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3121</v>
+        <v>-0.2298</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.6178</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5072</v>
+        <v>0.5951</v>
       </c>
       <c r="J37" t="n">
-        <v>9.1296</v>
+        <v>10.7118</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1404</v>
+        <v>0.1203</v>
       </c>
       <c r="J38" t="n">
-        <v>2.5272</v>
+        <v>2.1654</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1274</v>
+        <v>-0.1013</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.2932</v>
+        <v>-1.8234</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5099</v>
+        <v>-0.3321</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.1782</v>
+        <v>-5.9778</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7013</v>
+        <v>-0.4717</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.6234</v>
+        <v>-8.490600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.26</v>
       </c>
       <c r="I42" t="n">
-        <v>2.179</v>
+        <v>1.8681</v>
       </c>
       <c r="J42" t="n">
-        <v>30.506</v>
+        <v>26.1534</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.53</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0607</v>
+        <v>1.1214</v>
       </c>
       <c r="J43" t="n">
-        <v>14.8498</v>
+        <v>15.6996</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.835</v>
+        <v>0.9742</v>
       </c>
       <c r="J44" t="n">
-        <v>11.69</v>
+        <v>13.6388</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7732</v>
+        <v>0.9163</v>
       </c>
       <c r="J45" t="n">
-        <v>10.8248</v>
+        <v>12.8282</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7318</v>
+        <v>0.8737</v>
       </c>
       <c r="J46" t="n">
-        <v>10.2452</v>
+        <v>12.2318</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9388</v>
+        <v>1.1766</v>
       </c>
       <c r="J47" t="n">
-        <v>13.1432</v>
+        <v>16.4724</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.4721</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.702</v>
+        <v>-6.6094</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.48</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7202</v>
+        <v>-0.4909</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.0828</v>
+        <v>-6.8726</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8244</v>
+        <v>-0.5666</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.5416</v>
+        <v>-7.9324</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9474</v>
+        <v>-0.6615</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.2636</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6022</v>
+        <v>0.5224</v>
       </c>
       <c r="J52" t="n">
-        <v>18.066</v>
+        <v>15.672</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3785</v>
+        <v>0.3186</v>
       </c>
       <c r="J53" t="n">
-        <v>11.355</v>
+        <v>9.558</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1576</v>
+        <v>0.1489</v>
       </c>
       <c r="J54" t="n">
-        <v>4.728</v>
+        <v>4.467</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0796</v>
+        <v>-0.0297</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.388</v>
+        <v>-0.891</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4035</v>
+        <v>-0.2498</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.105</v>
+        <v>-7.494</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5743</v>
+        <v>0.5276</v>
       </c>
       <c r="J57" t="n">
-        <v>17.229</v>
+        <v>15.828</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.523</v>
+        <v>0.4746</v>
       </c>
       <c r="J58" t="n">
-        <v>15.69</v>
+        <v>14.238</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1899</v>
+        <v>-0.1108</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.697</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.72</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4924</v>
+        <v>-0.3163</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.772</v>
+        <v>-9.489000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5447</v>
+        <v>-0.3542</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.341</v>
+        <v>-10.626</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6359</v>
+        <v>0.7751</v>
       </c>
       <c r="J62" t="n">
-        <v>14.6257</v>
+        <v>17.8273</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1049</v>
+        <v>-0.0529</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.4127</v>
+        <v>-1.2167</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1465</v>
+        <v>-0.0789</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.3695</v>
+        <v>-1.8147</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2024</v>
+        <v>-0.1149</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.6552</v>
+        <v>-2.6427</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2198</v>
+        <v>-0.1263</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.0554</v>
+        <v>-2.9049</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.07</v>
       </c>
       <c r="I67" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J67" t="n">
-        <v>47.3639</v>
+        <v>42.1774</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.715</v>
+        <v>0.7091</v>
       </c>
       <c r="J68" t="n">
-        <v>16.445</v>
+        <v>16.3093</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1109</v>
+        <v>-0.0405</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.5507</v>
+        <v>-0.9315</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.84</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6242</v>
+        <v>-0.5621</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.3566</v>
+        <v>-12.9283</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0132</v>
+        <v>-0.9897</v>
       </c>
       <c r="J71" t="n">
-        <v>-23.3036</v>
+        <v>-22.7631</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8665</v>
+        <v>1.058</v>
       </c>
       <c r="J72" t="n">
-        <v>25.995</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0509</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>1.527</v>
+        <v>2.508</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2114</v>
+        <v>-0.1184</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.342</v>
+        <v>-3.552</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2453</v>
+        <v>-0.1411</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.359</v>
+        <v>-4.233</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.324</v>
+        <v>-0.1949</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.720000000000001</v>
+        <v>-5.847</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7023</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>21.069</v>
+        <v>20.097</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5495</v>
+        <v>0.5174</v>
       </c>
       <c r="J78" t="n">
-        <v>16.485</v>
+        <v>15.522</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3164</v>
+        <v>0.3012</v>
       </c>
       <c r="J79" t="n">
-        <v>9.492000000000001</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2038</v>
+        <v>-0.1468</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.114</v>
+        <v>-4.404</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5121</v>
+        <v>-0.4528</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.363</v>
+        <v>-13.584</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.85</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8003</v>
+        <v>1.2976</v>
       </c>
       <c r="J82" t="n">
-        <v>39.6066</v>
+        <v>28.5472</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0093</v>
+        <v>0.7356</v>
       </c>
       <c r="J83" t="n">
-        <v>22.2046</v>
+        <v>16.1832</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.186</v>
+        <v>-0.1066</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.092</v>
+        <v>-2.3452</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.265</v>
+        <v>-0.185</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.83</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.611</v>
+        <v>-0.5461</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.442</v>
+        <v>-12.0142</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2426</v>
+        <v>0.2447</v>
       </c>
       <c r="J87" t="n">
-        <v>5.3372</v>
+        <v>5.3834</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0299</v>
+        <v>-0.0055</v>
       </c>
       <c r="J88" t="n">
-        <v>0.6578000000000001</v>
+        <v>-0.121</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2616</v>
+        <v>-0.1733</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.7552</v>
+        <v>-3.8126</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4066</v>
+        <v>-0.2627</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.9452</v>
+        <v>-5.7794</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5194</v>
+        <v>-0.3395</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.4268</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5987</v>
+        <v>0.4629</v>
       </c>
       <c r="J92" t="n">
-        <v>9.5792</v>
+        <v>7.4064</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.06</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2002</v>
+        <v>0.148</v>
       </c>
       <c r="J93" t="n">
-        <v>3.2032</v>
+        <v>2.368</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.88</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2141</v>
+        <v>-0.1442</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.4256</v>
+        <v>-2.3072</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2871</v>
+        <v>-0.1852</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.5936</v>
+        <v>-2.9632</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.6601</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.088</v>
+        <v>-10.5616</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.67</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8605</v>
+        <v>0.5975</v>
       </c>
       <c r="J97" t="n">
-        <v>13.768</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3889</v>
+        <v>0.3595</v>
       </c>
       <c r="J98" t="n">
-        <v>6.2224</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3889</v>
+        <v>0.3595</v>
       </c>
       <c r="J99" t="n">
-        <v>6.2224</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2881</v>
+        <v>0.2957</v>
       </c>
       <c r="J100" t="n">
-        <v>4.6096</v>
+        <v>4.7312</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="J101" t="n">
-        <v>1.2368</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.41</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0544</v>
+        <v>0.7587</v>
       </c>
       <c r="J102" t="n">
-        <v>24.2512</v>
+        <v>17.4501</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9467</v>
+        <v>0.6921</v>
       </c>
       <c r="J103" t="n">
-        <v>21.7741</v>
+        <v>15.9183</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.08</v>
       </c>
       <c r="I104" t="n">
-        <v>0.194</v>
+        <v>0.2529</v>
       </c>
       <c r="J104" t="n">
-        <v>4.462</v>
+        <v>5.8167</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.8847</v>
+        <v>-2.1827</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.8847</v>
+        <v>-2.1827</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3464</v>
+        <v>0.3614</v>
       </c>
       <c r="J107" t="n">
-        <v>7.9672</v>
+        <v>8.312200000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1331</v>
+        <v>-0.1024</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.0613</v>
+        <v>-2.3552</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2914</v>
+        <v>-0.1863</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.7022</v>
+        <v>-4.2849</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3239</v>
+        <v>-0.2066</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.4497</v>
+        <v>-4.7518</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.5381</v>
+        <v>-6.1203</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9661</v>
+        <v>0.7094</v>
       </c>
       <c r="J112" t="n">
-        <v>23.1864</v>
+        <v>17.0256</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8546</v>
+        <v>0.6431</v>
       </c>
       <c r="J113" t="n">
-        <v>20.5104</v>
+        <v>15.4344</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8316</v>
+        <v>0.6297</v>
       </c>
       <c r="J114" t="n">
-        <v>19.9584</v>
+        <v>15.1128</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3431</v>
+        <v>0.3779</v>
       </c>
       <c r="J115" t="n">
-        <v>8.234400000000001</v>
+        <v>9.069599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.89</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5069</v>
+        <v>-0.4352</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.1656</v>
+        <v>-10.4448</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3245</v>
+        <v>0.3409</v>
       </c>
       <c r="J117" t="n">
-        <v>7.788</v>
+        <v>8.1816</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0805</v>
+        <v>0.0428</v>
       </c>
       <c r="J118" t="n">
-        <v>1.932</v>
+        <v>1.0272</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4231</v>
+        <v>-0.277</v>
       </c>
       <c r="J119" t="n">
-        <v>-10.1544</v>
+        <v>-6.648</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4525</v>
+        <v>-0.2962</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.86</v>
+        <v>-7.1088</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6287</v>
+        <v>-0.4188</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.0888</v>
+        <v>-10.0512</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6674</v>
+        <v>1.171</v>
       </c>
       <c r="J122" t="n">
-        <v>30.0132</v>
+        <v>21.078</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2405</v>
+        <v>0.9008</v>
       </c>
       <c r="J123" t="n">
-        <v>22.329</v>
+        <v>16.2144</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8052</v>
+        <v>0.6717</v>
       </c>
       <c r="J124" t="n">
-        <v>14.4936</v>
+        <v>12.0906</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.28</v>
       </c>
       <c r="I125" t="n">
-        <v>0.599</v>
+        <v>0.5544</v>
       </c>
       <c r="J125" t="n">
-        <v>10.782</v>
+        <v>9.979200000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.06</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0463</v>
+        <v>0.1352</v>
       </c>
       <c r="J126" t="n">
-        <v>0.8334</v>
+        <v>2.4336</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.353</v>
+        <v>0.3644</v>
       </c>
       <c r="J127" t="n">
-        <v>6.354</v>
+        <v>6.5592</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.84</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2077</v>
+        <v>-0.1711</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.7386</v>
+        <v>-3.0798</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4861</v>
+        <v>-0.3245</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.7498</v>
+        <v>-5.841</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5849</v>
+        <v>-0.3903</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.5282</v>
+        <v>-7.0254</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6251</v>
+        <v>-0.4184</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.2518</v>
+        <v>-7.5312</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.2</v>
       </c>
       <c r="I132" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J132" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>2.08</v>
       </c>
       <c r="I133" t="n">
-        <v>2.0208</v>
+        <v>1.7352</v>
       </c>
       <c r="J133" t="n">
-        <v>30.312</v>
+        <v>26.028</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9253</v>
+        <v>1.039</v>
       </c>
       <c r="J134" t="n">
-        <v>13.8795</v>
+        <v>15.585</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6331</v>
+        <v>0.7673</v>
       </c>
       <c r="J135" t="n">
-        <v>9.496499999999999</v>
+        <v>11.5095</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7952</v>
+        <v>-0.7461</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.928</v>
+        <v>-11.1915</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.91</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0361</v>
+        <v>-0.0618</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.5415</v>
+        <v>-0.927</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.89</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0707</v>
+        <v>-0.0867</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.0605</v>
+        <v>-1.3005</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.645</v>
+        <v>-0.4381</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.675000000000001</v>
+        <v>-6.5715</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7131</v>
+        <v>-0.4851</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.6965</v>
+        <v>-7.2765</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7526</v>
+        <v>-0.5133</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.289</v>
+        <v>-7.6995</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7347</v>
+        <v>0.7039</v>
       </c>
       <c r="J142" t="n">
-        <v>12.4899</v>
+        <v>11.9663</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0113</v>
+        <v>-0.0336</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.1921</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2703</v>
+        <v>-0.1818</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.5951</v>
+        <v>-3.0906</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5556</v>
+        <v>-0.3657</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.4452</v>
+        <v>-6.2169</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.39</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8727</v>
+        <v>-0.6039</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.8359</v>
+        <v>-10.2663</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9062</v>
       </c>
       <c r="J147" t="n">
-        <v>16.7518</v>
+        <v>15.4054</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.72</v>
       </c>
       <c r="I148" t="n">
-        <v>0.893</v>
+        <v>0.8169</v>
       </c>
       <c r="J148" t="n">
-        <v>15.181</v>
+        <v>13.8873</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2824</v>
+        <v>0.2993</v>
       </c>
       <c r="J149" t="n">
-        <v>4.8008</v>
+        <v>5.0881</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2688</v>
+        <v>0.2872</v>
       </c>
       <c r="J150" t="n">
-        <v>4.5696</v>
+        <v>4.8824</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1803</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.0651</v>
+        <v>-1.4773</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>1.8263</v>
+        <v>1.5501</v>
       </c>
       <c r="J152" t="n">
-        <v>34.6997</v>
+        <v>29.4519</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.7</v>
       </c>
       <c r="I153" t="n">
-        <v>1.4898</v>
+        <v>1.3325</v>
       </c>
       <c r="J153" t="n">
-        <v>28.3062</v>
+        <v>25.3175</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.3</v>
       </c>
       <c r="I154" t="n">
-        <v>0.628</v>
+        <v>0.7453</v>
       </c>
       <c r="J154" t="n">
-        <v>11.932</v>
+        <v>14.1607</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5607</v>
+        <v>0.6764</v>
       </c>
       <c r="J155" t="n">
-        <v>10.6533</v>
+        <v>12.8516</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.11</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1758</v>
+        <v>0.2734</v>
       </c>
       <c r="J156" t="n">
-        <v>3.3402</v>
+        <v>5.1946</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.83</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.194</v>
+        <v>-0.1695</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.686</v>
+        <v>-3.2205</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.82</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2102</v>
+        <v>-0.1803</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.9938</v>
+        <v>-3.4257</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4733</v>
+        <v>-0.3251</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.992699999999999</v>
+        <v>-6.1769</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5048</v>
+        <v>-0.3436</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.591200000000001</v>
+        <v>-6.5284</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6341</v>
+        <v>-0.4276</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.0479</v>
+        <v>-8.1244</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9378</v>
+        <v>0.9428</v>
       </c>
       <c r="J162" t="n">
-        <v>18.756</v>
+        <v>18.856</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.36</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9157</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>18.314</v>
+        <v>18.438</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.25</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6523</v>
+        <v>0.6725</v>
       </c>
       <c r="J164" t="n">
-        <v>13.046</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5288</v>
+        <v>0.5806</v>
       </c>
       <c r="J165" t="n">
-        <v>10.576</v>
+        <v>11.612</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3976</v>
+        <v>-0.3199</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.952</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.19</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4074</v>
+        <v>0.4604</v>
       </c>
       <c r="J167" t="n">
-        <v>8.148</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0279</v>
+        <v>-0.0397</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.794</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1718</v>
+        <v>-0.124</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.436</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.74</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4422</v>
+        <v>-0.285</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.843999999999999</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5381</v>
+        <v>-0.3519</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.762</v>
+        <v>-7.038</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4585</v>
+        <v>1.2937</v>
       </c>
       <c r="J172" t="n">
-        <v>35.004</v>
+        <v>31.0488</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.621</v>
+        <v>0.6026</v>
       </c>
       <c r="J173" t="n">
-        <v>14.904</v>
+        <v>14.4624</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4283</v>
+        <v>0.4254</v>
       </c>
       <c r="J174" t="n">
-        <v>10.2792</v>
+        <v>10.2096</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5836</v>
+        <v>-0.5221</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.0064</v>
+        <v>-12.5304</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.732</v>
+        <v>-0.6804</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.568</v>
+        <v>-16.3296</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3098</v>
+        <v>0.3455</v>
       </c>
       <c r="J177" t="n">
-        <v>7.4352</v>
+        <v>8.292</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0418</v>
+        <v>0.038</v>
       </c>
       <c r="J178" t="n">
-        <v>1.0032</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0029</v>
+        <v>0.0001</v>
       </c>
       <c r="J179" t="n">
-        <v>0.0696</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1136</v>
+        <v>-0.063</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.7264</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.277</v>
+        <v>-0.1666</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.648</v>
+        <v>-3.9984</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2924</v>
+        <v>0.3042</v>
       </c>
       <c r="J182" t="n">
-        <v>5.5556</v>
+        <v>5.7798</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.79</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3177</v>
+        <v>-0.2242</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.0363</v>
+        <v>-4.2598</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3177</v>
+        <v>-0.2242</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.0363</v>
+        <v>-4.2598</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4667</v>
+        <v>-0.3094</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.8673</v>
+        <v>-5.8786</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6188</v>
+        <v>-0.4129</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.7572</v>
+        <v>-7.8451</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3335</v>
+        <v>1.2234</v>
       </c>
       <c r="J187" t="n">
-        <v>25.3365</v>
+        <v>23.2446</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.51</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1755</v>
+        <v>1.1257</v>
       </c>
       <c r="J188" t="n">
-        <v>22.3345</v>
+        <v>21.3883</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7927</v>
+        <v>0.8539</v>
       </c>
       <c r="J189" t="n">
-        <v>15.0613</v>
+        <v>16.2241</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4641</v>
+        <v>0.5579</v>
       </c>
       <c r="J190" t="n">
-        <v>8.8179</v>
+        <v>10.6001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.04</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0031</v>
+        <v>0.0864</v>
       </c>
       <c r="J191" t="n">
-        <v>0.0589</v>
+        <v>1.6416</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9998</v>
+        <v>0.9193</v>
       </c>
       <c r="J192" t="n">
-        <v>17.9964</v>
+        <v>16.5474</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7238</v>
+        <v>0.6573</v>
       </c>
       <c r="J193" t="n">
-        <v>13.0284</v>
+        <v>11.8314</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.37</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4809</v>
+        <v>0.4591</v>
       </c>
       <c r="J194" t="n">
-        <v>8.6562</v>
+        <v>8.2638</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0327</v>
+        <v>0.0723</v>
       </c>
       <c r="J195" t="n">
-        <v>0.5886</v>
+        <v>1.3014</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0149</v>
+        <v>0.0563</v>
       </c>
       <c r="J196" t="n">
-        <v>0.2682</v>
+        <v>1.0134</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5935</v>
+        <v>0.5488</v>
       </c>
       <c r="J197" t="n">
-        <v>10.683</v>
+        <v>9.878399999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1564</v>
+        <v>-0.1283</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.8152</v>
+        <v>-2.3094</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3296</v>
+        <v>-0.2191</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.9328</v>
+        <v>-3.9438</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3936</v>
+        <v>-0.258</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.0848</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.42</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8358</v>
+        <v>-0.5748</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.0444</v>
+        <v>-10.3464</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6132</v>
+        <v>0.7486</v>
       </c>
       <c r="J202" t="n">
-        <v>14.7168</v>
+        <v>17.9664</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.23</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3914</v>
+        <v>0.464</v>
       </c>
       <c r="J203" t="n">
-        <v>9.393599999999999</v>
+        <v>11.136</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2366</v>
+        <v>0.2844</v>
       </c>
       <c r="J204" t="n">
-        <v>5.6784</v>
+        <v>6.8256</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.93</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.204</v>
+        <v>-0.1109</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.896</v>
+        <v>-2.6616</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.376</v>
+        <v>-0.2301</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.023999999999999</v>
+        <v>-5.5224</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.43</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1795</v>
+        <v>1.1053</v>
       </c>
       <c r="J207" t="n">
-        <v>28.308</v>
+        <v>26.5272</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5029</v>
+        <v>0.4565</v>
       </c>
       <c r="J208" t="n">
-        <v>12.0696</v>
+        <v>10.956</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0184</v>
+        <v>-0.0018</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.4416</v>
+        <v>-0.0432</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.9</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.403</v>
+        <v>-0.3523</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.672000000000001</v>
+        <v>-8.4552</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.1477</v>
+        <v>-1.1423</v>
       </c>
       <c r="J211" t="n">
-        <v>-27.5448</v>
+        <v>-27.4152</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.417</v>
+        <v>0.3612</v>
       </c>
       <c r="J212" t="n">
-        <v>7.089</v>
+        <v>6.1404</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0145</v>
+        <v>-0.0216</v>
       </c>
       <c r="J213" t="n">
-        <v>0.2465</v>
+        <v>-0.3672</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4971</v>
+        <v>-0.3289</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.450699999999999</v>
+        <v>-5.5913</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5113</v>
+        <v>-0.3384</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.6921</v>
+        <v>-5.7528</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7461</v>
+        <v>-0.5061</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.6837</v>
+        <v>-8.6037</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1101</v>
+        <v>1.0125</v>
       </c>
       <c r="J217" t="n">
-        <v>18.8717</v>
+        <v>17.2125</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6187</v>
+        <v>0.5536</v>
       </c>
       <c r="J218" t="n">
-        <v>10.5179</v>
+        <v>9.411199999999999</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2509</v>
+        <v>0.2612</v>
       </c>
       <c r="J219" t="n">
-        <v>4.2653</v>
+        <v>4.4404</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2215</v>
+        <v>0.236</v>
       </c>
       <c r="J220" t="n">
-        <v>3.7655</v>
+        <v>4.012</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3442</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.0746</v>
+        <v>-5.8514</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6902</v>
+        <v>1.4577</v>
       </c>
       <c r="J222" t="n">
-        <v>32.1138</v>
+        <v>27.6963</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.183</v>
+        <v>1.1394</v>
       </c>
       <c r="J223" t="n">
-        <v>22.477</v>
+        <v>21.6486</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.32</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6931</v>
+        <v>0.7996</v>
       </c>
       <c r="J224" t="n">
-        <v>13.1689</v>
+        <v>15.1924</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4145</v>
+        <v>0.5188</v>
       </c>
       <c r="J225" t="n">
-        <v>7.8755</v>
+        <v>9.857200000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3662</v>
+        <v>0.4687</v>
       </c>
       <c r="J226" t="n">
-        <v>6.9578</v>
+        <v>8.9053</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4124</v>
+        <v>0.4665</v>
       </c>
       <c r="J227" t="n">
-        <v>7.8356</v>
+        <v>8.8635</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0161</v>
+        <v>-0.0437</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.3059</v>
+        <v>-0.8303</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3159</v>
+        <v>-0.2319</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.0021</v>
+        <v>-4.4061</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.54</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6786</v>
+        <v>-0.4565</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.8934</v>
+        <v>-8.673500000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8144</v>
+        <v>-0.5581</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.4736</v>
+        <v>-10.6039</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8107</v>
+        <v>0.7935</v>
       </c>
       <c r="J232" t="n">
-        <v>19.4568</v>
+        <v>19.044</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J233" t="n">
-        <v>14.16</v>
+        <v>13.812</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4515</v>
+        <v>0.4496</v>
       </c>
       <c r="J234" t="n">
-        <v>10.836</v>
+        <v>10.7904</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.13</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3875</v>
+        <v>0.3983</v>
       </c>
       <c r="J235" t="n">
-        <v>9.300000000000001</v>
+        <v>9.559200000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5603</v>
+        <v>-0.497</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.4472</v>
+        <v>-11.928</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.22</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4368</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J237" t="n">
-        <v>10.4832</v>
+        <v>12.036</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2712</v>
+        <v>0.2875</v>
       </c>
       <c r="J238" t="n">
-        <v>6.5088</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2874</v>
+        <v>-0.1798</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.8976</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4517</v>
+        <v>-0.2896</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.8408</v>
+        <v>-6.9504</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4655</v>
+        <v>-0.2992</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.172</v>
+        <v>-7.1808</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.43</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6143</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J242" t="n">
-        <v>12.286</v>
+        <v>10.856</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4483</v>
+        <v>0.3964</v>
       </c>
       <c r="J243" t="n">
-        <v>8.965999999999999</v>
+        <v>7.928</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2733</v>
+        <v>0.2682</v>
       </c>
       <c r="J244" t="n">
-        <v>5.466</v>
+        <v>5.364</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.17</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2418</v>
+        <v>0.2433</v>
       </c>
       <c r="J245" t="n">
-        <v>4.836</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.01</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.0415</v>
+        <v>0.0007</v>
       </c>
       <c r="J246" t="n">
-        <v>-0.83</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.48</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7461</v>
+        <v>0.7105</v>
       </c>
       <c r="J247" t="n">
-        <v>14.922</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0133</v>
+        <v>0.0015</v>
       </c>
       <c r="J248" t="n">
-        <v>0.266</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0575</v>
+        <v>-0.0348</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.15</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2889</v>
+        <v>-0.1756</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.778</v>
+        <v>-3.512</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6435</v>
+        <v>-0.4276</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.87</v>
+        <v>-8.552</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.61</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9105</v>
+        <v>1.1012</v>
       </c>
       <c r="J252" t="n">
-        <v>19.1205</v>
+        <v>23.1252</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1145</v>
+        <v>-0.0825</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.4045</v>
+        <v>-1.7325</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2025</v>
+        <v>-0.1272</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.2525</v>
+        <v>-2.6712</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3664</v>
+        <v>-0.2311</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.6944</v>
+        <v>-4.8531</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.42</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8475</v>
+        <v>-0.5844</v>
       </c>
       <c r="J256" t="n">
-        <v>-17.7975</v>
+        <v>-12.2724</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.62</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4303</v>
+        <v>1.2792</v>
       </c>
       <c r="J257" t="n">
-        <v>30.0363</v>
+        <v>26.8632</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.6</v>
       </c>
       <c r="I258" t="n">
-        <v>1.3924</v>
+        <v>1.2545</v>
       </c>
       <c r="J258" t="n">
-        <v>29.2404</v>
+        <v>26.3445</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4552</v>
+        <v>0.527</v>
       </c>
       <c r="J259" t="n">
-        <v>9.559200000000001</v>
+        <v>11.067</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.241</v>
+        <v>0.3183</v>
       </c>
       <c r="J260" t="n">
-        <v>5.061</v>
+        <v>6.6843</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8783</v>
+        <v>-0.8381</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.4443</v>
+        <v>-17.6001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9054</v>
+        <v>1.0918</v>
       </c>
       <c r="J262" t="n">
-        <v>31.689</v>
+        <v>38.213</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.4531</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J263" t="n">
-        <v>15.8585</v>
+        <v>18.648</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2059</v>
+        <v>-0.1162</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.2065</v>
+        <v>-4.067</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.73</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4884</v>
+        <v>-0.3123</v>
       </c>
       <c r="J265" t="n">
-        <v>-17.094</v>
+        <v>-10.9305</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5782</v>
+        <v>-0.3783</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.237</v>
+        <v>-13.2405</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>2.04</v>
       </c>
       <c r="I267" t="n">
-        <v>2.0593</v>
+        <v>1.802</v>
       </c>
       <c r="J267" t="n">
-        <v>72.07550000000001</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4904</v>
+        <v>0.5363</v>
       </c>
       <c r="J268" t="n">
-        <v>17.164</v>
+        <v>18.7705</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3207</v>
+        <v>0.3843</v>
       </c>
       <c r="J269" t="n">
-        <v>11.2245</v>
+        <v>13.4505</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.83</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6581</v>
+        <v>-0.5972</v>
       </c>
       <c r="J270" t="n">
-        <v>-23.0335</v>
+        <v>-20.902</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6825</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="J271" t="n">
-        <v>-23.8875</v>
+        <v>-21.8225</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0816</v>
+        <v>1.0479</v>
       </c>
       <c r="J272" t="n">
-        <v>36.7744</v>
+        <v>35.6286</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6236</v>
+        <v>0.6171</v>
       </c>
       <c r="J273" t="n">
-        <v>21.2024</v>
+        <v>20.9814</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4549</v>
+        <v>0.4699</v>
       </c>
       <c r="J274" t="n">
-        <v>15.4666</v>
+        <v>15.9766</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.15</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4158</v>
+        <v>0.4454</v>
       </c>
       <c r="J275" t="n">
-        <v>14.1372</v>
+        <v>15.1436</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6697</v>
+        <v>-0.6117</v>
       </c>
       <c r="J276" t="n">
-        <v>-22.7698</v>
+        <v>-20.7978</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.8753</v>
       </c>
       <c r="J277" t="n">
-        <v>24.0788</v>
+        <v>29.7602</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.133</v>
+        <v>0.1252</v>
       </c>
       <c r="J278" t="n">
-        <v>4.522</v>
+        <v>4.2568</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1566</v>
+        <v>-0.0958</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.3244</v>
+        <v>-3.2572</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.7</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5122</v>
+        <v>-0.3314</v>
       </c>
       <c r="J280" t="n">
-        <v>-17.4148</v>
+        <v>-11.2676</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5384</v>
+        <v>-0.3503</v>
       </c>
       <c r="J281" t="n">
-        <v>-18.3056</v>
+        <v>-11.9102</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.37</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9792</v>
+        <v>0.9669</v>
       </c>
       <c r="J282" t="n">
-        <v>23.5008</v>
+        <v>23.2056</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9354</v>
+        <v>0.9253</v>
       </c>
       <c r="J283" t="n">
-        <v>22.4496</v>
+        <v>22.2072</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7994</v>
+        <v>0.7867</v>
       </c>
       <c r="J284" t="n">
-        <v>19.1856</v>
+        <v>18.8808</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4591</v>
+        <v>-0.3896</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.0184</v>
+        <v>-9.3504</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6675</v>
+        <v>-0.6096</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.02</v>
+        <v>-14.6304</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2942</v>
+        <v>0.3263</v>
       </c>
       <c r="J287" t="n">
-        <v>7.0608</v>
+        <v>7.8312</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2783</v>
+        <v>0.3068</v>
       </c>
       <c r="J288" t="n">
-        <v>6.6792</v>
+        <v>7.3632</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0391</v>
+        <v>-0.0204</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.9384</v>
+        <v>-0.4896</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.192</v>
+        <v>-0.1114</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.608</v>
+        <v>-2.6736</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3686</v>
+        <v>-0.2287</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.846399999999999</v>
+        <v>-5.4888</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3037</v>
+        <v>1.1917</v>
       </c>
       <c r="J292" t="n">
-        <v>31.2888</v>
+        <v>28.6008</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.25</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6978</v>
+        <v>0.6887</v>
       </c>
       <c r="J293" t="n">
-        <v>16.7472</v>
+        <v>16.5288</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5139</v>
+        <v>0.5189</v>
       </c>
       <c r="J294" t="n">
-        <v>12.3336</v>
+        <v>12.4536</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1649</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.9576</v>
+        <v>-2.2152</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.5857</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.4968</v>
+        <v>-14.0568</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.39</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6418</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="J297" t="n">
-        <v>15.4032</v>
+        <v>18.7632</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0189</v>
+        <v>-0.0191</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.4536</v>
+        <v>-0.4584</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.98</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0477</v>
+        <v>-0.0344</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.1448</v>
+        <v>-0.8256</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1649</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.9576</v>
+        <v>-2.3424</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6545</v>
+        <v>-0.4359</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.708</v>
+        <v>-10.4616</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.75</v>
       </c>
       <c r="I302" t="n">
-        <v>1.6464</v>
+        <v>1.4239</v>
       </c>
       <c r="J302" t="n">
-        <v>32.928</v>
+        <v>28.478</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.56</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2919</v>
+        <v>1.1939</v>
       </c>
       <c r="J303" t="n">
-        <v>25.838</v>
+        <v>23.878</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6834</v>
+        <v>0.7511</v>
       </c>
       <c r="J304" t="n">
-        <v>13.668</v>
+        <v>15.022</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.23</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5301</v>
+        <v>0.6136</v>
       </c>
       <c r="J305" t="n">
-        <v>10.602</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0161</v>
+        <v>-0.9933</v>
       </c>
       <c r="J306" t="n">
-        <v>-20.322</v>
+        <v>-19.866</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.78</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0992</v>
+        <v>1.2726</v>
       </c>
       <c r="J307" t="n">
-        <v>21.984</v>
+        <v>25.452</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2813</v>
+        <v>-0.1779</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.626</v>
+        <v>-3.558</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.74</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4476</v>
+        <v>-0.2876</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.952</v>
+        <v>-5.752</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5814</v>
+        <v>-0.3825</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.628</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6813</v>
+        <v>-0.4564</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.626</v>
+        <v>-9.128</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.18</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3853</v>
+        <v>0.3309</v>
       </c>
       <c r="J312" t="n">
-        <v>8.8619</v>
+        <v>7.6107</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0592</v>
+        <v>-0.0558</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.3616</v>
+        <v>-1.2834</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0805</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.8515</v>
+        <v>-1.5778</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3138</v>
+        <v>-0.1984</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.2174</v>
+        <v>-4.5632</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5686</v>
+        <v>-0.3732</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.0778</v>
+        <v>-8.583600000000001</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4741</v>
+        <v>0.4081</v>
       </c>
       <c r="J317" t="n">
-        <v>10.9043</v>
+        <v>9.3863</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.25</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4059</v>
+        <v>0.3484</v>
       </c>
       <c r="J318" t="n">
-        <v>9.335699999999999</v>
+        <v>8.013199999999999</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3774</v>
+        <v>0.3242</v>
       </c>
       <c r="J319" t="n">
-        <v>8.680199999999999</v>
+        <v>7.4566</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0439</v>
+        <v>0.0672</v>
       </c>
       <c r="J320" t="n">
-        <v>1.0097</v>
+        <v>1.5456</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.279</v>
+        <v>-0.1606</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.417</v>
+        <v>-3.6938</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.75</v>
       </c>
       <c r="I322" t="n">
-        <v>1.5769</v>
+        <v>1.3884</v>
       </c>
       <c r="J322" t="n">
-        <v>26.8073</v>
+        <v>23.6028</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1741</v>
+        <v>1.1439</v>
       </c>
       <c r="J323" t="n">
-        <v>19.9597</v>
+        <v>19.4463</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.4</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8451</v>
+        <v>0.9581</v>
       </c>
       <c r="J324" t="n">
-        <v>14.3667</v>
+        <v>16.2877</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.39</v>
       </c>
       <c r="I325" t="n">
-        <v>0.823</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J325" t="n">
-        <v>13.991</v>
+        <v>15.963</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4892</v>
+        <v>0.6037</v>
       </c>
       <c r="J326" t="n">
-        <v>8.3164</v>
+        <v>10.2629</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.04</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2431</v>
+        <v>0.2412</v>
       </c>
       <c r="J327" t="n">
-        <v>4.1327</v>
+        <v>4.1004</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.82</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2062</v>
+        <v>-0.1784</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.5054</v>
+        <v>-3.0328</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.7</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4083</v>
+        <v>-0.2973</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.9411</v>
+        <v>-5.0541</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.63</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5315</v>
+        <v>-0.3609</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.035500000000001</v>
+        <v>-6.1353</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.3</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.9563</v>
+        <v>-0.669</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.2571</v>
+        <v>-11.373</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.56</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3326</v>
+        <v>1.2136</v>
       </c>
       <c r="J332" t="n">
-        <v>27.9846</v>
+        <v>25.4856</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.2343</v>
+        <v>1.1504</v>
       </c>
       <c r="J333" t="n">
-        <v>25.9203</v>
+        <v>24.1584</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.28</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7342</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>15.4182</v>
+        <v>15.6114</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.9</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.4809</v>
+        <v>-0.4074</v>
       </c>
       <c r="J335" t="n">
-        <v>-10.0989</v>
+        <v>-8.555400000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6617</v>
+        <v>-0.6005</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.8957</v>
+        <v>-12.6105</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4367</v>
+        <v>0.4995</v>
       </c>
       <c r="J337" t="n">
-        <v>9.1707</v>
+        <v>10.4895</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0487</v>
+        <v>-0.053</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.0227</v>
+        <v>-1.113</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.217</v>
+        <v>-0.1445</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.557</v>
+        <v>-3.0345</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3216</v>
+        <v>-0.2059</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.7536</v>
+        <v>-4.3239</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.59</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6405</v>
+        <v>-0.4263</v>
       </c>
       <c r="J341" t="n">
-        <v>-13.4505</v>
+        <v>-8.952299999999999</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.7</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5337</v>
+        <v>1.3524</v>
       </c>
       <c r="J342" t="n">
-        <v>24.5392</v>
+        <v>21.6384</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.51</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1687</v>
+        <v>1.1234</v>
       </c>
       <c r="J343" t="n">
-        <v>18.6992</v>
+        <v>17.9744</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.22</v>
       </c>
       <c r="I344" t="n">
-        <v>0.4825</v>
+        <v>0.5792</v>
       </c>
       <c r="J344" t="n">
-        <v>7.72</v>
+        <v>9.267200000000001</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4095</v>
+        <v>0.5056</v>
       </c>
       <c r="J345" t="n">
-        <v>6.552</v>
+        <v>8.089600000000001</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.14</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2837</v>
+        <v>0.3769</v>
       </c>
       <c r="J346" t="n">
-        <v>4.5392</v>
+        <v>6.0304</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.2005</v>
+        <v>-0.1783</v>
       </c>
       <c r="J347" t="n">
-        <v>-3.208</v>
+        <v>-2.8528</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2164</v>
+        <v>-0.1892</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.4624</v>
+        <v>-3.0272</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.7</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3753</v>
+        <v>-0.2914</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.0048</v>
+        <v>-4.6624</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.67</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4269</v>
+        <v>-0.3194</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.8304</v>
+        <v>-5.1104</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.3</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.9503</v>
+        <v>-0.6639</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.2048</v>
+        <v>-10.6224</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.5</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1413</v>
+        <v>1.1089</v>
       </c>
       <c r="J352" t="n">
-        <v>20.5434</v>
+        <v>19.9602</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.47</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0787</v>
+        <v>1.0722</v>
       </c>
       <c r="J353" t="n">
-        <v>19.4166</v>
+        <v>19.2996</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.41</v>
       </c>
       <c r="I354" t="n">
-        <v>0.9469</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J354" t="n">
-        <v>17.0442</v>
+        <v>17.7732</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.36</v>
       </c>
       <c r="I355" t="n">
-        <v>0.8146</v>
+        <v>0.8927</v>
       </c>
       <c r="J355" t="n">
-        <v>14.6628</v>
+        <v>16.0686</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.09</v>
       </c>
       <c r="I356" t="n">
-        <v>0.1455</v>
+        <v>0.2354</v>
       </c>
       <c r="J356" t="n">
-        <v>2.619</v>
+        <v>4.2372</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.25</v>
       </c>
       <c r="I357" t="n">
-        <v>0.5296</v>
+        <v>0.6291</v>
       </c>
       <c r="J357" t="n">
-        <v>9.5328</v>
+        <v>11.3238</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.82</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2601</v>
+        <v>-0.1963</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.6818</v>
+        <v>-3.5334</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.75</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3928</v>
+        <v>-0.2626</v>
       </c>
       <c r="J359" t="n">
-        <v>-7.0704</v>
+        <v>-4.7268</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.61</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.5939</v>
+        <v>-0.3951</v>
       </c>
       <c r="J360" t="n">
-        <v>-10.6902</v>
+        <v>-7.1118</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.659</v>
+        <v>-0.4417</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.862</v>
+        <v>-7.9506</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.27</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7786</v>
+        <v>0.7552</v>
       </c>
       <c r="J362" t="n">
-        <v>17.9078</v>
+        <v>17.3696</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.26</v>
       </c>
       <c r="I363" t="n">
-        <v>0.7549</v>
+        <v>0.731</v>
       </c>
       <c r="J363" t="n">
-        <v>17.3627</v>
+        <v>16.813</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.08</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2375</v>
+        <v>0.2675</v>
       </c>
       <c r="J364" t="n">
-        <v>5.4625</v>
+        <v>6.1525</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.08</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2375</v>
+        <v>0.2675</v>
       </c>
       <c r="J365" t="n">
-        <v>5.4625</v>
+        <v>6.1525</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6782</v>
+        <v>-0.6237</v>
       </c>
       <c r="J366" t="n">
-        <v>-15.5986</v>
+        <v>-14.3451</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.25</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4717</v>
+        <v>0.5491</v>
       </c>
       <c r="J367" t="n">
-        <v>10.8491</v>
+        <v>12.6293</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.03</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1158</v>
+        <v>0.1029</v>
       </c>
       <c r="J368" t="n">
-        <v>2.6634</v>
+        <v>2.3667</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0672</v>
+        <v>0.0474</v>
       </c>
       <c r="J369" t="n">
-        <v>1.5456</v>
+        <v>1.0902</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3851</v>
+        <v>-0.2428</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.8573</v>
+        <v>-5.5844</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.66</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5624</v>
+        <v>-0.3679</v>
       </c>
       <c r="J371" t="n">
-        <v>-12.9352</v>
+        <v>-8.4617</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.8783</v>
+        <v>0.8635</v>
       </c>
       <c r="J372" t="n">
-        <v>19.3226</v>
+        <v>18.997</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>0.8327</v>
+        <v>0.8165</v>
       </c>
       <c r="J373" t="n">
-        <v>18.3194</v>
+        <v>17.963</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.17</v>
       </c>
       <c r="I374" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="J374" t="n">
-        <v>11.1672</v>
+        <v>10.9978</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.98</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1954</v>
+        <v>-0.1261</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.2988</v>
+        <v>-2.7742</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.87</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5346</v>
+        <v>-0.4699</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.7612</v>
+        <v>-10.3378</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.24</v>
       </c>
       <c r="I377" t="n">
-        <v>0.4868</v>
+        <v>0.5671</v>
       </c>
       <c r="J377" t="n">
-        <v>10.7096</v>
+        <v>12.4762</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I378" t="n">
-        <v>0.2074</v>
+        <v>0.2001</v>
       </c>
       <c r="J378" t="n">
-        <v>4.5628</v>
+        <v>4.4022</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.3288</v>
+        <v>-0.2132</v>
       </c>
       <c r="J379" t="n">
-        <v>-7.2336</v>
+        <v>-4.6904</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.74</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4351</v>
+        <v>-0.2818</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.5722</v>
+        <v>-6.1996</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7466</v>
+        <v>-0.5061</v>
       </c>
       <c r="J381" t="n">
-        <v>-16.4252</v>
+        <v>-11.1342</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0684</v>
+        <v>7.0567</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5559</v>
+        <v>1.5533</v>
       </c>
       <c r="D2" t="n">
-        <v>2.553</v>
+        <v>2.5882</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0684</v>
+        <v>7.0567</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6486</v>
+        <v>2.5741</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4198</v>
+        <v>4.4826</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8455</v>
+        <v>3.5986</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9995</v>
+        <v>1.9432</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4198</v>
+        <v>4.4826</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>6.419300000000001</v>
+        <v>6.4258</v>
       </c>
       <c r="N2" t="n">
         <v>239</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2285</v>
+        <v>6.1756</v>
       </c>
       <c r="C3" t="n">
-        <v>1.371</v>
+        <v>1.3593</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1738</v>
+        <v>2.1871</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2285</v>
+        <v>6.1756</v>
       </c>
       <c r="F3" t="n">
-        <v>3.225</v>
+        <v>3.1058</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0035</v>
+        <v>3.0698</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8765</v>
+        <v>5.353</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0555</v>
+        <v>2.8906</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0035</v>
+        <v>3.0698</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>6.058999999999999</v>
+        <v>5.9604</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7533</v>
+        <v>5.7179</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2664</v>
+        <v>1.2586</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9593</v>
+        <v>1.9787</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7533</v>
+        <v>5.7179</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5043</v>
+        <v>2.4066</v>
       </c>
       <c r="G4" t="n">
-        <v>3.249</v>
+        <v>3.3113</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3372</v>
+        <v>3.046</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7352</v>
+        <v>1.6448</v>
       </c>
       <c r="J4" t="n">
-        <v>3.249</v>
+        <v>3.3113</v>
       </c>
       <c r="K4" t="n">
         <v>103</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9842</v>
+        <v>4.9561</v>
       </c>
       <c r="N4" t="n">
         <v>239</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.455</v>
+        <v>5.3033</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2007</v>
+        <v>1.1673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8246</v>
+        <v>1.79</v>
       </c>
       <c r="E5" t="n">
-        <v>5.455</v>
+        <v>5.3033</v>
       </c>
       <c r="F5" t="n">
-        <v>3.136</v>
+        <v>3.0247</v>
       </c>
       <c r="G5" t="n">
-        <v>2.319</v>
+        <v>2.2786</v>
       </c>
       <c r="H5" t="n">
-        <v>5.563</v>
+        <v>5.0854</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8925</v>
+        <v>2.7461</v>
       </c>
       <c r="J5" t="n">
-        <v>2.319</v>
+        <v>2.2786</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2115</v>
+        <v>5.0247</v>
       </c>
       <c r="N5" t="n">
         <v>276</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0247</v>
+        <v>5.0359</v>
       </c>
       <c r="C6" t="n">
-        <v>1.106</v>
+        <v>1.1085</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6304</v>
+        <v>1.6682</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0247</v>
+        <v>5.0359</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2196</v>
+        <v>3.1154</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8051</v>
+        <v>1.9205</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8576</v>
+        <v>5.3847</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0457</v>
+        <v>2.9077</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8051</v>
+        <v>1.9205</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8508</v>
+        <v>4.828200000000001</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3548</v>
+        <v>4.3149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9586</v>
+        <v>0.9498</v>
       </c>
       <c r="D7" t="n">
-        <v>1.328</v>
+        <v>1.34</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3548</v>
+        <v>4.3149</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2229</v>
+        <v>4.1657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1319</v>
+        <v>0.1492</v>
       </c>
       <c r="H7" t="n">
-        <v>9.3926</v>
+        <v>8.8499</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8837</v>
+        <v>4.7788</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1319</v>
+        <v>0.1492</v>
       </c>
       <c r="K7" t="n">
         <v>219</v>
@@ -759,7 +759,7 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0156</v>
+        <v>4.928000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>280</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8503</v>
+        <v>3.9447</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8475</v>
+        <v>0.8683</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1002</v>
+        <v>1.1715</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8503</v>
+        <v>3.9447</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6015</v>
+        <v>-0.636</v>
       </c>
       <c r="H8" t="n">
-        <v>13.6829</v>
+        <v>13.3056</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1145</v>
+        <v>7.1849</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6015</v>
+        <v>-0.636</v>
       </c>
       <c r="K8" t="n">
         <v>238</v>
@@ -805,7 +805,7 @@
         <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>6.513</v>
+        <v>6.5489</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7372</v>
+        <v>3.8362</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8226</v>
+        <v>0.8444</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0491</v>
+        <v>1.1221</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7372</v>
+        <v>3.8362</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7146</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>10.862</v>
+        <v>10.3083</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6478</v>
+        <v>5.5664</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7146</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>238</v>
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9332</v>
+        <v>4.821899999999999</v>
       </c>
       <c r="N9" t="n">
         <v>280</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6393</v>
+        <v>3.7339</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8011</v>
+        <v>0.8219</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0049</v>
+        <v>1.0755</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6393</v>
+        <v>3.7339</v>
       </c>
       <c r="F10" t="n">
-        <v>3.16</v>
+        <v>3.108</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4793</v>
+        <v>0.6259</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6474</v>
+        <v>5.3603</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9364</v>
+        <v>2.8945</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4793</v>
+        <v>0.6259</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4157</v>
+        <v>3.5204</v>
       </c>
       <c r="N10" t="n">
         <v>276</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5446</v>
+        <v>3.4643</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7802</v>
+        <v>0.7625</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9528</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5446</v>
+        <v>3.4643</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7139</v>
+        <v>2.9453</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1693</v>
+        <v>0.519</v>
       </c>
       <c r="H11" t="n">
-        <v>7.599</v>
+        <v>4.8235</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9511</v>
+        <v>2.6046</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1693</v>
+        <v>0.519</v>
       </c>
       <c r="K11" t="n">
         <v>219</v>
@@ -943,7 +943,7 @@
         <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7818</v>
+        <v>3.1236</v>
       </c>
       <c r="N11" t="n">
         <v>280</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5391</v>
+        <v>3.4434</v>
       </c>
       <c r="C12" t="n">
-        <v>0.779</v>
+        <v>0.7579</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9597</v>
+        <v>0.9433</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5391</v>
+        <v>3.4434</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0373</v>
+        <v>3.1693</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5018</v>
+        <v>0.2741</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2152</v>
+        <v>5.5624</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7116</v>
+        <v>3.0036</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5018</v>
+        <v>0.2741</v>
       </c>
       <c r="K12" t="n">
         <v>219</v>
@@ -989,7 +989,7 @@
         <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2134</v>
+        <v>3.2777</v>
       </c>
       <c r="N12" t="n">
         <v>280</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4614</v>
+        <v>3.4237</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7619</v>
+        <v>0.7536</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9246</v>
+        <v>0.9343</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4614</v>
+        <v>3.4237</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2438</v>
+        <v>3.5901</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2176</v>
+        <v>-0.1664</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9427</v>
+        <v>6.9508</v>
       </c>
       <c r="I13" t="n">
-        <v>3.09</v>
+        <v>3.7534</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2176</v>
+        <v>-0.1664</v>
       </c>
       <c r="K13" t="n">
         <v>219</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3076</v>
+        <v>3.587</v>
       </c>
       <c r="N13" t="n">
         <v>280</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0241</v>
+        <v>3.2113</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6656</v>
+        <v>0.7069</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7272</v>
+        <v>0.8376</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0241</v>
+        <v>3.2113</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4647</v>
+        <v>1.495</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5594</v>
+        <v>1.7163</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4647</v>
+        <v>1.495</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8073</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5594</v>
+        <v>1.7163</v>
       </c>
       <c r="K14" t="n">
         <v>121</v>
@@ -1081,7 +1081,7 @@
         <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>2.321</v>
+        <v>2.5236</v>
       </c>
       <c r="N14" t="n">
         <v>276</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9442</v>
+        <v>2.8413</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6481</v>
+        <v>0.6254</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6911</v>
+        <v>0.6692</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9442</v>
+        <v>2.8413</v>
       </c>
       <c r="F15" t="n">
-        <v>2.537</v>
+        <v>2.4466</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4072</v>
+        <v>0.3947</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4525</v>
+        <v>3.1779</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7951</v>
+        <v>1.7161</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4072</v>
+        <v>0.3947</v>
       </c>
       <c r="K15" t="n">
         <v>238</v>
@@ -1127,7 +1127,7 @@
         <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2023</v>
+        <v>2.1108</v>
       </c>
       <c r="N15" t="n">
         <v>280</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flayy</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8278</v>
+        <v>2.5883</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6224</v>
+        <v>0.5697</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8278</v>
+        <v>2.5883</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8278</v>
+        <v>0.4693</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.119</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8496</v>
+        <v>0.4693</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8496</v>
+        <v>0.2534</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.119</v>
       </c>
       <c r="K16" t="n">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8496</v>
+        <v>2.3724</v>
       </c>
       <c r="N16" t="n">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>flayy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4563</v>
+        <v>2.4631</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5407</v>
+        <v>0.5422</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4709</v>
+        <v>0.4971</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4563</v>
+        <v>2.4631</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4563</v>
+        <v>2.4631</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4563</v>
+        <v>2.6661</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4563</v>
+        <v>2.6661</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4563</v>
+        <v>2.6661</v>
       </c>
       <c r="N17" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.452</v>
+        <v>2.3319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5397</v>
+        <v>0.5133</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4689</v>
+        <v>0.4373</v>
       </c>
       <c r="E18" t="n">
-        <v>2.452</v>
+        <v>2.3319</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4537</v>
+        <v>2.3319</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9983</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4537</v>
+        <v>2.3789</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2359</v>
+        <v>2.3789</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9983</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="L18" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2342</v>
+        <v>2.3789</v>
       </c>
       <c r="N18" t="n">
-        <v>239</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4208</v>
+        <v>0.4028</v>
       </c>
       <c r="D19" t="n">
-        <v>0.225</v>
+        <v>0.2088</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9117</v>
+        <v>1.8298</v>
       </c>
       <c r="N19" t="n">
         <v>121</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7228</v>
+        <v>1.8033</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3792</v>
+        <v>0.3969</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1397</v>
+        <v>0.1967</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7228</v>
+        <v>1.8033</v>
       </c>
       <c r="F20" t="n">
-        <v>2.868</v>
+        <v>-0.6874</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1452</v>
+        <v>2.4907</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6189</v>
+        <v>-0.6874</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4016</v>
+        <v>-0.3712</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1452</v>
+        <v>2.4907</v>
       </c>
       <c r="K20" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L20" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2564</v>
+        <v>2.1195</v>
       </c>
       <c r="N20" t="n">
-        <v>276</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6876</v>
+        <v>1.6623</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3715</v>
+        <v>0.3659</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1239</v>
+        <v>0.1325</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6876</v>
+        <v>1.6623</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7624</v>
+        <v>2.758</v>
       </c>
       <c r="G21" t="n">
-        <v>2.45</v>
+        <v>-1.0957</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7624</v>
+        <v>4.2054</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3964</v>
+        <v>2.2709</v>
       </c>
       <c r="J21" t="n">
-        <v>2.45</v>
+        <v>-1.0957</v>
       </c>
       <c r="K21" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0536</v>
+        <v>1.1752</v>
       </c>
       <c r="N21" t="n">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3351</v>
+        <v>0.3231</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0493</v>
+        <v>0.0439</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5225</v>
+        <v>1.4677</v>
       </c>
       <c r="N22" t="n">
         <v>121</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="C23" t="n">
-        <v>0.308</v>
+        <v>0.3019</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0063</v>
+        <v>0.0002</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3994</v>
+        <v>1.3716</v>
       </c>
       <c r="N23" t="n">
         <v>122</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2821</v>
+        <v>0.2564</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0595</v>
+        <v>-0.0939</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2814</v>
+        <v>1.1649</v>
       </c>
       <c r="N24" t="n">
         <v>154</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7881</v>
+        <v>0.6745</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1735</v>
+        <v>0.1485</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2822</v>
+        <v>-0.3172</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7881</v>
+        <v>0.6745</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6183</v>
+        <v>0.5296</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1698</v>
+        <v>0.1449</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6183</v>
+        <v>0.5296</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3215</v>
+        <v>0.286</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1698</v>
+        <v>0.1449</v>
       </c>
       <c r="K25" t="n">
         <v>238</v>
@@ -1587,7 +1587,7 @@
         <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4913</v>
+        <v>0.4308999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>280</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hfah</t>
+          <t>Qlocuu</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1117</v>
+        <v>0.1103</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4089</v>
+        <v>-0.3961</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5075</v>
+        <v>0.5011</v>
       </c>
       <c r="N26" t="n">
         <v>156</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Qlocuu</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1111</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4101</v>
+        <v>-0.4263</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5049</v>
+        <v>0.4347</v>
       </c>
       <c r="N27" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>hfah</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1056</v>
+        <v>0.0893</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4214</v>
+        <v>-0.4396</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4799</v>
+        <v>0.4056</v>
       </c>
       <c r="N28" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0806</v>
+        <v>0.0772</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4727</v>
+        <v>-0.4646</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3661</v>
+        <v>0.3507</v>
       </c>
       <c r="N29" t="n">
         <v>154</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0401</v>
+        <v>0.0267</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5558</v>
+        <v>-0.569</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1821</v>
+        <v>0.1213</v>
       </c>
       <c r="N30" t="n">
         <v>122</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0105</v>
+        <v>0.0066</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.6105</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0479</v>
+        <v>0.0302</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2222</v>
+        <v>-0.1511</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0489</v>
+        <v>-0.0333</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7383</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2222</v>
+        <v>-0.1511</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5869</v>
+        <v>0.6845</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8091</v>
+        <v>-0.8356</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5869</v>
+        <v>0.6845</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3052</v>
+        <v>0.3696</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8091</v>
+        <v>-0.8356</v>
       </c>
       <c r="K32" t="n">
         <v>238</v>
@@ -1909,7 +1909,7 @@
         <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5039</v>
+        <v>-0.466</v>
       </c>
       <c r="N32" t="n">
         <v>280</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sobol</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0511</v>
+        <v>-0.0648</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7428</v>
+        <v>-0.7581</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2322</v>
+        <v>-0.2942</v>
       </c>
       <c r="N33" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>Sobol</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0578</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7567</v>
+        <v>-0.766</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2628</v>
+        <v>-0.3116</v>
       </c>
       <c r="N34" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>urban0</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0687</v>
+        <v>-0.0741</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7788</v>
+        <v>-0.7774</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3366</v>
       </c>
       <c r="N35" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>urban0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0707</v>
+        <v>-0.0815</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.783</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3212</v>
+        <v>-0.3704</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0839</v>
+        <v>-0.0823</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.7945</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.381</v>
+        <v>-0.374</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1171</v>
+        <v>-0.1259</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8782</v>
+        <v>-0.8845</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.532</v>
+        <v>-0.5718</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2188</v>
+        <v>-0.2301</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0867</v>
+        <v>-1.1</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9939</v>
+        <v>-1.0452</v>
       </c>
       <c r="N39" t="n">
         <v>156</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7414</v>
+        <v>-1.507</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3833</v>
+        <v>-0.3317</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4242</v>
+        <v>-1.3102</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7414</v>
+        <v>-1.507</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8453</v>
+        <v>-1.6059</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1039</v>
+        <v>0.0989</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8453</v>
+        <v>-1.6059</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9594</v>
+        <v>-0.8672</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1039</v>
+        <v>0.0989</v>
       </c>
       <c r="K40" t="n">
         <v>219</v>
@@ -2277,7 +2277,7 @@
         <v>61</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.8555</v>
+        <v>-0.7683</v>
       </c>
       <c r="N40" t="n">
         <v>280</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4647</v>
+        <v>-0.4559</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5911</v>
+        <v>-1.5671</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1111</v>
+        <v>-2.0714</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3376</v>
+        <v>0.3296</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4144</v>
+        <v>6.2624</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1529</v>
+        <v>0.1504</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9051</v>
+        <v>2.8576</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1469</v>
+        <v>-0.1649</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.7911</v>
+        <v>-3.1331</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3125</v>
+        <v>-0.3291</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.9375</v>
+        <v>-6.2529</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6896</v>
+        <v>-0.6843</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.1024</v>
+        <v>-13.0017</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1008</v>
+        <v>1.1339</v>
       </c>
       <c r="J7" t="n">
-        <v>20.9152</v>
+        <v>21.5441</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7113</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>13.5147</v>
+        <v>13.5508</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4661</v>
+        <v>0.4819</v>
       </c>
       <c r="J9" t="n">
-        <v>8.8559</v>
+        <v>9.1561</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1819</v>
+        <v>0.206</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4561</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1959</v>
+        <v>-0.2005</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7221</v>
+        <v>-3.8095</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5674</v>
+        <v>0.5554</v>
       </c>
       <c r="J12" t="n">
-        <v>12.4828</v>
+        <v>12.2188</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2213</v>
+        <v>0.2294</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8686</v>
+        <v>5.0468</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.099</v>
+        <v>-0.1107</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.178</v>
+        <v>-2.4354</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2177</v>
+        <v>-0.2315</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.7894</v>
+        <v>-5.093</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3256</v>
+        <v>-0.3376</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.1632</v>
+        <v>-7.4272</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3821</v>
+        <v>0.3931</v>
       </c>
       <c r="J17" t="n">
-        <v>8.4062</v>
+        <v>8.648199999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2824</v>
+        <v>0.2968</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2128</v>
+        <v>6.5296</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.177</v>
+        <v>0.1924</v>
       </c>
       <c r="J19" t="n">
-        <v>3.894</v>
+        <v>4.2328</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0738</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6236</v>
+        <v>1.892</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2184</v>
+        <v>-0.2299</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.8048</v>
+        <v>-5.0578</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.46</v>
       </c>
       <c r="I22" t="n">
-        <v>1.106</v>
+        <v>1.0839</v>
       </c>
       <c r="J22" t="n">
-        <v>23.226</v>
+        <v>22.7619</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7426</v>
+        <v>0.7045</v>
       </c>
       <c r="J23" t="n">
-        <v>15.5946</v>
+        <v>14.7945</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4981</v>
+        <v>0.4866</v>
       </c>
       <c r="J24" t="n">
-        <v>10.4601</v>
+        <v>10.2186</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2974</v>
+        <v>-0.2855</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.2454</v>
+        <v>-5.9955</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.85</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5269</v>
+        <v>-0.4958</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.0649</v>
+        <v>-10.4118</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7967</v>
+        <v>0.7604</v>
       </c>
       <c r="J27" t="n">
-        <v>16.7307</v>
+        <v>15.9684</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3015</v>
+        <v>0.3062</v>
       </c>
       <c r="J28" t="n">
-        <v>6.3315</v>
+        <v>6.4302</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1359</v>
+        <v>0.1455</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8539</v>
+        <v>3.0555</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2004</v>
+        <v>-0.2135</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.2084</v>
+        <v>-4.4835</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3758</v>
+        <v>-0.3856</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.8918</v>
+        <v>-8.0976</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1421</v>
+        <v>1.1437</v>
       </c>
       <c r="J32" t="n">
-        <v>20.5578</v>
+        <v>20.5866</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9353</v>
+        <v>0.8811</v>
       </c>
       <c r="J33" t="n">
-        <v>16.8354</v>
+        <v>15.8598</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5995</v>
+        <v>0.5824</v>
       </c>
       <c r="J34" t="n">
-        <v>10.791</v>
+        <v>10.4832</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5515</v>
+        <v>0.5394</v>
       </c>
       <c r="J35" t="n">
-        <v>9.927</v>
+        <v>9.709199999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2298</v>
+        <v>-0.2143</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.1364</v>
+        <v>-3.8574</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5951</v>
+        <v>0.5689</v>
       </c>
       <c r="J37" t="n">
-        <v>10.7118</v>
+        <v>10.2402</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1203</v>
+        <v>0.1206</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1654</v>
+        <v>2.1708</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1013</v>
+        <v>-0.1158</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.8234</v>
+        <v>-2.0844</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3321</v>
+        <v>-0.3462</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.9778</v>
+        <v>-6.2316</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4717</v>
+        <v>-0.4796</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.490600000000001</v>
+        <v>-8.6328</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.26</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J42" t="n">
-        <v>26.1534</v>
+        <v>25.8342</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.53</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1214</v>
+        <v>1.1264</v>
       </c>
       <c r="J43" t="n">
-        <v>15.6996</v>
+        <v>15.7696</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9742</v>
+        <v>0.9312</v>
       </c>
       <c r="J44" t="n">
-        <v>13.6388</v>
+        <v>13.0368</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9163</v>
+        <v>0.8754</v>
       </c>
       <c r="J45" t="n">
-        <v>12.8282</v>
+        <v>12.2556</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8737</v>
+        <v>0.8376</v>
       </c>
       <c r="J46" t="n">
-        <v>12.2318</v>
+        <v>11.7264</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1766</v>
+        <v>1.1599</v>
       </c>
       <c r="J47" t="n">
-        <v>16.4724</v>
+        <v>16.2386</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4721</v>
+        <v>-0.4857</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.6094</v>
+        <v>-6.7998</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.48</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4909</v>
+        <v>-0.5033</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.8726</v>
+        <v>-7.0462</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5666</v>
+        <v>-0.5735</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.9324</v>
+        <v>-8.029</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6615</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.260999999999999</v>
+        <v>-9.251200000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5224</v>
+        <v>0.5266</v>
       </c>
       <c r="J52" t="n">
-        <v>15.672</v>
+        <v>15.798</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3186</v>
+        <v>0.3323</v>
       </c>
       <c r="J53" t="n">
-        <v>9.558</v>
+        <v>9.968999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1489</v>
+        <v>0.164</v>
       </c>
       <c r="J54" t="n">
-        <v>4.467</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0297</v>
+        <v>-0.0322</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.891</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2498</v>
+        <v>-0.2609</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.494</v>
+        <v>-7.827</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5276</v>
+        <v>0.5188</v>
       </c>
       <c r="J57" t="n">
-        <v>15.828</v>
+        <v>15.564</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4746</v>
+        <v>0.4697</v>
       </c>
       <c r="J58" t="n">
-        <v>14.238</v>
+        <v>14.091</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1108</v>
+        <v>-0.123</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.324</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.72</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3163</v>
+        <v>-0.3285</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.489000000000001</v>
+        <v>-9.855</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3542</v>
+        <v>-0.3653</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.626</v>
+        <v>-10.959</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7751</v>
+        <v>0.7418</v>
       </c>
       <c r="J62" t="n">
-        <v>17.8273</v>
+        <v>17.0614</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0529</v>
+        <v>-0.0604</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.2167</v>
+        <v>-1.3892</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0789</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.8147</v>
+        <v>-2.0332</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1149</v>
+        <v>-0.1261</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.6427</v>
+        <v>-2.9003</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1263</v>
+        <v>-0.138</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.9049</v>
+        <v>-3.174</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.07</v>
       </c>
       <c r="I67" t="n">
-        <v>1.8338</v>
+        <v>1.8493</v>
       </c>
       <c r="J67" t="n">
-        <v>42.1774</v>
+        <v>42.5339</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7091</v>
+        <v>0.6768</v>
       </c>
       <c r="J68" t="n">
-        <v>16.3093</v>
+        <v>15.5664</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0405</v>
+        <v>-0.0279</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.9315</v>
+        <v>-0.6417</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.84</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5621</v>
+        <v>-0.5259</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.9283</v>
+        <v>-12.0957</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9897</v>
+        <v>-0.9028</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.7631</v>
+        <v>-20.7644</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.058</v>
+        <v>1.0207</v>
       </c>
       <c r="J72" t="n">
-        <v>31.74</v>
+        <v>30.621</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>2.508</v>
+        <v>2.826</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1184</v>
+        <v>-0.1288</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.552</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1411</v>
+        <v>-0.1523</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.233</v>
+        <v>-4.569</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1949</v>
+        <v>-0.2069</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.847</v>
+        <v>-6.207</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="J77" t="n">
-        <v>20.097</v>
+        <v>19.074</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5174</v>
+        <v>0.4998</v>
       </c>
       <c r="J78" t="n">
-        <v>15.522</v>
+        <v>14.994</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3012</v>
+        <v>0.3024</v>
       </c>
       <c r="J79" t="n">
-        <v>9.036</v>
+        <v>9.071999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1468</v>
+        <v>-0.147</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.404</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4528</v>
+        <v>-0.4327</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.584</v>
+        <v>-12.981</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.85</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2976</v>
+        <v>1.4123</v>
       </c>
       <c r="J82" t="n">
-        <v>28.5472</v>
+        <v>31.0706</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7356</v>
+        <v>0.8149</v>
       </c>
       <c r="J83" t="n">
-        <v>16.1832</v>
+        <v>17.9278</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1066</v>
+        <v>-0.0955</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.3452</v>
+        <v>-2.101</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.185</v>
+        <v>-0.1736</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.07</v>
+        <v>-3.8192</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5461</v>
+        <v>-0.5093</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.0142</v>
+        <v>-11.2046</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2447</v>
+        <v>0.2414</v>
       </c>
       <c r="J87" t="n">
-        <v>5.3834</v>
+        <v>5.3108</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0055</v>
+        <v>-0.0137</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.121</v>
+        <v>-0.3014</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1733</v>
+        <v>-0.1902</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.8126</v>
+        <v>-4.1844</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2627</v>
+        <v>-0.279</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.7794</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3395</v>
+        <v>-0.3537</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.469</v>
+        <v>-7.7814</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4629</v>
+        <v>0.5103</v>
       </c>
       <c r="J92" t="n">
-        <v>7.4064</v>
+        <v>8.1648</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.06</v>
       </c>
       <c r="I93" t="n">
-        <v>0.148</v>
+        <v>0.1513</v>
       </c>
       <c r="J93" t="n">
-        <v>2.368</v>
+        <v>2.4208</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.88</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1442</v>
+        <v>-0.1601</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.3072</v>
+        <v>-2.5616</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1852</v>
+        <v>-0.2017</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.9632</v>
+        <v>-3.2272</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6601</v>
+        <v>-0.6562</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.5616</v>
+        <v>-10.4992</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.67</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5975</v>
+        <v>0.6872</v>
       </c>
       <c r="J97" t="n">
-        <v>9.56</v>
+        <v>10.9952</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3595</v>
+        <v>0.3942</v>
       </c>
       <c r="J98" t="n">
-        <v>5.752</v>
+        <v>6.3072</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3595</v>
+        <v>0.3942</v>
       </c>
       <c r="J99" t="n">
-        <v>5.752</v>
+        <v>6.3072</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2957</v>
+        <v>0.3152</v>
       </c>
       <c r="J100" t="n">
-        <v>4.7312</v>
+        <v>5.0432</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.11</v>
+        <v>0.1308</v>
       </c>
       <c r="J101" t="n">
-        <v>1.76</v>
+        <v>2.0928</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.41</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7587</v>
+        <v>0.8379</v>
       </c>
       <c r="J102" t="n">
-        <v>17.4501</v>
+        <v>19.2717</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6921</v>
+        <v>0.7655</v>
       </c>
       <c r="J103" t="n">
-        <v>15.9183</v>
+        <v>17.6065</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.08</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2529</v>
+        <v>0.2623</v>
       </c>
       <c r="J104" t="n">
-        <v>5.8167</v>
+        <v>6.0329</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.1827</v>
+        <v>-2.0102</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.1827</v>
+        <v>-2.0102</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3614</v>
+        <v>0.3721</v>
       </c>
       <c r="J107" t="n">
-        <v>8.312200000000001</v>
+        <v>8.558299999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1024</v>
+        <v>-0.1166</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.3552</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1863</v>
+        <v>-0.2026</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.2849</v>
+        <v>-4.6598</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2066</v>
+        <v>-0.2229</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.7518</v>
+        <v>-5.1267</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.1203</v>
+        <v>-6.4768</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7094</v>
+        <v>0.7863</v>
       </c>
       <c r="J112" t="n">
-        <v>17.0256</v>
+        <v>18.8712</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6431</v>
+        <v>0.7138</v>
       </c>
       <c r="J113" t="n">
-        <v>15.4344</v>
+        <v>17.1312</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6297</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>15.1128</v>
+        <v>16.7784</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3779</v>
+        <v>0.4078</v>
       </c>
       <c r="J115" t="n">
-        <v>9.069599999999999</v>
+        <v>9.7872</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.89</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4352</v>
+        <v>-0.4086</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.4448</v>
+        <v>-9.8064</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3409</v>
+        <v>0.3358</v>
       </c>
       <c r="J117" t="n">
-        <v>8.1816</v>
+        <v>8.059200000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0428</v>
+        <v>0.031</v>
       </c>
       <c r="J118" t="n">
-        <v>1.0272</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.277</v>
+        <v>-0.294</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.648</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2962</v>
+        <v>-0.3128</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1088</v>
+        <v>-7.5072</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4188</v>
+        <v>-0.4305</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.0512</v>
+        <v>-10.332</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.171</v>
+        <v>1.2884</v>
       </c>
       <c r="J122" t="n">
-        <v>21.078</v>
+        <v>23.1912</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9008</v>
+        <v>1.0006</v>
       </c>
       <c r="J123" t="n">
-        <v>16.2144</v>
+        <v>18.0108</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6717</v>
+        <v>0.7508</v>
       </c>
       <c r="J124" t="n">
-        <v>12.0906</v>
+        <v>13.5144</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.28</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5544</v>
+        <v>0.6211</v>
       </c>
       <c r="J125" t="n">
-        <v>9.979200000000001</v>
+        <v>11.1798</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.06</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1352</v>
+        <v>0.1655</v>
       </c>
       <c r="J126" t="n">
-        <v>2.4336</v>
+        <v>2.979</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3644</v>
+        <v>0.3637</v>
       </c>
       <c r="J127" t="n">
-        <v>6.5592</v>
+        <v>6.5466</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.84</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1711</v>
+        <v>-0.1909</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.0798</v>
+        <v>-3.4362</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3245</v>
+        <v>-0.342</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.841</v>
+        <v>-6.156</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3903</v>
+        <v>-0.4051</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.0254</v>
+        <v>-7.2918</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4184</v>
+        <v>-0.4317</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.5312</v>
+        <v>-7.7706</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1.8338</v>
+        <v>1.8807</v>
       </c>
       <c r="J132" t="n">
-        <v>27.507</v>
+        <v>28.2105</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>2.08</v>
       </c>
       <c r="I133" t="n">
-        <v>1.7352</v>
+        <v>1.746</v>
       </c>
       <c r="J133" t="n">
-        <v>26.028</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>1.039</v>
+        <v>0.9998</v>
       </c>
       <c r="J134" t="n">
-        <v>15.585</v>
+        <v>14.997</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7673</v>
+        <v>0.7436</v>
       </c>
       <c r="J135" t="n">
-        <v>11.5095</v>
+        <v>11.154</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7461</v>
+        <v>-0.6756</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.1915</v>
+        <v>-10.134</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.91</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0618</v>
+        <v>-0.0878</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.927</v>
+        <v>-1.317</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.89</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0867</v>
+        <v>-0.1127</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.3005</v>
+        <v>-1.6905</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4381</v>
+        <v>-0.4532</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.5715</v>
+        <v>-6.798</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4851</v>
+        <v>-0.4973</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.2765</v>
+        <v>-7.4595</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5133</v>
+        <v>-0.5236</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.6995</v>
+        <v>-7.854</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7039</v>
+        <v>0.6711</v>
       </c>
       <c r="J142" t="n">
-        <v>11.9663</v>
+        <v>11.4087</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0336</v>
+        <v>-0.0456</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.5712</v>
+        <v>-0.7752</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1818</v>
+        <v>-0.1991</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.0906</v>
+        <v>-3.3847</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3657</v>
+        <v>-0.3793</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.2169</v>
+        <v>-6.4481</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.39</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6039</v>
+        <v>-0.6042</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.2663</v>
+        <v>-10.2714</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9062</v>
+        <v>0.8924</v>
       </c>
       <c r="J147" t="n">
-        <v>15.4054</v>
+        <v>15.1708</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.72</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8169</v>
+        <v>0.8101</v>
       </c>
       <c r="J148" t="n">
-        <v>13.8873</v>
+        <v>13.7717</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2993</v>
+        <v>0.3206</v>
       </c>
       <c r="J149" t="n">
-        <v>5.0881</v>
+        <v>5.4502</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2872</v>
+        <v>0.3088</v>
       </c>
       <c r="J150" t="n">
-        <v>4.8824</v>
+        <v>5.2496</v>
       </c>
     </row>
     <row r="151">
@@ -8429,10 +8429,10 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5501</v>
+        <v>1.5482</v>
       </c>
       <c r="J152" t="n">
-        <v>29.4519</v>
+        <v>29.4158</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.7</v>
       </c>
       <c r="I153" t="n">
-        <v>1.3325</v>
+        <v>1.3182</v>
       </c>
       <c r="J153" t="n">
-        <v>25.3175</v>
+        <v>25.0458</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.3</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7453</v>
+        <v>0.7199</v>
       </c>
       <c r="J154" t="n">
-        <v>14.1607</v>
+        <v>13.6781</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6764</v>
+        <v>0.659</v>
       </c>
       <c r="J155" t="n">
-        <v>12.8516</v>
+        <v>12.521</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.11</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2734</v>
+        <v>0.2962</v>
       </c>
       <c r="J156" t="n">
-        <v>5.1946</v>
+        <v>5.6278</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.83</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1695</v>
+        <v>-0.192</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.2205</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.82</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1803</v>
+        <v>-0.2026</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.4257</v>
+        <v>-3.8494</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3251</v>
+        <v>-0.3443</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.1769</v>
+        <v>-6.5417</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3436</v>
+        <v>-0.3621</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.5284</v>
+        <v>-6.8799</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4276</v>
+        <v>-0.442</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.1244</v>
+        <v>-8.398</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9428</v>
+        <v>0.8867</v>
       </c>
       <c r="J162" t="n">
-        <v>18.856</v>
+        <v>17.734</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.36</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.8673</v>
       </c>
       <c r="J163" t="n">
-        <v>18.438</v>
+        <v>17.346</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.25</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6725</v>
+        <v>0.647</v>
       </c>
       <c r="J164" t="n">
-        <v>13.45</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5806</v>
+        <v>0.5644</v>
       </c>
       <c r="J165" t="n">
-        <v>11.612</v>
+        <v>11.288</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3199</v>
+        <v>-0.3013</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.398</v>
+        <v>-6.026</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.19</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4604</v>
+        <v>0.446</v>
       </c>
       <c r="J167" t="n">
-        <v>9.208</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0397</v>
+        <v>-0.0503</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.794</v>
+        <v>-1.006</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.124</v>
+        <v>-0.1391</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.48</v>
+        <v>-2.782</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.74</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.285</v>
+        <v>-0.3002</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.7</v>
+        <v>-6.004</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3519</v>
+        <v>-0.3651</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.038</v>
+        <v>-7.302</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2937</v>
+        <v>1.2622</v>
       </c>
       <c r="J172" t="n">
-        <v>31.0488</v>
+        <v>30.2928</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6026</v>
+        <v>0.5794</v>
       </c>
       <c r="J173" t="n">
-        <v>14.4624</v>
+        <v>13.9056</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4254</v>
+        <v>0.4196</v>
       </c>
       <c r="J174" t="n">
-        <v>10.2096</v>
+        <v>10.0704</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5221</v>
+        <v>-0.4924</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.5304</v>
+        <v>-11.8176</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6804</v>
+        <v>-0.6338</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.3296</v>
+        <v>-15.2112</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3455</v>
+        <v>0.3466</v>
       </c>
       <c r="J177" t="n">
-        <v>8.292</v>
+        <v>8.3184</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.038</v>
+        <v>0.0435</v>
       </c>
       <c r="J178" t="n">
-        <v>0.912</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="179">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.063</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.512</v>
+        <v>-1.7376</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1666</v>
+        <v>-0.18</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.9984</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3042</v>
+        <v>0.2901</v>
       </c>
       <c r="J182" t="n">
-        <v>5.7798</v>
+        <v>5.5119</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.79</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2242</v>
+        <v>-0.2431</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.2598</v>
+        <v>-4.6189</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2242</v>
+        <v>-0.2431</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.2598</v>
+        <v>-4.6189</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3094</v>
+        <v>-0.3267</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.8786</v>
+        <v>-6.2073</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4129</v>
+        <v>-0.4259</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.8451</v>
+        <v>-8.0921</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2234</v>
+        <v>1.1977</v>
       </c>
       <c r="J187" t="n">
-        <v>23.2446</v>
+        <v>22.7563</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.51</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1257</v>
+        <v>1.0928</v>
       </c>
       <c r="J188" t="n">
-        <v>21.3883</v>
+        <v>20.7632</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8539</v>
+        <v>0.8117</v>
       </c>
       <c r="J189" t="n">
-        <v>16.2241</v>
+        <v>15.4223</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5579</v>
+        <v>0.5488</v>
       </c>
       <c r="J190" t="n">
-        <v>10.6001</v>
+        <v>10.4272</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.04</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0864</v>
+        <v>0.1149</v>
       </c>
       <c r="J191" t="n">
-        <v>1.6416</v>
+        <v>2.1831</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9193</v>
+        <v>0.9041</v>
       </c>
       <c r="J192" t="n">
-        <v>16.5474</v>
+        <v>16.2738</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6573</v>
+        <v>0.6616</v>
       </c>
       <c r="J193" t="n">
-        <v>11.8314</v>
+        <v>11.9088</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.37</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4591</v>
+        <v>0.4743</v>
       </c>
       <c r="J194" t="n">
-        <v>8.2638</v>
+        <v>8.5374</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0723</v>
+        <v>0.0941</v>
       </c>
       <c r="J195" t="n">
-        <v>1.3014</v>
+        <v>1.6938</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0563</v>
+        <v>0.0775</v>
       </c>
       <c r="J196" t="n">
-        <v>1.0134</v>
+        <v>1.395</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5488</v>
+        <v>0.5282</v>
       </c>
       <c r="J197" t="n">
-        <v>9.878399999999999</v>
+        <v>9.5076</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1283</v>
+        <v>-0.1453</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.3094</v>
+        <v>-2.6154</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2191</v>
+        <v>-0.2369</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.9438</v>
+        <v>-4.2642</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.258</v>
+        <v>-0.2753</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.644</v>
+        <v>-4.9554</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.42</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5748</v>
+        <v>-0.5774</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.3464</v>
+        <v>-10.3932</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7486</v>
+        <v>0.7224</v>
       </c>
       <c r="J202" t="n">
-        <v>17.9664</v>
+        <v>17.3376</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.23</v>
       </c>
       <c r="I203" t="n">
-        <v>0.464</v>
+        <v>0.4628</v>
       </c>
       <c r="J203" t="n">
-        <v>11.136</v>
+        <v>11.1072</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2844</v>
+        <v>0.2938</v>
       </c>
       <c r="J204" t="n">
-        <v>6.8256</v>
+        <v>7.0512</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.93</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1109</v>
+        <v>-0.1199</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.6616</v>
+        <v>-2.8776</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2301</v>
+        <v>-0.2412</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.5224</v>
+        <v>-5.7888</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.43</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1053</v>
+        <v>1.054</v>
       </c>
       <c r="J207" t="n">
-        <v>26.5272</v>
+        <v>25.296</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4565</v>
+        <v>0.4411</v>
       </c>
       <c r="J208" t="n">
-        <v>10.956</v>
+        <v>10.5864</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0018</v>
+        <v>-0.0012</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.0432</v>
+        <v>-0.0288</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.9</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3523</v>
+        <v>-0.3444</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.4552</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.1423</v>
+        <v>-1.04</v>
       </c>
       <c r="J211" t="n">
-        <v>-27.4152</v>
+        <v>-24.96</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3612</v>
+        <v>0.3505</v>
       </c>
       <c r="J212" t="n">
-        <v>6.1404</v>
+        <v>5.9585</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0216</v>
+        <v>-0.0362</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.3672</v>
+        <v>-0.6153999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3289</v>
+        <v>-0.3454</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.5913</v>
+        <v>-5.8718</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3384</v>
+        <v>-0.3545</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.7528</v>
+        <v>-6.0265</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5061</v>
+        <v>-0.5138</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.6037</v>
+        <v>-8.7346</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0125</v>
+        <v>0.9954</v>
       </c>
       <c r="J217" t="n">
-        <v>17.2125</v>
+        <v>16.9218</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5536</v>
+        <v>0.5623</v>
       </c>
       <c r="J218" t="n">
-        <v>9.411199999999999</v>
+        <v>9.559100000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2612</v>
+        <v>0.281</v>
       </c>
       <c r="J219" t="n">
-        <v>4.4404</v>
+        <v>4.777</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.236</v>
+        <v>0.2561</v>
       </c>
       <c r="J220" t="n">
-        <v>4.012</v>
+        <v>4.3537</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3442</v>
+        <v>-0.3504</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.8514</v>
+        <v>-5.9568</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4577</v>
+        <v>1.4491</v>
       </c>
       <c r="J222" t="n">
-        <v>27.6963</v>
+        <v>27.5329</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1394</v>
+        <v>1.1099</v>
       </c>
       <c r="J223" t="n">
-        <v>21.6486</v>
+        <v>21.0881</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.32</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7996</v>
+        <v>0.766</v>
       </c>
       <c r="J224" t="n">
-        <v>15.1924</v>
+        <v>14.554</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5188</v>
+        <v>0.5167</v>
       </c>
       <c r="J225" t="n">
-        <v>9.857200000000001</v>
+        <v>9.817299999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4687</v>
+        <v>0.4718</v>
       </c>
       <c r="J226" t="n">
-        <v>8.9053</v>
+        <v>8.9642</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4665</v>
+        <v>0.4396</v>
       </c>
       <c r="J227" t="n">
-        <v>8.8635</v>
+        <v>8.352399999999999</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0437</v>
+        <v>-0.0612</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.8303</v>
+        <v>-1.1628</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2319</v>
+        <v>-0.2512</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.4061</v>
+        <v>-4.7728</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.54</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4565</v>
+        <v>-0.4677</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.673500000000001</v>
+        <v>-8.8863</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5581</v>
+        <v>-0.5629</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.6039</v>
+        <v>-10.6951</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7935</v>
+        <v>0.7487</v>
       </c>
       <c r="J232" t="n">
-        <v>19.044</v>
+        <v>17.9688</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J233" t="n">
-        <v>13.812</v>
+        <v>13.3368</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4496</v>
+        <v>0.442</v>
       </c>
       <c r="J234" t="n">
-        <v>10.7904</v>
+        <v>10.608</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.13</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3983</v>
+        <v>0.395</v>
       </c>
       <c r="J235" t="n">
-        <v>9.559200000000001</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.497</v>
+        <v>-0.4693</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.928</v>
+        <v>-11.2632</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.22</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4868</v>
       </c>
       <c r="J237" t="n">
-        <v>12.036</v>
+        <v>11.6832</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2875</v>
+        <v>0.2871</v>
       </c>
       <c r="J238" t="n">
-        <v>6.9</v>
+        <v>6.8904</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1798</v>
+        <v>-0.1951</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.3152</v>
+        <v>-4.6824</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2896</v>
+        <v>-0.3038</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.9504</v>
+        <v>-7.2912</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2992</v>
+        <v>-0.3133</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.1808</v>
+        <v>-7.5192</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.43</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5501</v>
       </c>
       <c r="J242" t="n">
-        <v>10.856</v>
+        <v>11.002</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3964</v>
+        <v>0.4111</v>
       </c>
       <c r="J243" t="n">
-        <v>7.928</v>
+        <v>8.222</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2682</v>
+        <v>0.2862</v>
       </c>
       <c r="J244" t="n">
-        <v>5.364</v>
+        <v>5.724</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.17</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2433</v>
+        <v>0.2617</v>
       </c>
       <c r="J245" t="n">
-        <v>4.866</v>
+        <v>5.234</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.01</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0007</v>
+        <v>0.0125</v>
       </c>
       <c r="J246" t="n">
-        <v>0.014</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.48</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7105</v>
+        <v>0.6857</v>
       </c>
       <c r="J247" t="n">
-        <v>14.21</v>
+        <v>13.714</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
       <c r="J248" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0348</v>
+        <v>-0.0418</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.696</v>
+        <v>-0.836</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1756</v>
+        <v>-0.1895</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.512</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4276</v>
+        <v>-0.4359</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.552</v>
+        <v>-8.718</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.61</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1012</v>
+        <v>1.0638</v>
       </c>
       <c r="J252" t="n">
-        <v>23.1252</v>
+        <v>22.3398</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0825</v>
+        <v>-0.0948</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.7325</v>
+        <v>-1.9908</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1272</v>
+        <v>-0.1415</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.6712</v>
+        <v>-2.9715</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2311</v>
+        <v>-0.2462</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.8531</v>
+        <v>-5.1702</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.42</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5844</v>
+        <v>-0.5851</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.2724</v>
+        <v>-12.2871</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.62</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2792</v>
+        <v>1.2538</v>
       </c>
       <c r="J257" t="n">
-        <v>26.8632</v>
+        <v>26.3298</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.6</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2545</v>
+        <v>1.2275</v>
       </c>
       <c r="J258" t="n">
-        <v>26.3445</v>
+        <v>25.7775</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.527</v>
+        <v>0.5174</v>
       </c>
       <c r="J259" t="n">
-        <v>11.067</v>
+        <v>10.8654</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3183</v>
+        <v>0.3276</v>
       </c>
       <c r="J260" t="n">
-        <v>6.6843</v>
+        <v>6.8796</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8381</v>
+        <v>-0.7673</v>
       </c>
       <c r="J261" t="n">
-        <v>-17.6001</v>
+        <v>-16.1133</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0918</v>
+        <v>1.0595</v>
       </c>
       <c r="J262" t="n">
-        <v>38.213</v>
+        <v>37.0825</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.523</v>
       </c>
       <c r="J263" t="n">
-        <v>18.648</v>
+        <v>18.305</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1162</v>
+        <v>-0.1271</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.067</v>
+        <v>-4.4485</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.73</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3123</v>
+        <v>-0.3235</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.9305</v>
+        <v>-11.3225</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3783</v>
+        <v>-0.3875</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.2405</v>
+        <v>-13.5625</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>2.04</v>
       </c>
       <c r="I267" t="n">
-        <v>1.802</v>
+        <v>1.7989</v>
       </c>
       <c r="J267" t="n">
-        <v>63.07</v>
+        <v>62.9615</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5363</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>18.7705</v>
+        <v>18.3295</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3843</v>
+        <v>0.3855</v>
       </c>
       <c r="J269" t="n">
-        <v>13.4505</v>
+        <v>13.4925</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.83</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5972</v>
+        <v>-0.5557</v>
       </c>
       <c r="J270" t="n">
-        <v>-20.902</v>
+        <v>-19.4495</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.5793</v>
       </c>
       <c r="J271" t="n">
-        <v>-21.8225</v>
+        <v>-20.2755</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0479</v>
+        <v>0.9953</v>
       </c>
       <c r="J272" t="n">
-        <v>35.6286</v>
+        <v>33.8402</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6171</v>
+        <v>0.5944</v>
       </c>
       <c r="J273" t="n">
-        <v>20.9814</v>
+        <v>20.2096</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4699</v>
+        <v>0.4617</v>
       </c>
       <c r="J274" t="n">
-        <v>15.9766</v>
+        <v>15.6978</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.15</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4454</v>
+        <v>0.4392</v>
       </c>
       <c r="J275" t="n">
-        <v>15.1436</v>
+        <v>14.9328</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6117</v>
+        <v>-0.5709</v>
       </c>
       <c r="J276" t="n">
-        <v>-20.7978</v>
+        <v>-19.4106</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8753</v>
+        <v>0.8262</v>
       </c>
       <c r="J277" t="n">
-        <v>29.7602</v>
+        <v>28.0908</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1252</v>
+        <v>0.1312</v>
       </c>
       <c r="J278" t="n">
-        <v>4.2568</v>
+        <v>4.4608</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0958</v>
+        <v>-0.1083</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.2572</v>
+        <v>-3.6822</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.7</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3314</v>
+        <v>-0.3439</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.2676</v>
+        <v>-11.6926</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3503</v>
+        <v>-0.3622</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.9102</v>
+        <v>-12.3148</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.37</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9669</v>
+        <v>0.9056</v>
       </c>
       <c r="J282" t="n">
-        <v>23.2056</v>
+        <v>21.7344</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9253</v>
+        <v>0.8659</v>
       </c>
       <c r="J283" t="n">
-        <v>22.2072</v>
+        <v>20.7816</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7867</v>
+        <v>0.7439</v>
       </c>
       <c r="J284" t="n">
-        <v>18.8808</v>
+        <v>17.8536</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3896</v>
+        <v>-0.3704</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.3504</v>
+        <v>-8.8896</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6096</v>
+        <v>-0.5695</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.6304</v>
+        <v>-13.668</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3263</v>
+        <v>0.3284</v>
       </c>
       <c r="J287" t="n">
-        <v>7.8312</v>
+        <v>7.8816</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3068</v>
+        <v>0.31</v>
       </c>
       <c r="J288" t="n">
-        <v>7.3632</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0204</v>
+        <v>-0.0251</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.4896</v>
+        <v>-0.6024</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1114</v>
+        <v>-0.1235</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.6736</v>
+        <v>-2.964</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2287</v>
+        <v>-0.2423</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.4888</v>
+        <v>-5.8152</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1917</v>
+        <v>1.1558</v>
       </c>
       <c r="J292" t="n">
-        <v>28.6008</v>
+        <v>27.7392</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.25</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6887</v>
+        <v>0.6581</v>
       </c>
       <c r="J293" t="n">
-        <v>16.5288</v>
+        <v>15.7944</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5189</v>
+        <v>0.5063</v>
       </c>
       <c r="J294" t="n">
-        <v>12.4536</v>
+        <v>12.1512</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.2152</v>
+        <v>-2.0544</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5857</v>
+        <v>-0.5477</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.0568</v>
+        <v>-13.1448</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.39</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7442</v>
       </c>
       <c r="J297" t="n">
-        <v>18.7632</v>
+        <v>17.8608</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0191</v>
+        <v>-0.0241</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.4584</v>
+        <v>-0.5784</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.98</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0344</v>
+        <v>-0.0416</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.8256</v>
+        <v>-0.9984</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1096</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.3424</v>
+        <v>-2.6304</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4359</v>
+        <v>-0.444</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.4616</v>
+        <v>-10.656</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.75</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4239</v>
+        <v>1.4093</v>
       </c>
       <c r="J302" t="n">
-        <v>28.478</v>
+        <v>28.186</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.56</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1939</v>
+        <v>1.1648</v>
       </c>
       <c r="J303" t="n">
-        <v>23.878</v>
+        <v>23.296</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7511</v>
+        <v>0.7195</v>
       </c>
       <c r="J304" t="n">
-        <v>15.022</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.23</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6136</v>
+        <v>0.5971</v>
       </c>
       <c r="J305" t="n">
-        <v>12.272</v>
+        <v>11.942</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9933</v>
+        <v>-0.9014</v>
       </c>
       <c r="J306" t="n">
-        <v>-19.866</v>
+        <v>-18.028</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.78</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2726</v>
+        <v>1.2498</v>
       </c>
       <c r="J307" t="n">
-        <v>25.452</v>
+        <v>24.996</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1779</v>
+        <v>-0.1937</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.558</v>
+        <v>-3.874</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.74</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2876</v>
+        <v>-0.3023</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.752</v>
+        <v>-6.046</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3825</v>
+        <v>-0.3941</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.65</v>
+        <v>-7.882</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4564</v>
+        <v>-0.4647</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.128</v>
+        <v>-9.294</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.18</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3309</v>
+        <v>0.3304</v>
       </c>
       <c r="J312" t="n">
-        <v>7.6107</v>
+        <v>7.5992</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0558</v>
+        <v>-0.0669</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.2834</v>
+        <v>-1.5387</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0805</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.5778</v>
+        <v>-1.8515</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1984</v>
+        <v>-0.2142</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.5632</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3732</v>
+        <v>-0.3852</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.583600000000001</v>
+        <v>-8.8596</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4081</v>
+        <v>0.4199</v>
       </c>
       <c r="J317" t="n">
-        <v>9.3863</v>
+        <v>9.6577</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.25</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3484</v>
+        <v>0.3626</v>
       </c>
       <c r="J318" t="n">
-        <v>8.013199999999999</v>
+        <v>8.3398</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3242</v>
+        <v>0.3392</v>
       </c>
       <c r="J319" t="n">
-        <v>7.4566</v>
+        <v>7.8016</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0672</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>1.5456</v>
+        <v>1.8653</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1606</v>
+        <v>-0.1702</v>
       </c>
       <c r="J321" t="n">
-        <v>-3.6938</v>
+        <v>-3.9146</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.75</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3884</v>
+        <v>1.3779</v>
       </c>
       <c r="J322" t="n">
-        <v>23.6028</v>
+        <v>23.4243</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1439</v>
+        <v>1.1163</v>
       </c>
       <c r="J323" t="n">
-        <v>19.4463</v>
+        <v>18.9771</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.4</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9581</v>
+        <v>0.9103</v>
       </c>
       <c r="J324" t="n">
-        <v>16.2877</v>
+        <v>15.4751</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.39</v>
       </c>
       <c r="I325" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.892</v>
       </c>
       <c r="J325" t="n">
-        <v>15.963</v>
+        <v>15.164</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.6037</v>
+        <v>0.5949</v>
       </c>
       <c r="J326" t="n">
-        <v>10.2629</v>
+        <v>10.1133</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.04</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2412</v>
+        <v>0.2164</v>
       </c>
       <c r="J327" t="n">
-        <v>4.1004</v>
+        <v>3.6788</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.82</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1784</v>
+        <v>-0.2012</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.0328</v>
+        <v>-3.4204</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.7</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2973</v>
+        <v>-0.3174</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.0541</v>
+        <v>-5.3958</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.63</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3609</v>
+        <v>-0.3789</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.1353</v>
+        <v>-6.4413</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.3</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.669</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.373</v>
+        <v>-11.3356</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.56</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2136</v>
+        <v>1.1822</v>
       </c>
       <c r="J332" t="n">
-        <v>25.4856</v>
+        <v>24.8262</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1504</v>
+        <v>1.1145</v>
       </c>
       <c r="J333" t="n">
-        <v>24.1584</v>
+        <v>23.4045</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.28</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7096</v>
       </c>
       <c r="J334" t="n">
-        <v>15.6114</v>
+        <v>14.9016</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.9</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.4074</v>
+        <v>-0.3829</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.555400000000001</v>
+        <v>-8.040900000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6005</v>
+        <v>-0.5581</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.6105</v>
+        <v>-11.7201</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4995</v>
+        <v>0.4819</v>
       </c>
       <c r="J337" t="n">
-        <v>10.4895</v>
+        <v>10.1199</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.053</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.113</v>
+        <v>-1.3587</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1445</v>
+        <v>-0.1604</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.0345</v>
+        <v>-3.3684</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2059</v>
+        <v>-0.2223</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.3239</v>
+        <v>-4.6683</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.59</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4263</v>
+        <v>-0.4364</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.952299999999999</v>
+        <v>-9.164400000000001</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.7</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3524</v>
+        <v>1.3357</v>
       </c>
       <c r="J342" t="n">
-        <v>21.6384</v>
+        <v>21.3712</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.51</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1234</v>
+        <v>1.0908</v>
       </c>
       <c r="J343" t="n">
-        <v>17.9744</v>
+        <v>17.4528</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.22</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5792</v>
+        <v>0.5685</v>
       </c>
       <c r="J344" t="n">
-        <v>9.267200000000001</v>
+        <v>9.096</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5056</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J345" t="n">
-        <v>8.089600000000001</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.14</v>
       </c>
       <c r="I346" t="n">
-        <v>0.3769</v>
+        <v>0.3862</v>
       </c>
       <c r="J346" t="n">
-        <v>6.0304</v>
+        <v>6.1792</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.1783</v>
+        <v>-0.2033</v>
       </c>
       <c r="J347" t="n">
-        <v>-2.8528</v>
+        <v>-3.2528</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1892</v>
+        <v>-0.2139</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.0272</v>
+        <v>-3.4224</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.7</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2914</v>
+        <v>-0.3129</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.6624</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.67</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3194</v>
+        <v>-0.3399</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.1104</v>
+        <v>-5.4384</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.3</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6639</v>
+        <v>-0.6627</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.6224</v>
+        <v>-10.6032</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.5</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1089</v>
+        <v>1.0756</v>
       </c>
       <c r="J352" t="n">
-        <v>19.9602</v>
+        <v>19.3608</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.47</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0722</v>
+        <v>1.0338</v>
       </c>
       <c r="J353" t="n">
-        <v>19.2996</v>
+        <v>18.6084</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.41</v>
       </c>
       <c r="I354" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9372</v>
       </c>
       <c r="J354" t="n">
-        <v>17.7732</v>
+        <v>16.8696</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.36</v>
       </c>
       <c r="I355" t="n">
-        <v>0.8927</v>
+        <v>0.8468</v>
       </c>
       <c r="J355" t="n">
-        <v>16.0686</v>
+        <v>15.2424</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.09</v>
       </c>
       <c r="I356" t="n">
-        <v>0.2354</v>
+        <v>0.2569</v>
       </c>
       <c r="J356" t="n">
-        <v>4.2372</v>
+        <v>4.6242</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.25</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6291</v>
+        <v>0.591</v>
       </c>
       <c r="J357" t="n">
-        <v>11.3238</v>
+        <v>10.638</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.82</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1963</v>
+        <v>-0.215</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.5334</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.75</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2626</v>
+        <v>-0.281</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.7268</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.61</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3951</v>
+        <v>-0.4088</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.1118</v>
+        <v>-7.3584</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4417</v>
+        <v>-0.453</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.9506</v>
+        <v>-8.154</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.27</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7552</v>
+        <v>0.7133</v>
       </c>
       <c r="J362" t="n">
-        <v>17.3696</v>
+        <v>16.4059</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.26</v>
       </c>
       <c r="I363" t="n">
-        <v>0.731</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J363" t="n">
-        <v>16.813</v>
+        <v>15.916</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.08</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2675</v>
+        <v>0.2723</v>
       </c>
       <c r="J364" t="n">
-        <v>6.1525</v>
+        <v>6.2629</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.08</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2675</v>
+        <v>0.2723</v>
       </c>
       <c r="J365" t="n">
-        <v>6.1525</v>
+        <v>6.2629</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6237</v>
+        <v>-0.5844</v>
       </c>
       <c r="J366" t="n">
-        <v>-14.3451</v>
+        <v>-13.4412</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.25</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5491</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="J367" t="n">
-        <v>12.6293</v>
+        <v>12.2314</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.03</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1029</v>
+        <v>0.108</v>
       </c>
       <c r="J368" t="n">
-        <v>2.3667</v>
+        <v>2.484</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0474</v>
+        <v>0.0503</v>
       </c>
       <c r="J369" t="n">
-        <v>1.0902</v>
+        <v>1.1569</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2428</v>
+        <v>-0.2574</v>
       </c>
       <c r="J370" t="n">
-        <v>-5.5844</v>
+        <v>-5.9202</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.66</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3679</v>
+        <v>-0.3794</v>
       </c>
       <c r="J371" t="n">
-        <v>-8.4617</v>
+        <v>-8.7262</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.8635</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J372" t="n">
-        <v>18.997</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>0.8165</v>
+        <v>0.7689</v>
       </c>
       <c r="J373" t="n">
-        <v>17.963</v>
+        <v>16.9158</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.17</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4999</v>
+        <v>0.4878</v>
       </c>
       <c r="J374" t="n">
-        <v>10.9978</v>
+        <v>10.7316</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.98</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1261</v>
+        <v>-0.1219</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.7742</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.87</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4699</v>
+        <v>-0.4447</v>
       </c>
       <c r="J376" t="n">
-        <v>-10.3378</v>
+        <v>-9.7834</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.24</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5671</v>
+        <v>0.5419</v>
       </c>
       <c r="J377" t="n">
-        <v>12.4762</v>
+        <v>11.9218</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I378" t="n">
-        <v>0.2001</v>
+        <v>0.1981</v>
       </c>
       <c r="J378" t="n">
-        <v>4.4022</v>
+        <v>4.3582</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2132</v>
+        <v>-0.2302</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.6904</v>
+        <v>-5.0644</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.74</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2818</v>
+        <v>-0.2978</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.1996</v>
+        <v>-6.5516</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5061</v>
+        <v>-0.5124</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.1342</v>
+        <v>-11.2728</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0567</v>
+        <v>7.1985</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5533</v>
+        <v>1.5845</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5882</v>
+        <v>2.6016</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0567</v>
+        <v>7.1985</v>
       </c>
       <c r="F2" t="n">
         <v>2.5741</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4826</v>
+        <v>4.4832</v>
       </c>
       <c r="H2" t="n">
         <v>3.5986</v>
@@ -520,7 +520,7 @@
         <v>1.9432</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4826</v>
+        <v>4.4832</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4258</v>
+        <v>6.4264</v>
       </c>
       <c r="N2" t="n">
         <v>239</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1756</v>
+        <v>6.2157</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3593</v>
+        <v>1.3682</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1871</v>
+        <v>2.1626</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1756</v>
+        <v>6.2157</v>
       </c>
       <c r="F3" t="n">
         <v>3.1058</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0698</v>
+        <v>3.0708</v>
       </c>
       <c r="H3" t="n">
         <v>5.353</v>
@@ -566,7 +566,7 @@
         <v>2.8906</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0698</v>
+        <v>3.0708</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9604</v>
+        <v>5.9614</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7179</v>
+        <v>5.982</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2586</v>
+        <v>1.3167</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9787</v>
+        <v>2.0582</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7179</v>
+        <v>5.982</v>
       </c>
       <c r="F4" t="n">
         <v>2.4066</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3113</v>
+        <v>3.2836</v>
       </c>
       <c r="H4" t="n">
         <v>3.046</v>
@@ -612,7 +612,7 @@
         <v>1.6448</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3113</v>
+        <v>3.2836</v>
       </c>
       <c r="K4" t="n">
         <v>103</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9561</v>
+        <v>4.9284</v>
       </c>
       <c r="N4" t="n">
         <v>239</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3033</v>
+        <v>5.2727</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1673</v>
+        <v>1.1606</v>
       </c>
       <c r="D5" t="n">
-        <v>1.79</v>
+        <v>1.7414</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3033</v>
+        <v>5.2727</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0247</v>
+        <v>3.0248</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2786</v>
+        <v>2.2684</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0854</v>
+        <v>5.0858</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7461</v>
+        <v>2.7463</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2786</v>
+        <v>2.2684</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0247</v>
+        <v>5.0147</v>
       </c>
       <c r="N5" t="n">
         <v>276</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0359</v>
+        <v>5.239</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1085</v>
+        <v>1.1532</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6682</v>
+        <v>1.7263</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0359</v>
+        <v>5.239</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1154</v>
+        <v>3.1156</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9205</v>
+        <v>1.9433</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3847</v>
+        <v>5.3853</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9077</v>
+        <v>2.908</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9205</v>
+        <v>1.9433</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.828200000000001</v>
+        <v>4.8513</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3149</v>
+        <v>4.5798</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9498</v>
+        <v>1.0081</v>
       </c>
       <c r="D7" t="n">
-        <v>1.34</v>
+        <v>1.4319</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3149</v>
+        <v>4.5798</v>
       </c>
       <c r="F7" t="n">
         <v>4.1657</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9447</v>
+        <v>4.0592</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8683</v>
+        <v>0.8935</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1715</v>
+        <v>1.1993</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9447</v>
+        <v>4.0592</v>
       </c>
       <c r="F8" t="n">
         <v>4.5807</v>
@@ -790,10 +790,10 @@
         <v>-0.636</v>
       </c>
       <c r="H8" t="n">
-        <v>13.3056</v>
+        <v>13.3313</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1849</v>
+        <v>7.1988</v>
       </c>
       <c r="J8" t="n">
         <v>-0.636</v>
@@ -805,7 +805,7 @@
         <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>6.5489</v>
+        <v>6.5628</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8362</v>
+        <v>4.0054</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8444</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1221</v>
+        <v>1.1753</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8362</v>
+        <v>4.0054</v>
       </c>
       <c r="F9" t="n">
         <v>4.5807</v>
@@ -836,10 +836,10 @@
         <v>-0.7445000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>10.3083</v>
+        <v>10.29</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5664</v>
+        <v>5.5565</v>
       </c>
       <c r="J9" t="n">
         <v>-0.7445000000000001</v>
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>4.821899999999999</v>
+        <v>4.811999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>280</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7339</v>
+        <v>3.7632</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8219</v>
+        <v>0.8283</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0755</v>
+        <v>1.0671</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7339</v>
+        <v>3.7632</v>
       </c>
       <c r="F10" t="n">
-        <v>3.108</v>
+        <v>3.1009</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6259</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3603</v>
+        <v>5.3369</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8945</v>
+        <v>2.8819</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6259</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5204</v>
+        <v>3.5074</v>
       </c>
       <c r="N10" t="n">
         <v>276</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4643</v>
+        <v>3.4993</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7625</v>
+        <v>0.7702</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9528</v>
+        <v>0.9492</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4643</v>
+        <v>3.4993</v>
       </c>
       <c r="F11" t="n">
         <v>2.9453</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4434</v>
+        <v>3.4054</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7579</v>
+        <v>0.7496</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9433</v>
+        <v>0.9073</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4434</v>
+        <v>3.4054</v>
       </c>
       <c r="F12" t="n">
         <v>3.1693</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4237</v>
+        <v>3.3873</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7536</v>
+        <v>0.7456</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9343</v>
+        <v>0.8992</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4237</v>
+        <v>3.3873</v>
       </c>
       <c r="F13" t="n">
         <v>3.5901</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2113</v>
+        <v>3.2049</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7069</v>
+        <v>0.7054</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8376</v>
+        <v>0.8177</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2113</v>
+        <v>3.2049</v>
       </c>
       <c r="F14" t="n">
-        <v>1.495</v>
+        <v>1.4956</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7163</v>
+        <v>1.7162</v>
       </c>
       <c r="H14" t="n">
-        <v>1.495</v>
+        <v>1.4956</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8073</v>
+        <v>0.8076</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7163</v>
+        <v>1.7162</v>
       </c>
       <c r="K14" t="n">
         <v>121</v>
@@ -1081,7 +1081,7 @@
         <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5236</v>
+        <v>2.5238</v>
       </c>
       <c r="N14" t="n">
         <v>276</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8413</v>
+        <v>2.8925</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6254</v>
+        <v>0.6367</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6692</v>
+        <v>0.6782</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8413</v>
+        <v>2.8925</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4466</v>
+        <v>2.4467</v>
       </c>
       <c r="G15" t="n">
         <v>0.3947</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1779</v>
+        <v>3.1783</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7161</v>
+        <v>1.7162</v>
       </c>
       <c r="J15" t="n">
         <v>0.3947</v>
@@ -1127,7 +1127,7 @@
         <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1108</v>
+        <v>2.1109</v>
       </c>
       <c r="N15" t="n">
         <v>280</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Luken</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5883</v>
+        <v>2.7177</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5697</v>
+        <v>0.5982</v>
       </c>
       <c r="D16" t="n">
-        <v>0.554</v>
+        <v>0.6001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5883</v>
+        <v>2.7177</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4693</v>
+        <v>2.3321</v>
       </c>
       <c r="G16" t="n">
-        <v>2.119</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4693</v>
+        <v>2.3793</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2534</v>
+        <v>2.3793</v>
       </c>
       <c r="J16" t="n">
-        <v>2.119</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="L16" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3724</v>
+        <v>2.3793</v>
       </c>
       <c r="N16" t="n">
-        <v>239</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4631</v>
+        <v>2.6482</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5422</v>
+        <v>0.5829</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4971</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4631</v>
+        <v>2.6482</v>
       </c>
       <c r="F17" t="n">
         <v>2.4631</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luken</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3319</v>
+        <v>2.5297</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5133</v>
+        <v>0.5568</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4373</v>
+        <v>0.5161</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3319</v>
+        <v>2.5297</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3319</v>
+        <v>0.4693</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.1197</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3789</v>
+        <v>0.4693</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3789</v>
+        <v>0.2534</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.1197</v>
       </c>
       <c r="K18" t="n">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3789</v>
+        <v>2.3731</v>
       </c>
       <c r="N18" t="n">
-        <v>154</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8298</v>
+        <v>2.2626</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4028</v>
+        <v>0.498</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2088</v>
+        <v>0.3968</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8298</v>
+        <v>2.2626</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8298</v>
+        <v>1.8294</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8298</v>
+        <v>1.8294</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8298</v>
+        <v>1.8294</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8298</v>
+        <v>1.8294</v>
       </c>
       <c r="N19" t="n">
         <v>121</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8033</v>
+        <v>1.6144</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3969</v>
+        <v>0.3554</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1967</v>
+        <v>0.1073</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8033</v>
+        <v>1.6144</v>
       </c>
       <c r="F20" t="n">
         <v>-0.6874</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4907</v>
+        <v>2.4728</v>
       </c>
       <c r="H20" t="n">
         <v>-0.6874</v>
@@ -1348,7 +1348,7 @@
         <v>-0.3712</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4907</v>
+        <v>2.4728</v>
       </c>
       <c r="K20" t="n">
         <v>103</v>
@@ -1357,7 +1357,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1195</v>
+        <v>2.1016</v>
       </c>
       <c r="N20" t="n">
         <v>239</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6623</v>
+        <v>1.5958</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3659</v>
+        <v>0.3513</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1325</v>
+        <v>0.099</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6623</v>
+        <v>1.5958</v>
       </c>
       <c r="F21" t="n">
-        <v>2.758</v>
+        <v>1.3714</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0957</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2054</v>
+        <v>1.3714</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2709</v>
+        <v>1.3714</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0957</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1752</v>
+        <v>1.3714</v>
       </c>
       <c r="N21" t="n">
-        <v>276</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4677</v>
+        <v>1.5815</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3231</v>
+        <v>0.3481</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0439</v>
+        <v>0.0926</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4677</v>
+        <v>1.5815</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4677</v>
+        <v>1.49</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4677</v>
+        <v>1.49</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4677</v>
+        <v>1.49</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4677</v>
+        <v>1.49</v>
       </c>
       <c r="N22" t="n">
         <v>121</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3716</v>
+        <v>1.3688</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3019</v>
+        <v>0.3013</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002</v>
+        <v>-0.0024</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3716</v>
+        <v>1.3688</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3716</v>
+        <v>2.7581</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1.0957</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3716</v>
+        <v>4.2058</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3716</v>
+        <v>2.2711</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1.0957</v>
       </c>
       <c r="K23" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3716</v>
+        <v>1.1754</v>
       </c>
       <c r="N23" t="n">
-        <v>122</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1649</v>
+        <v>1.0915</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2564</v>
+        <v>0.2403</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0939</v>
+        <v>-0.1263</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1649</v>
+        <v>1.0915</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1649</v>
+        <v>1.1651</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1649</v>
+        <v>1.1651</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1649</v>
+        <v>1.1651</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1649</v>
+        <v>1.1651</v>
       </c>
       <c r="N24" t="n">
         <v>154</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>hfah</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6745</v>
+        <v>0.6137</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1485</v>
+        <v>0.1351</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3172</v>
+        <v>-0.3397</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6745</v>
+        <v>0.6137</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5296</v>
+        <v>0.4056</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1449</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5296</v>
+        <v>0.4056</v>
       </c>
       <c r="I25" t="n">
-        <v>0.286</v>
+        <v>0.4056</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1449</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4308999999999999</v>
+        <v>0.4056</v>
       </c>
       <c r="N25" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qlocuu</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5011</v>
+        <v>0.5412</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1103</v>
+        <v>0.1191</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3961</v>
+        <v>-0.3721</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5011</v>
+        <v>0.5412</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5011</v>
+        <v>0.4345</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5011</v>
+        <v>0.4345</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5011</v>
+        <v>0.4345</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5011</v>
+        <v>0.4345</v>
       </c>
       <c r="N26" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>Qlocuu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4347</v>
+        <v>0.4577</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4263</v>
+        <v>-0.4094</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4347</v>
+        <v>0.4577</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4347</v>
+        <v>0.5011</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4347</v>
+        <v>0.5011</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4347</v>
+        <v>0.5011</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4347</v>
+        <v>0.5011</v>
       </c>
       <c r="N27" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hfah</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4056</v>
+        <v>0.4505</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0893</v>
+        <v>0.0992</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4396</v>
+        <v>-0.4126</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4056</v>
+        <v>0.4505</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4056</v>
+        <v>0.5295</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.1449</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4056</v>
+        <v>0.5295</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4056</v>
+        <v>0.2859</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1449</v>
       </c>
       <c r="K28" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4056</v>
+        <v>0.4308</v>
       </c>
       <c r="N28" t="n">
-        <v>156</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3507</v>
+        <v>0.2694</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0772</v>
+        <v>0.0593</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4646</v>
+        <v>-0.4935</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3507</v>
+        <v>0.2694</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3507</v>
+        <v>0.3511</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3507</v>
+        <v>0.3511</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3507</v>
+        <v>0.3511</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3507</v>
+        <v>0.3511</v>
       </c>
       <c r="N29" t="n">
         <v>154</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1213</v>
+        <v>-0.0307</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0267</v>
+        <v>-0.0068</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.569</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1213</v>
+        <v>-0.0307</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1213</v>
+        <v>0.03</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1213</v>
+        <v>0.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1213</v>
+        <v>0.03</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1213</v>
+        <v>0.03</v>
       </c>
       <c r="N30" t="n">
         <v>122</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0302</v>
+        <v>-0.0824</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0066</v>
+        <v>-0.0181</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6105</v>
+        <v>-0.6506</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0302</v>
+        <v>-0.0824</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0302</v>
+        <v>0.138</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0302</v>
+        <v>0.138</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0302</v>
+        <v>0.138</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0302</v>
+        <v>0.138</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1872,170 +1872,170 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>Sobol</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1511</v>
+        <v>-0.2426</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0333</v>
+        <v>-0.0534</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.7222</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1511</v>
+        <v>-0.2426</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6845</v>
+        <v>-0.3116</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8356</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6845</v>
+        <v>-0.3116</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3696</v>
+        <v>-0.3116</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8356</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="L32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.466</v>
+        <v>-0.3116</v>
       </c>
       <c r="N32" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2942</v>
+        <v>-0.2574</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0648</v>
+        <v>-0.0567</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7581</v>
+        <v>-0.7288</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2942</v>
+        <v>-0.2574</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2942</v>
+        <v>0.6553</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.8356</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2942</v>
+        <v>0.6553</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2942</v>
+        <v>0.3538</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.8356</v>
       </c>
       <c r="K33" t="n">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2942</v>
+        <v>-0.4818</v>
       </c>
       <c r="N33" t="n">
-        <v>122</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sobol</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3116</v>
+        <v>-0.3854</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0848</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.766</v>
+        <v>-0.786</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3116</v>
+        <v>-0.3854</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3116</v>
+        <v>-0.2943</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3116</v>
+        <v>-0.2943</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3116</v>
+        <v>-0.2943</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3116</v>
+        <v>-0.2943</v>
       </c>
       <c r="N34" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3366</v>
+        <v>-0.6078</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0741</v>
+        <v>-0.1338</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7774</v>
+        <v>-0.8853</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3366</v>
+        <v>-0.6078</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3366</v>
+        <v>-0.5722</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3366</v>
+        <v>-0.5722</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3366</v>
+        <v>-0.5722</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3366</v>
+        <v>-0.5722</v>
       </c>
       <c r="N35" t="n">
         <v>121</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3704</v>
+        <v>-0.6256</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0815</v>
+        <v>-0.1377</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.8933</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3704</v>
+        <v>-0.6256</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3704</v>
+        <v>-0.3959</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3704</v>
+        <v>-0.3959</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3704</v>
+        <v>-0.3959</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3704</v>
+        <v>-0.3959</v>
       </c>
       <c r="N36" t="n">
         <v>154</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.374</v>
+        <v>-0.6647</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0823</v>
+        <v>-0.1463</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7945</v>
+        <v>-0.9107</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.374</v>
+        <v>-0.6647</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.374</v>
+        <v>-0.3623</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.374</v>
+        <v>-0.3623</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.374</v>
+        <v>-0.3623</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.374</v>
+        <v>-0.3623</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5718</v>
+        <v>-0.6975</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1259</v>
+        <v>-0.1535</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8845</v>
+        <v>-0.9254</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5718</v>
+        <v>-0.6975</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5718</v>
+        <v>-0.3371</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5718</v>
+        <v>-0.3371</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5718</v>
+        <v>-0.3371</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.5718</v>
+        <v>-0.3371</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0452</v>
+        <v>-1.4106</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2301</v>
+        <v>-0.3105</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1</v>
+        <v>-1.2439</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0452</v>
+        <v>-1.4106</v>
       </c>
       <c r="F39" t="n">
         <v>-1.0452</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.507</v>
+        <v>-1.5944</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3317</v>
+        <v>-0.351</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3102</v>
+        <v>-1.326</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.507</v>
+        <v>-1.5944</v>
       </c>
       <c r="F40" t="n">
         <v>-1.6059</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0714</v>
+        <v>-2.2199</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4559</v>
+        <v>-0.4886</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5671</v>
+        <v>-1.6054</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0714</v>
+        <v>-2.2199</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.0714</v>
+        <v>-2.0711</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.0714</v>
+        <v>-2.0711</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0714</v>
+        <v>-2.0711</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0714</v>
+        <v>-2.0711</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2629,10 +2629,10 @@
         <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1339</v>
+        <v>1.1343</v>
       </c>
       <c r="J7" t="n">
-        <v>21.5441</v>
+        <v>21.5517</v>
       </c>
     </row>
     <row r="8">
@@ -2666,13 +2666,13 @@
         <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="J8" t="n">
-        <v>13.5508</v>
+        <v>13.376</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4819</v>
+        <v>0.482</v>
       </c>
       <c r="J9" t="n">
-        <v>9.1561</v>
+        <v>9.157999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.206</v>
+        <v>0.2062</v>
       </c>
       <c r="J10" t="n">
-        <v>3.914</v>
+        <v>3.9178</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2005</v>
+        <v>-0.2004</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8095</v>
+        <v>-3.8076</v>
       </c>
     </row>
     <row r="12">
@@ -3226,13 +3226,13 @@
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0839</v>
+        <v>1.066</v>
       </c>
       <c r="J22" t="n">
-        <v>22.7619</v>
+        <v>22.386</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7045</v>
+        <v>0.7055</v>
       </c>
       <c r="J23" t="n">
-        <v>14.7945</v>
+        <v>14.8155</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4866</v>
+        <v>0.4872</v>
       </c>
       <c r="J24" t="n">
-        <v>10.2186</v>
+        <v>10.2312</v>
       </c>
     </row>
     <row r="25">
@@ -3346,13 +3346,13 @@
         <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2855</v>
+        <v>-0.3132</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.9955</v>
+        <v>-6.5772</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.85</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4958</v>
+        <v>-0.4951</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.4118</v>
+        <v>-10.3971</v>
       </c>
     </row>
     <row r="27">
@@ -3426,13 +3426,13 @@
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7604</v>
+        <v>0.7746</v>
       </c>
       <c r="J27" t="n">
-        <v>15.9684</v>
+        <v>16.2666</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3062</v>
+        <v>0.3058</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4302</v>
+        <v>6.4218</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1455</v>
+        <v>0.1452</v>
       </c>
       <c r="J29" t="n">
-        <v>3.0555</v>
+        <v>3.0492</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2135</v>
+        <v>-0.2137</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.4835</v>
+        <v>-4.4877</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3856</v>
+        <v>-0.3857</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.0976</v>
+        <v>-8.0997</v>
       </c>
     </row>
     <row r="32">
@@ -3829,10 +3829,10 @@
         <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5689</v>
+        <v>0.5681</v>
       </c>
       <c r="J37" t="n">
-        <v>10.2402</v>
+        <v>10.2258</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1206</v>
+        <v>0.1201</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1708</v>
+        <v>2.1618</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1158</v>
+        <v>-0.1159</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.0844</v>
+        <v>-2.0862</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3462</v>
+        <v>-0.3464</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.2316</v>
+        <v>-6.2352</v>
       </c>
     </row>
     <row r="41">
@@ -3986,13 +3986,13 @@
         <v>18</v>
       </c>
       <c r="H41" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4796</v>
+        <v>-0.4711</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.6328</v>
+        <v>-8.479799999999999</v>
       </c>
     </row>
     <row r="42">
@@ -7629,10 +7629,10 @@
         <v>2.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1.8807</v>
+        <v>1.8812</v>
       </c>
       <c r="J132" t="n">
-        <v>28.2105</v>
+        <v>28.218</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>2.08</v>
       </c>
       <c r="I133" t="n">
-        <v>1.746</v>
+        <v>1.7464</v>
       </c>
       <c r="J133" t="n">
-        <v>26.19</v>
+        <v>26.196</v>
       </c>
     </row>
     <row r="134">
@@ -7706,13 +7706,13 @@
         <v>15</v>
       </c>
       <c r="H134" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9998</v>
+        <v>0.9842</v>
       </c>
       <c r="J134" t="n">
-        <v>14.997</v>
+        <v>14.763</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7436</v>
+        <v>0.7438</v>
       </c>
       <c r="J135" t="n">
-        <v>11.154</v>
+        <v>11.157</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6756</v>
+        <v>-0.6754</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.134</v>
+        <v>-10.131</v>
       </c>
     </row>
     <row r="137">
@@ -9638,7 +9638,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9678,7 +9678,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11029,10 +11029,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9954</v>
+        <v>0.9957</v>
       </c>
       <c r="J217" t="n">
-        <v>16.9218</v>
+        <v>16.9269</v>
       </c>
     </row>
     <row r="218">
@@ -11066,13 +11066,13 @@
         <v>17</v>
       </c>
       <c r="H218" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5623</v>
+        <v>0.5523</v>
       </c>
       <c r="J218" t="n">
-        <v>9.559100000000001</v>
+        <v>9.389099999999999</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.281</v>
+        <v>0.2811</v>
       </c>
       <c r="J219" t="n">
-        <v>4.777</v>
+        <v>4.7787</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2561</v>
+        <v>0.2563</v>
       </c>
       <c r="J220" t="n">
-        <v>4.3537</v>
+        <v>4.3571</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3504</v>
+        <v>-0.3503</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.9568</v>
+        <v>-5.9551</v>
       </c>
     </row>
     <row r="222">
@@ -12029,10 +12029,10 @@
         <v>1.43</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5501</v>
+        <v>0.5496</v>
       </c>
       <c r="J242" t="n">
-        <v>11.002</v>
+        <v>10.992</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4111</v>
+        <v>0.4107</v>
       </c>
       <c r="J243" t="n">
-        <v>8.222</v>
+        <v>8.214</v>
       </c>
     </row>
     <row r="244">
@@ -12106,13 +12106,13 @@
         <v>20</v>
       </c>
       <c r="H244" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2862</v>
+        <v>0.2979</v>
       </c>
       <c r="J244" t="n">
-        <v>5.724</v>
+        <v>5.958</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.17</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2617</v>
+        <v>0.2613</v>
       </c>
       <c r="J245" t="n">
-        <v>5.234</v>
+        <v>5.226</v>
       </c>
     </row>
     <row r="246">
@@ -12186,13 +12186,13 @@
         <v>20</v>
       </c>
       <c r="H246" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0125</v>
+        <v>0.0348</v>
       </c>
       <c r="J246" t="n">
-        <v>0.25</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="247">
@@ -12629,10 +12629,10 @@
         <v>1.62</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2538</v>
+        <v>1.2542</v>
       </c>
       <c r="J257" t="n">
-        <v>26.3298</v>
+        <v>26.3382</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.6</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2275</v>
+        <v>1.2279</v>
       </c>
       <c r="J258" t="n">
-        <v>25.7775</v>
+        <v>25.7859</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5174</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>10.8654</v>
+        <v>10.8696</v>
       </c>
     </row>
     <row r="260">
@@ -12746,13 +12746,13 @@
         <v>21</v>
       </c>
       <c r="H260" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3276</v>
+        <v>0.3021</v>
       </c>
       <c r="J260" t="n">
-        <v>6.8796</v>
+        <v>6.3441</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7673</v>
+        <v>-0.767</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.1133</v>
+        <v>-16.107</v>
       </c>
     </row>
     <row r="262">
@@ -14026,13 +14026,13 @@
         <v>24</v>
       </c>
       <c r="H292" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1558</v>
+        <v>1.169</v>
       </c>
       <c r="J292" t="n">
-        <v>27.7392</v>
+        <v>28.056</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.25</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6581</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J293" t="n">
-        <v>15.7944</v>
+        <v>15.7872</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5063</v>
+        <v>0.506</v>
       </c>
       <c r="J294" t="n">
-        <v>12.1512</v>
+        <v>12.144</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0856</v>
+        <v>-0.0859</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.0544</v>
+        <v>-2.0616</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5477</v>
+        <v>-0.548</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.1448</v>
+        <v>-13.152</v>
       </c>
     </row>
     <row r="297">
@@ -15229,10 +15229,10 @@
         <v>1.75</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3779</v>
+        <v>1.3782</v>
       </c>
       <c r="J322" t="n">
-        <v>23.4243</v>
+        <v>23.4294</v>
       </c>
     </row>
     <row r="323">
@@ -15266,13 +15266,13 @@
         <v>17</v>
       </c>
       <c r="H323" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1163</v>
+        <v>1.1037</v>
       </c>
       <c r="J323" t="n">
-        <v>18.9771</v>
+        <v>18.7629</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.4</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9103</v>
+        <v>0.9105</v>
       </c>
       <c r="J324" t="n">
-        <v>15.4751</v>
+        <v>15.4785</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.39</v>
       </c>
       <c r="I325" t="n">
-        <v>0.892</v>
+        <v>0.8922</v>
       </c>
       <c r="J325" t="n">
-        <v>15.164</v>
+        <v>15.1674</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5949</v>
+        <v>0.5952</v>
       </c>
       <c r="J326" t="n">
-        <v>10.1133</v>
+        <v>10.1184</v>
       </c>
     </row>
     <row r="327">
@@ -15826,13 +15826,13 @@
         <v>21</v>
       </c>
       <c r="H337" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4819</v>
+        <v>0.4986</v>
       </c>
       <c r="J337" t="n">
-        <v>10.1199</v>
+        <v>10.4706</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0649</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.3587</v>
+        <v>-1.3629</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1604</v>
+        <v>-0.1605</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.3684</v>
+        <v>-3.3705</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2223</v>
+        <v>-0.2225</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.6683</v>
+        <v>-4.6725</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.59</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4364</v>
+        <v>-0.4366</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.164400000000001</v>
+        <v>-9.1686</v>
       </c>
     </row>
     <row r="342">

--- a/database/event/8067/event_8067_evp_summary.xlsx
+++ b/database/event/8067/event_8067_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1985</v>
+        <v>7.1065</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5845</v>
+        <v>1.5642</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6016</v>
+        <v>2.6316</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1985</v>
+        <v>7.1065</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5741</v>
+        <v>2.5716</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4832</v>
+        <v>4.3937</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5986</v>
+        <v>3.2125</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9432</v>
+        <v>1.8037</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4832</v>
+        <v>4.3937</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4264</v>
+        <v>6.1974</v>
       </c>
       <c r="N2" t="n">
         <v>239</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2157</v>
+        <v>6.2191</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3682</v>
+        <v>1.3689</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1626</v>
+        <v>2.2273</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2157</v>
+        <v>6.2191</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1058</v>
+        <v>2.4742</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0708</v>
+        <v>3.4531</v>
       </c>
       <c r="H3" t="n">
-        <v>5.353</v>
+        <v>2.8465</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8906</v>
+        <v>1.5982</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0708</v>
+        <v>3.4531</v>
       </c>
       <c r="K3" t="n">
         <v>103</v>
@@ -575,7 +575,7 @@
         <v>136</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9614</v>
+        <v>5.0513</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.982</v>
+        <v>6.132</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3167</v>
+        <v>1.3497</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0582</v>
+        <v>2.1876</v>
       </c>
       <c r="E4" t="n">
-        <v>5.982</v>
+        <v>6.132</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4066</v>
+        <v>3.0339</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2836</v>
+        <v>3.059</v>
       </c>
       <c r="H4" t="n">
-        <v>3.046</v>
+        <v>4.9481</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6448</v>
+        <v>2.7782</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2836</v>
+        <v>3.059</v>
       </c>
       <c r="K4" t="n">
         <v>103</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9284</v>
+        <v>5.8372</v>
       </c>
       <c r="N4" t="n">
         <v>239</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2727</v>
+        <v>5.2239</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1606</v>
+        <v>1.1499</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7414</v>
+        <v>1.7739</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2727</v>
+        <v>5.2239</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0248</v>
+        <v>3.0062</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2684</v>
+        <v>2.2382</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0858</v>
+        <v>4.8441</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7463</v>
+        <v>2.7198</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2684</v>
+        <v>2.2382</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0147</v>
+        <v>4.958</v>
       </c>
       <c r="N5" t="n">
         <v>276</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.239</v>
+        <v>5.0529</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1532</v>
+        <v>1.1122</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7263</v>
+        <v>1.696</v>
       </c>
       <c r="E6" t="n">
-        <v>5.239</v>
+        <v>5.0529</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1156</v>
+        <v>3.0925</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9433</v>
+        <v>1.7803</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3853</v>
+        <v>5.1681</v>
       </c>
       <c r="I6" t="n">
-        <v>2.908</v>
+        <v>2.9017</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9433</v>
+        <v>1.7803</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8513</v>
+        <v>4.682</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5798</v>
+        <v>4.2431</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0081</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4319</v>
+        <v>1.3271</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5798</v>
+        <v>4.2431</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1657</v>
+        <v>3.8978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1492</v>
+        <v>0.0804</v>
       </c>
       <c r="H7" t="n">
-        <v>8.8499</v>
+        <v>8.1913</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7788</v>
+        <v>4.5992</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1492</v>
+        <v>0.0804</v>
       </c>
       <c r="K7" t="n">
         <v>219</v>
@@ -759,7 +759,7 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>4.928000000000001</v>
+        <v>4.6796</v>
       </c>
       <c r="N7" t="n">
         <v>280</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0592</v>
+        <v>4.1161</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8935</v>
+        <v>0.906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1993</v>
+        <v>1.2693</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0592</v>
+        <v>4.1161</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5807</v>
+        <v>4.605</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.636</v>
+        <v>-0.6034</v>
       </c>
       <c r="H8" t="n">
-        <v>13.3313</v>
+        <v>12.7219</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1988</v>
+        <v>7.1429</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.636</v>
+        <v>-0.6034</v>
       </c>
       <c r="K8" t="n">
         <v>238</v>
@@ -805,7 +805,7 @@
         <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>6.5628</v>
+        <v>6.5395</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0054</v>
+        <v>3.7526</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1753</v>
+        <v>1.1037</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0054</v>
+        <v>3.7526</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5807</v>
+        <v>4.3021</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7187</v>
       </c>
       <c r="H9" t="n">
-        <v>10.29</v>
+        <v>9.7094</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5565</v>
+        <v>5.4515</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7187</v>
       </c>
       <c r="K9" t="n">
         <v>238</v>
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>4.811999999999999</v>
+        <v>4.7328</v>
       </c>
       <c r="N9" t="n">
         <v>280</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7632</v>
+        <v>3.7423</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8283</v>
+        <v>0.8237</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0671</v>
+        <v>1.099</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7632</v>
+        <v>3.7423</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1009</v>
+        <v>3.1119</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5936</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3369</v>
+        <v>5.2407</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8819</v>
+        <v>2.9425</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5936</v>
       </c>
       <c r="K10" t="n">
         <v>121</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5074</v>
+        <v>3.5361</v>
       </c>
       <c r="N10" t="n">
         <v>276</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4993</v>
+        <v>3.4309</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7702</v>
+        <v>0.7552</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9492</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4993</v>
+        <v>3.4309</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9453</v>
+        <v>2.964</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519</v>
+        <v>0.4319</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8235</v>
+        <v>4.6857</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6046</v>
+        <v>2.6308</v>
       </c>
       <c r="J11" t="n">
-        <v>0.519</v>
+        <v>0.4319</v>
       </c>
       <c r="K11" t="n">
         <v>219</v>
@@ -943,7 +943,7 @@
         <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1236</v>
+        <v>3.0627</v>
       </c>
       <c r="N11" t="n">
         <v>280</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4054</v>
+        <v>3.3612</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7496</v>
+        <v>0.7399</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9073</v>
+        <v>0.9254</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4054</v>
+        <v>3.3612</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1693</v>
+        <v>3.1311</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2741</v>
+        <v>0.2681</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5624</v>
+        <v>5.313</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0036</v>
+        <v>2.9831</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2741</v>
+        <v>0.2681</v>
       </c>
       <c r="K12" t="n">
         <v>219</v>
@@ -989,7 +989,7 @@
         <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2777</v>
+        <v>3.2512</v>
       </c>
       <c r="N12" t="n">
         <v>280</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3873</v>
+        <v>3.2475</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7456</v>
+        <v>0.7148</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8992</v>
+        <v>0.8736</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3873</v>
+        <v>3.2475</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5901</v>
+        <v>3.4715</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1664</v>
+        <v>-0.1876</v>
       </c>
       <c r="H13" t="n">
-        <v>6.9508</v>
+        <v>6.5908</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7534</v>
+        <v>3.7005</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1664</v>
+        <v>-0.1876</v>
       </c>
       <c r="K13" t="n">
         <v>219</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.587</v>
+        <v>3.5129</v>
       </c>
       <c r="N13" t="n">
         <v>280</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2049</v>
+        <v>3.1447</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7054</v>
+        <v>0.6922</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8177</v>
+        <v>0.8268</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2049</v>
+        <v>3.1447</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4956</v>
+        <v>1.5801</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7162</v>
+        <v>1.5715</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4956</v>
+        <v>1.5801</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8076</v>
+        <v>0.8872</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7162</v>
+        <v>1.5715</v>
       </c>
       <c r="K14" t="n">
         <v>121</v>
@@ -1081,7 +1081,7 @@
         <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5238</v>
+        <v>2.4587</v>
       </c>
       <c r="N14" t="n">
         <v>276</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8925</v>
+        <v>2.9081</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6367</v>
+        <v>0.6401</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6782</v>
+        <v>0.719</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8925</v>
+        <v>2.9081</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4467</v>
+        <v>2.5116</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3947</v>
+        <v>0.3454</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1783</v>
+        <v>2.9871</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7162</v>
+        <v>1.6772</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3947</v>
+        <v>0.3454</v>
       </c>
       <c r="K15" t="n">
         <v>238</v>
@@ -1127,7 +1127,7 @@
         <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1109</v>
+        <v>2.0226</v>
       </c>
       <c r="N15" t="n">
         <v>280</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7177</v>
+        <v>2.7416</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5982</v>
+        <v>0.6035</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6001</v>
+        <v>0.6431</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7177</v>
+        <v>2.7416</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3321</v>
+        <v>2.356</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3793</v>
+        <v>2.4492</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3793</v>
+        <v>2.4492</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3793</v>
+        <v>2.4492</v>
       </c>
       <c r="N16" t="n">
         <v>154</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6482</v>
+        <v>2.651</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5829</v>
+        <v>0.5835</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.6019</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6482</v>
+        <v>2.651</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4631</v>
+        <v>2.4659</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6661</v>
+        <v>2.701</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6661</v>
+        <v>2.701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6661</v>
+        <v>2.701</v>
       </c>
       <c r="N17" t="n">
         <v>156</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5297</v>
+        <v>2.6047</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5568</v>
+        <v>0.5733</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5161</v>
+        <v>0.5808</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5297</v>
+        <v>2.6047</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4693</v>
+        <v>0.5251</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1197</v>
+        <v>2.1389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4693</v>
+        <v>0.5251</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2534</v>
+        <v>0.2948</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1197</v>
+        <v>2.1389</v>
       </c>
       <c r="K18" t="n">
         <v>103</v>
@@ -1265,7 +1265,7 @@
         <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3731</v>
+        <v>2.4337</v>
       </c>
       <c r="N18" t="n">
         <v>239</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2626</v>
+        <v>2.2097</v>
       </c>
       <c r="C19" t="n">
-        <v>0.498</v>
+        <v>0.4864</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3968</v>
+        <v>0.4008</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2626</v>
+        <v>2.2097</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8294</v>
+        <v>1.7765</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8294</v>
+        <v>1.7765</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8294</v>
+        <v>1.7765</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8294</v>
+        <v>1.7765</v>
       </c>
       <c r="N19" t="n">
         <v>121</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6144</v>
+        <v>1.761</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3554</v>
+        <v>0.3876</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1073</v>
+        <v>0.1964</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6144</v>
+        <v>1.761</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6874</v>
+        <v>-0.5304</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4728</v>
+        <v>2.4624</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6874</v>
+        <v>-0.5304</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3712</v>
+        <v>-0.2978</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4728</v>
+        <v>2.4624</v>
       </c>
       <c r="K20" t="n">
         <v>103</v>
@@ -1357,7 +1357,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1016</v>
+        <v>2.1646</v>
       </c>
       <c r="N20" t="n">
         <v>239</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>spooke</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5958</v>
+        <v>1.4077</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3513</v>
+        <v>0.3099</v>
       </c>
       <c r="D21" t="n">
-        <v>0.099</v>
+        <v>0.0355</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5958</v>
+        <v>1.4077</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3714</v>
+        <v>1.3162</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3714</v>
+        <v>1.3162</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3714</v>
+        <v>1.3162</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3714</v>
+        <v>1.3162</v>
       </c>
       <c r="N21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>spooke</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5815</v>
+        <v>1.3826</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3481</v>
+        <v>0.3043</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0926</v>
+        <v>0.0241</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5815</v>
+        <v>1.3826</v>
       </c>
       <c r="F22" t="n">
-        <v>1.49</v>
+        <v>1.1582</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.49</v>
+        <v>1.1582</v>
       </c>
       <c r="I22" t="n">
-        <v>1.49</v>
+        <v>1.1582</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.49</v>
+        <v>1.1582</v>
       </c>
       <c r="N22" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3688</v>
+        <v>1.3599</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3013</v>
+        <v>0.2993</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0024</v>
+        <v>0.0137</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3688</v>
+        <v>1.3599</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7581</v>
+        <v>2.7588</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0957</v>
+        <v>-1.1053</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2058</v>
+        <v>3.9151</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2711</v>
+        <v>2.1982</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0957</v>
+        <v>-1.1053</v>
       </c>
       <c r="K23" t="n">
         <v>121</v>
@@ -1495,7 +1495,7 @@
         <v>155</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1754</v>
+        <v>1.0929</v>
       </c>
       <c r="N23" t="n">
         <v>276</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0915</v>
+        <v>1.0344</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2403</v>
+        <v>0.2277</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1263</v>
+        <v>-0.1346</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0915</v>
+        <v>1.0344</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1651</v>
+        <v>1.108</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1651</v>
+        <v>1.108</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1651</v>
+        <v>1.108</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1651</v>
+        <v>1.108</v>
       </c>
       <c r="N24" t="n">
         <v>154</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6137</v>
+        <v>0.6621</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1351</v>
+        <v>0.1457</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3397</v>
+        <v>-0.3042</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6137</v>
+        <v>0.6621</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4056</v>
+        <v>0.454</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4056</v>
+        <v>0.454</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4056</v>
+        <v>0.454</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4056</v>
+        <v>0.454</v>
       </c>
       <c r="N25" t="n">
         <v>156</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5412</v>
+        <v>0.446</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1191</v>
+        <v>0.0982</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3721</v>
+        <v>-0.4026</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5412</v>
+        <v>0.446</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4345</v>
+        <v>0.3393</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4345</v>
+        <v>0.3393</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4345</v>
+        <v>0.3393</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4345</v>
+        <v>0.3393</v>
       </c>
       <c r="N26" t="n">
         <v>122</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4577</v>
+        <v>0.4405</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1007</v>
+        <v>0.097</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4094</v>
+        <v>-0.4051</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4577</v>
+        <v>0.4405</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5011</v>
+        <v>0.4839</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5011</v>
+        <v>0.4839</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5011</v>
+        <v>0.4839</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5011</v>
+        <v>0.4839</v>
       </c>
       <c r="N27" t="n">
         <v>156</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4505</v>
+        <v>0.3626</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0992</v>
+        <v>0.0798</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4126</v>
+        <v>-0.4406</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4505</v>
+        <v>0.3626</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5295</v>
+        <v>0.4443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1449</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5295</v>
+        <v>0.4443</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2859</v>
+        <v>0.4443</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1449</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4308</v>
+        <v>0.4443</v>
       </c>
       <c r="N28" t="n">
-        <v>280</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2694</v>
+        <v>0.2981</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0593</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4935</v>
+        <v>-0.47</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2694</v>
+        <v>0.2981</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3511</v>
+        <v>0.41</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3511</v>
+        <v>0.41</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3511</v>
+        <v>0.2302</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="K29" t="n">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3511</v>
+        <v>0.3422</v>
       </c>
       <c r="N29" t="n">
-        <v>154</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0307</v>
+        <v>-0.1246</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0068</v>
+        <v>-0.0274</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0307</v>
+        <v>-0.1246</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03</v>
+        <v>0.7684</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.8159</v>
       </c>
       <c r="H30" t="n">
-        <v>0.03</v>
+        <v>0.7684</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03</v>
+        <v>0.4315</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.8159</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>0.03</v>
+        <v>-0.3844</v>
       </c>
       <c r="N30" t="n">
-        <v>122</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0824</v>
+        <v>-0.1319</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0181</v>
+        <v>-0.029</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6506</v>
+        <v>-0.6659</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0824</v>
+        <v>-0.1319</v>
       </c>
       <c r="F31" t="n">
-        <v>0.138</v>
+        <v>0.0885</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.138</v>
+        <v>0.0885</v>
       </c>
       <c r="I31" t="n">
-        <v>0.138</v>
+        <v>0.0885</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.138</v>
+        <v>0.0885</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sobol</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2426</v>
+        <v>-0.2244</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0534</v>
+        <v>-0.0494</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7222</v>
+        <v>-0.708</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2426</v>
+        <v>-0.2244</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3116</v>
+        <v>-0.1637</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3116</v>
+        <v>-0.1637</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3116</v>
+        <v>-0.1637</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3116</v>
+        <v>-0.1637</v>
       </c>
       <c r="N32" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>Sobol</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2574</v>
+        <v>-0.3243</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0567</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7288</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2574</v>
+        <v>-0.3243</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6553</v>
+        <v>-0.3933</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8356</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6553</v>
+        <v>-0.3933</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3538</v>
+        <v>-0.3933</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8356</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="L33" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4818</v>
+        <v>-0.3933</v>
       </c>
       <c r="N33" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3854</v>
+        <v>-0.4066</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0848</v>
+        <v>-0.0895</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.786</v>
+        <v>-0.791</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3854</v>
+        <v>-0.4066</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2943</v>
+        <v>-0.3155</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2943</v>
+        <v>-0.3155</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2943</v>
+        <v>-0.3155</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2943</v>
+        <v>-0.3155</v>
       </c>
       <c r="N34" t="n">
         <v>122</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6078</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1338</v>
+        <v>-0.1319</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8853</v>
+        <v>-0.8788</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6078</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5722</v>
+        <v>-0.5637</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5722</v>
+        <v>-0.5637</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5722</v>
+        <v>-0.5637</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5722</v>
+        <v>-0.5637</v>
       </c>
       <c r="N35" t="n">
         <v>121</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6256</v>
+        <v>-0.6238</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1377</v>
+        <v>-0.1373</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8933</v>
+        <v>-0.89</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6256</v>
+        <v>-0.6238</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3959</v>
+        <v>-0.3941</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3959</v>
+        <v>-0.3941</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3959</v>
+        <v>-0.3941</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3959</v>
+        <v>-0.3941</v>
       </c>
       <c r="N36" t="n">
         <v>154</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6647</v>
+        <v>-0.7714</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1463</v>
+        <v>-0.1698</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9107</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6647</v>
+        <v>-0.7714</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3623</v>
+        <v>-0.411</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3623</v>
+        <v>-0.411</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3623</v>
+        <v>-0.411</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.3623</v>
+        <v>-0.411</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6975</v>
+        <v>-0.7721</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1535</v>
+        <v>-0.17</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9254</v>
+        <v>-0.9575</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6975</v>
+        <v>-0.7721</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3371</v>
+        <v>-0.4697</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3371</v>
+        <v>-0.4697</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3371</v>
+        <v>-0.4697</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.3371</v>
+        <v>-0.4697</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4106</v>
+        <v>-1.4308</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3105</v>
+        <v>-0.3149</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2439</v>
+        <v>-1.2576</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4106</v>
+        <v>-1.4308</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0452</v>
+        <v>-1.4147</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0452</v>
+        <v>-1.4147</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0452</v>
+        <v>-0.7943</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="K39" t="n">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0452</v>
+        <v>-0.723</v>
       </c>
       <c r="N39" t="n">
-        <v>156</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5944</v>
+        <v>-1.4484</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.351</v>
+        <v>-0.3188</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.326</v>
+        <v>-1.2656</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5944</v>
+        <v>-1.4484</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6059</v>
+        <v>-1.083</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0989</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6059</v>
+        <v>-1.083</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8672</v>
+        <v>-1.083</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0989</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="L40" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.7683</v>
+        <v>-1.083</v>
       </c>
       <c r="N40" t="n">
-        <v>280</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2199</v>
+        <v>-2.1628</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4886</v>
+        <v>-0.4761</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6054</v>
+        <v>-1.591</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2199</v>
+        <v>-2.1628</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.0711</v>
+        <v>-2.014</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.0711</v>
+        <v>-2.014</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0711</v>
+        <v>-2.014</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0711</v>
+        <v>-2.014</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3296</v>
+        <v>0.3265</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2624</v>
+        <v>6.2035</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1504</v>
+        <v>0.1366</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8576</v>
+        <v>2.5954</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1649</v>
+        <v>-0.1485</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.1331</v>
+        <v>-2.8215</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3291</v>
+        <v>-0.3129</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.2529</v>
+        <v>-5.9451</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6843</v>
+        <v>-0.7148</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.0017</v>
+        <v>-13.5812</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1343</v>
+        <v>1.0762</v>
       </c>
       <c r="J7" t="n">
-        <v>21.5517</v>
+        <v>20.4478</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.61</v>
       </c>
       <c r="I8" t="n">
-        <v>0.704</v>
+        <v>0.6332</v>
       </c>
       <c r="J8" t="n">
-        <v>13.376</v>
+        <v>12.0308</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.482</v>
+        <v>0.4197</v>
       </c>
       <c r="J9" t="n">
-        <v>9.157999999999999</v>
+        <v>7.9743</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2062</v>
+        <v>0.1659</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9178</v>
+        <v>3.1521</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2004</v>
+        <v>-0.1835</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8076</v>
+        <v>-3.4865</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5554</v>
+        <v>0.5746</v>
       </c>
       <c r="J12" t="n">
-        <v>12.2188</v>
+        <v>12.6412</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2294</v>
+        <v>0.2134</v>
       </c>
       <c r="J13" t="n">
-        <v>5.0468</v>
+        <v>4.6948</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1107</v>
+        <v>-0.0931</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4354</v>
+        <v>-2.0482</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2315</v>
+        <v>-0.2111</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.093</v>
+        <v>-4.6442</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.71</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3376</v>
+        <v>-0.3219</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.4272</v>
+        <v>-7.0818</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3931</v>
+        <v>0.3302</v>
       </c>
       <c r="J17" t="n">
-        <v>8.648199999999999</v>
+        <v>7.2644</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2968</v>
+        <v>0.242</v>
       </c>
       <c r="J18" t="n">
-        <v>6.5296</v>
+        <v>5.324</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1924</v>
+        <v>0.1506</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2328</v>
+        <v>3.3132</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="J20" t="n">
-        <v>1.892</v>
+        <v>1.3838</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2299</v>
+        <v>-0.2098</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.0578</v>
+        <v>-4.6156</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.45</v>
       </c>
       <c r="I22" t="n">
-        <v>1.066</v>
+        <v>1.0651</v>
       </c>
       <c r="J22" t="n">
-        <v>22.386</v>
+        <v>22.3671</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7055</v>
+        <v>0.6734</v>
       </c>
       <c r="J23" t="n">
-        <v>14.8155</v>
+        <v>14.1414</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.17</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4872</v>
+        <v>0.4489</v>
       </c>
       <c r="J24" t="n">
-        <v>10.2312</v>
+        <v>9.4269</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3132</v>
+        <v>-0.272</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.5772</v>
+        <v>-5.712</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.85</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4951</v>
+        <v>-0.454</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.3971</v>
+        <v>-9.534000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7746</v>
+        <v>0.7208</v>
       </c>
       <c r="J27" t="n">
-        <v>16.2666</v>
+        <v>15.1368</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3058</v>
+        <v>0.2551</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4218</v>
+        <v>5.3571</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1452</v>
+        <v>0.1121</v>
       </c>
       <c r="J29" t="n">
-        <v>3.0492</v>
+        <v>2.3541</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2137</v>
+        <v>-0.1931</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.4877</v>
+        <v>-4.0551</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3857</v>
+        <v>-0.3744</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.0997</v>
+        <v>-7.8624</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1437</v>
+        <v>1.1519</v>
       </c>
       <c r="J32" t="n">
-        <v>20.5866</v>
+        <v>20.7342</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8811</v>
+        <v>0.8642</v>
       </c>
       <c r="J33" t="n">
-        <v>15.8598</v>
+        <v>15.5556</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5824</v>
+        <v>0.5517</v>
       </c>
       <c r="J34" t="n">
-        <v>10.4832</v>
+        <v>9.9306</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5394</v>
+        <v>0.5077</v>
       </c>
       <c r="J35" t="n">
-        <v>9.709199999999999</v>
+        <v>9.1386</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2143</v>
+        <v>-0.1807</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.8574</v>
+        <v>-3.2526</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5681</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>10.2258</v>
+        <v>9.2448</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1201</v>
+        <v>0.09</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1618</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1159</v>
+        <v>-0.1002</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.0862</v>
+        <v>-1.8036</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3464</v>
+        <v>-0.3309</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.2352</v>
+        <v>-5.9562</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4711</v>
+        <v>-0.4676</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.479799999999999</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.26</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J42" t="n">
-        <v>25.8342</v>
+        <v>27.7508</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.53</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1264</v>
+        <v>1.1462</v>
       </c>
       <c r="J43" t="n">
-        <v>15.7696</v>
+        <v>16.0468</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9312</v>
+        <v>0.9325</v>
       </c>
       <c r="J44" t="n">
-        <v>13.0368</v>
+        <v>13.055</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.39</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8754</v>
+        <v>0.8719</v>
       </c>
       <c r="J45" t="n">
-        <v>12.2556</v>
+        <v>12.2066</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8376</v>
+        <v>0.8309</v>
       </c>
       <c r="J46" t="n">
-        <v>11.7264</v>
+        <v>11.6326</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1599</v>
+        <v>1.2372</v>
       </c>
       <c r="J47" t="n">
-        <v>16.2386</v>
+        <v>17.3208</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4857</v>
+        <v>-0.4823</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.7998</v>
+        <v>-6.7522</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.48</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5033</v>
+        <v>-0.5017</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.0462</v>
+        <v>-7.0238</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5735</v>
+        <v>-0.5812</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.029</v>
+        <v>-8.136799999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6837</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.251200000000001</v>
+        <v>-9.5718</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.39</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5266</v>
+        <v>0.4573</v>
       </c>
       <c r="J52" t="n">
-        <v>15.798</v>
+        <v>13.719</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3323</v>
+        <v>0.2743</v>
       </c>
       <c r="J53" t="n">
-        <v>9.968999999999999</v>
+        <v>8.228999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.164</v>
+        <v>0.1269</v>
       </c>
       <c r="J54" t="n">
-        <v>4.92</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0322</v>
+        <v>-0.0233</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.966</v>
+        <v>-0.699</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2609</v>
+        <v>-0.2418</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.827</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5188</v>
+        <v>0.5319</v>
       </c>
       <c r="J57" t="n">
-        <v>15.564</v>
+        <v>15.957</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4697</v>
+        <v>0.4756</v>
       </c>
       <c r="J58" t="n">
-        <v>14.091</v>
+        <v>14.268</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.123</v>
+        <v>-0.1046</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.69</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.72</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3285</v>
+        <v>-0.3122</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.855</v>
+        <v>-9.366</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.68</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3653</v>
+        <v>-0.3518</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.959</v>
+        <v>-10.554</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7418</v>
+        <v>0.6862</v>
       </c>
       <c r="J62" t="n">
-        <v>17.0614</v>
+        <v>15.7826</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0604</v>
+        <v>-0.0472</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.3892</v>
+        <v>-1.0856</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0722</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.0332</v>
+        <v>-1.6606</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1261</v>
+        <v>-0.1073</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.9003</v>
+        <v>-2.4679</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.138</v>
+        <v>-0.1185</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.174</v>
+        <v>-2.7255</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.07</v>
       </c>
       <c r="I67" t="n">
-        <v>1.8493</v>
+        <v>1.9306</v>
       </c>
       <c r="J67" t="n">
-        <v>42.5339</v>
+        <v>44.4038</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6768</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>15.5664</v>
+        <v>14.8281</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0279</v>
+        <v>-0.0224</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.6417</v>
+        <v>-0.5152</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.84</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5259</v>
+        <v>-0.4865</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.0957</v>
+        <v>-11.1895</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9028</v>
+        <v>-0.8921</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.7644</v>
+        <v>-20.5183</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0207</v>
+        <v>0.9921</v>
       </c>
       <c r="J72" t="n">
-        <v>30.621</v>
+        <v>29.763</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>2.826</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.92</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1288</v>
+        <v>-0.1097</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.864</v>
+        <v>-3.291</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1523</v>
+        <v>-0.1322</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.569</v>
+        <v>-3.966</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2069</v>
+        <v>-0.1864</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.207</v>
+        <v>-5.592</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6358</v>
+        <v>0.5989</v>
       </c>
       <c r="J77" t="n">
-        <v>19.074</v>
+        <v>17.967</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4998</v>
+        <v>0.4589</v>
       </c>
       <c r="J78" t="n">
-        <v>14.994</v>
+        <v>13.767</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3024</v>
+        <v>0.2644</v>
       </c>
       <c r="J79" t="n">
-        <v>9.071999999999999</v>
+        <v>7.932</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.147</v>
+        <v>-0.1165</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.41</v>
+        <v>-3.495</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4327</v>
+        <v>-0.3897</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.981</v>
+        <v>-11.691</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.85</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4123</v>
+        <v>1.4282</v>
       </c>
       <c r="J82" t="n">
-        <v>31.0706</v>
+        <v>31.4204</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.4</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8149</v>
+        <v>0.7994</v>
       </c>
       <c r="J83" t="n">
-        <v>17.9278</v>
+        <v>17.5868</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0955</v>
+        <v>-0.0746</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.101</v>
+        <v>-1.6412</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1736</v>
+        <v>-0.1424</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.8192</v>
+        <v>-3.1328</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5093</v>
+        <v>-0.4704</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.2046</v>
+        <v>-10.3488</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2414</v>
+        <v>0.1969</v>
       </c>
       <c r="J87" t="n">
-        <v>5.3108</v>
+        <v>4.3318</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0137</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.3014</v>
+        <v>-0.2046</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1902</v>
+        <v>-0.1714</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.1844</v>
+        <v>-3.7708</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.279</v>
+        <v>-0.2603</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.138</v>
+        <v>-5.7266</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3537</v>
+        <v>-0.3387</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.7814</v>
+        <v>-7.4514</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.33</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5103</v>
+        <v>0.5436</v>
       </c>
       <c r="J92" t="n">
-        <v>8.1648</v>
+        <v>8.6976</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.06</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1513</v>
+        <v>0.1346</v>
       </c>
       <c r="J93" t="n">
-        <v>2.4208</v>
+        <v>2.1536</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.88</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1601</v>
+        <v>-0.1419</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.5616</v>
+        <v>-2.2704</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2017</v>
+        <v>-0.1823</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.2272</v>
+        <v>-2.9168</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6562</v>
+        <v>-0.6822</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.4992</v>
+        <v>-10.9152</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.67</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6872</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>10.9952</v>
+        <v>10.2816</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3942</v>
+        <v>0.3356</v>
       </c>
       <c r="J98" t="n">
-        <v>6.3072</v>
+        <v>5.3696</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3942</v>
+        <v>0.3356</v>
       </c>
       <c r="J99" t="n">
-        <v>6.3072</v>
+        <v>5.3696</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3152</v>
+        <v>0.2635</v>
       </c>
       <c r="J100" t="n">
-        <v>5.0432</v>
+        <v>4.216</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1308</v>
+        <v>0.1005</v>
       </c>
       <c r="J101" t="n">
-        <v>2.0928</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.41</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8379</v>
+        <v>0.822</v>
       </c>
       <c r="J102" t="n">
-        <v>19.2717</v>
+        <v>18.906</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7655</v>
+        <v>0.7497</v>
       </c>
       <c r="J103" t="n">
-        <v>17.6065</v>
+        <v>17.2431</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.08</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2623</v>
+        <v>0.2305</v>
       </c>
       <c r="J104" t="n">
-        <v>6.0329</v>
+        <v>5.3015</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.0102</v>
+        <v>-1.5272</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.0102</v>
+        <v>-1.5272</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3721</v>
+        <v>0.3186</v>
       </c>
       <c r="J107" t="n">
-        <v>8.558299999999999</v>
+        <v>7.3278</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1166</v>
+        <v>-0.1006</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.6818</v>
+        <v>-2.3138</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2026</v>
+        <v>-0.1829</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.6598</v>
+        <v>-4.2067</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2229</v>
+        <v>-0.2031</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.1267</v>
+        <v>-4.6713</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.4768</v>
+        <v>-6.0467</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7863</v>
+        <v>0.7711</v>
       </c>
       <c r="J112" t="n">
-        <v>18.8712</v>
+        <v>18.5064</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7138</v>
+        <v>0.6998</v>
       </c>
       <c r="J113" t="n">
-        <v>17.1312</v>
+        <v>16.7952</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6855</v>
       </c>
       <c r="J114" t="n">
-        <v>16.7784</v>
+        <v>16.452</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4078</v>
+        <v>0.3741</v>
       </c>
       <c r="J115" t="n">
-        <v>9.7872</v>
+        <v>8.978400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.89</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4086</v>
+        <v>-0.3678</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.8064</v>
+        <v>-8.827199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.12</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3358</v>
+        <v>0.287</v>
       </c>
       <c r="J117" t="n">
-        <v>8.059200000000001</v>
+        <v>6.888</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.031</v>
+        <v>0.0252</v>
       </c>
       <c r="J118" t="n">
-        <v>0.744</v>
+        <v>0.6048</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.294</v>
+        <v>-0.2763</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.056</v>
+        <v>-6.6312</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3128</v>
+        <v>-0.2957</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.5072</v>
+        <v>-7.0968</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4305</v>
+        <v>-0.4219</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.332</v>
+        <v>-10.1256</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2884</v>
+        <v>1.29</v>
       </c>
       <c r="J122" t="n">
-        <v>23.1912</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0006</v>
+        <v>0.9906</v>
       </c>
       <c r="J123" t="n">
-        <v>18.0108</v>
+        <v>17.8308</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7508</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>13.5144</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.28</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6211</v>
+        <v>0.6166</v>
       </c>
       <c r="J125" t="n">
-        <v>11.1798</v>
+        <v>11.0988</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.06</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1655</v>
+        <v>0.1361</v>
       </c>
       <c r="J126" t="n">
-        <v>2.979</v>
+        <v>2.4498</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3637</v>
+        <v>0.3202</v>
       </c>
       <c r="J127" t="n">
-        <v>6.5466</v>
+        <v>5.7636</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.84</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1909</v>
+        <v>-0.175</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.4362</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.342</v>
+        <v>-0.3271</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.156</v>
+        <v>-5.8878</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4051</v>
+        <v>-0.394</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.2918</v>
+        <v>-7.092</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4317</v>
+        <v>-0.423</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.7706</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1.8812</v>
+        <v>1.9467</v>
       </c>
       <c r="J132" t="n">
-        <v>28.218</v>
+        <v>29.2005</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>2.08</v>
       </c>
       <c r="I133" t="n">
-        <v>1.7464</v>
+        <v>1.7981</v>
       </c>
       <c r="J133" t="n">
-        <v>26.196</v>
+        <v>26.9715</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9842</v>
+        <v>0.9926</v>
       </c>
       <c r="J134" t="n">
-        <v>14.763</v>
+        <v>14.889</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7438</v>
+        <v>0.7294</v>
       </c>
       <c r="J135" t="n">
-        <v>11.157</v>
+        <v>10.941</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6754</v>
+        <v>-0.6559</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.131</v>
+        <v>-9.8385</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.91</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0878</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.317</v>
+        <v>-1.0425</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.89</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1127</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.6905</v>
+        <v>-1.4205</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.54</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4532</v>
+        <v>-0.4468</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.798</v>
+        <v>-6.702</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4973</v>
+        <v>-0.4951</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.4595</v>
+        <v>-7.4265</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5236</v>
+        <v>-0.5245</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.854</v>
+        <v>-7.8675</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6711</v>
+        <v>0.7236</v>
       </c>
       <c r="J142" t="n">
-        <v>11.4087</v>
+        <v>12.3012</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0456</v>
+        <v>-0.0363</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.7752</v>
+        <v>-0.6171</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1991</v>
+        <v>-0.1806</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.3847</v>
+        <v>-3.0702</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3793</v>
+        <v>-0.3661</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.4481</v>
+        <v>-6.2237</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.39</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6042</v>
+        <v>-0.6202</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.2714</v>
+        <v>-10.5434</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.81</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8924</v>
+        <v>0.8227</v>
       </c>
       <c r="J147" t="n">
-        <v>15.1708</v>
+        <v>13.9859</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.72</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8101</v>
+        <v>0.7388</v>
       </c>
       <c r="J148" t="n">
-        <v>13.7717</v>
+        <v>12.5596</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3206</v>
+        <v>0.2694</v>
       </c>
       <c r="J149" t="n">
-        <v>5.4502</v>
+        <v>4.5798</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3088</v>
+        <v>0.2586</v>
       </c>
       <c r="J150" t="n">
-        <v>5.2496</v>
+        <v>4.3962</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.4773</v>
+        <v>-1.2614</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.89</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5482</v>
+        <v>1.5831</v>
       </c>
       <c r="J152" t="n">
-        <v>29.4158</v>
+        <v>30.0789</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.7</v>
       </c>
       <c r="I153" t="n">
-        <v>1.3182</v>
+        <v>1.3395</v>
       </c>
       <c r="J153" t="n">
-        <v>25.0458</v>
+        <v>25.4505</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.3</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7199</v>
+        <v>0.702</v>
       </c>
       <c r="J154" t="n">
-        <v>13.6781</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I155" t="n">
-        <v>0.659</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>12.521</v>
+        <v>12.1144</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.11</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2962</v>
+        <v>0.2632</v>
       </c>
       <c r="J156" t="n">
-        <v>5.6278</v>
+        <v>5.0008</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.83</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.192</v>
+        <v>-0.1766</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.648</v>
+        <v>-3.3554</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.82</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2026</v>
+        <v>-0.1873</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.8494</v>
+        <v>-3.5587</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.67</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3443</v>
+        <v>-0.3308</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.5417</v>
+        <v>-6.2852</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.65</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3621</v>
+        <v>-0.3492</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.8799</v>
+        <v>-6.6348</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.442</v>
+        <v>-0.4342</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.398</v>
+        <v>-8.2498</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8867</v>
+        <v>0.8693</v>
       </c>
       <c r="J162" t="n">
-        <v>17.734</v>
+        <v>17.386</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.36</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8673</v>
+        <v>0.8484</v>
       </c>
       <c r="J163" t="n">
-        <v>17.346</v>
+        <v>16.968</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.25</v>
       </c>
       <c r="I164" t="n">
-        <v>0.647</v>
+        <v>0.6165</v>
       </c>
       <c r="J164" t="n">
-        <v>12.94</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5644</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>11.288</v>
+        <v>10.636</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3013</v>
+        <v>-0.2623</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.026</v>
+        <v>-5.246</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.19</v>
       </c>
       <c r="I167" t="n">
-        <v>0.446</v>
+        <v>0.3908</v>
       </c>
       <c r="J167" t="n">
-        <v>8.92</v>
+        <v>7.816</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0503</v>
+        <v>-0.0405</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.006</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1391</v>
+        <v>-0.1218</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.782</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.74</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3002</v>
+        <v>-0.2822</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.004</v>
+        <v>-5.644</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3651</v>
+        <v>-0.351</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.302</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.6</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2622</v>
+        <v>1.2827</v>
       </c>
       <c r="J172" t="n">
-        <v>30.2928</v>
+        <v>30.7848</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5794</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>13.9056</v>
+        <v>13.0032</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4196</v>
+        <v>0.381</v>
       </c>
       <c r="J174" t="n">
-        <v>10.0704</v>
+        <v>9.144</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4924</v>
+        <v>-0.451</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.8176</v>
+        <v>-10.824</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6338</v>
+        <v>-0.5985</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.2112</v>
+        <v>-14.364</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3466</v>
+        <v>0.2929</v>
       </c>
       <c r="J177" t="n">
-        <v>8.3184</v>
+        <v>7.0296</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0435</v>
+        <v>0.0294</v>
       </c>
       <c r="J178" t="n">
-        <v>1.044</v>
+        <v>0.7056</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.96</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.7376</v>
+        <v>-1.3944</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.18</v>
+        <v>-0.1595</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.32</v>
+        <v>-3.828</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2901</v>
+        <v>0.247</v>
       </c>
       <c r="J182" t="n">
-        <v>5.5119</v>
+        <v>4.693</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.79</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2431</v>
+        <v>-0.2259</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.6189</v>
+        <v>-4.2921</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2431</v>
+        <v>-0.2259</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.6189</v>
+        <v>-4.2921</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3267</v>
+        <v>-0.3107</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.2073</v>
+        <v>-5.9033</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4259</v>
+        <v>-0.4166</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.0921</v>
+        <v>-7.9154</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1977</v>
+        <v>1.213</v>
       </c>
       <c r="J187" t="n">
-        <v>22.7563</v>
+        <v>23.047</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.51</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0928</v>
+        <v>1.1052</v>
       </c>
       <c r="J188" t="n">
-        <v>20.7632</v>
+        <v>20.9988</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.34</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8117</v>
+        <v>0.7946</v>
       </c>
       <c r="J189" t="n">
-        <v>15.4223</v>
+        <v>15.0974</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5488</v>
+        <v>0.5203</v>
       </c>
       <c r="J190" t="n">
-        <v>10.4272</v>
+        <v>9.8857</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.04</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1149</v>
+        <v>0.0905</v>
       </c>
       <c r="J191" t="n">
-        <v>2.1831</v>
+        <v>1.7195</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9041</v>
+        <v>0.835</v>
       </c>
       <c r="J192" t="n">
-        <v>16.2738</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6616</v>
+        <v>0.5907</v>
       </c>
       <c r="J193" t="n">
-        <v>11.9088</v>
+        <v>10.6326</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.37</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4743</v>
+        <v>0.4114</v>
       </c>
       <c r="J194" t="n">
-        <v>8.5374</v>
+        <v>7.4052</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.06</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0941</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>1.6938</v>
+        <v>1.242</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0775</v>
+        <v>0.0551</v>
       </c>
       <c r="J196" t="n">
-        <v>1.395</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5282</v>
+        <v>0.553</v>
       </c>
       <c r="J197" t="n">
-        <v>9.5076</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1453</v>
+        <v>-0.1291</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.6154</v>
+        <v>-2.3238</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.8</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2369</v>
+        <v>-0.2184</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.2642</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2753</v>
+        <v>-0.2571</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.9554</v>
+        <v>-4.6278</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.42</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5774</v>
+        <v>-0.5884</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.3932</v>
+        <v>-10.5912</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7224</v>
+        <v>0.6644</v>
       </c>
       <c r="J202" t="n">
-        <v>17.3376</v>
+        <v>15.9456</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.23</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4628</v>
+        <v>0.4051</v>
       </c>
       <c r="J203" t="n">
-        <v>11.1072</v>
+        <v>9.7224</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2938</v>
+        <v>0.2463</v>
       </c>
       <c r="J204" t="n">
-        <v>7.0512</v>
+        <v>5.9112</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.93</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1199</v>
+        <v>-0.1013</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.8776</v>
+        <v>-2.4312</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2412</v>
+        <v>-0.2215</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.7888</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.43</v>
       </c>
       <c r="I207" t="n">
-        <v>1.054</v>
+        <v>1.0641</v>
       </c>
       <c r="J207" t="n">
-        <v>25.296</v>
+        <v>25.5384</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4411</v>
+        <v>0.3983</v>
       </c>
       <c r="J208" t="n">
-        <v>10.5864</v>
+        <v>9.559200000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0012</v>
+        <v>-0.0005</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.0288</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.9</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3444</v>
+        <v>-0.3022</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.265599999999999</v>
+        <v>-7.2528</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.04</v>
+        <v>-1.0415</v>
       </c>
       <c r="J211" t="n">
-        <v>-24.96</v>
+        <v>-24.996</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3505</v>
+        <v>0.3513</v>
       </c>
       <c r="J212" t="n">
-        <v>5.9585</v>
+        <v>5.9721</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0362</v>
+        <v>-0.0268</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4556</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3454</v>
+        <v>-0.3302</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.8718</v>
+        <v>-5.6134</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3545</v>
+        <v>-0.3399</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.0265</v>
+        <v>-5.7783</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5138</v>
+        <v>-0.5147</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.7346</v>
+        <v>-8.7499</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9957</v>
+        <v>0.9382</v>
       </c>
       <c r="J217" t="n">
-        <v>16.9269</v>
+        <v>15.9494</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.44</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5523</v>
+        <v>0.4833</v>
       </c>
       <c r="J218" t="n">
-        <v>9.389099999999999</v>
+        <v>8.216100000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2811</v>
+        <v>0.2324</v>
       </c>
       <c r="J219" t="n">
-        <v>4.7787</v>
+        <v>3.9508</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2563</v>
+        <v>0.2102</v>
       </c>
       <c r="J220" t="n">
-        <v>4.3571</v>
+        <v>3.5734</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3503</v>
+        <v>-0.339</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.9551</v>
+        <v>-5.763</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4491</v>
+        <v>1.477</v>
       </c>
       <c r="J222" t="n">
-        <v>27.5329</v>
+        <v>28.063</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.53</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1099</v>
+        <v>1.1247</v>
       </c>
       <c r="J223" t="n">
-        <v>21.0881</v>
+        <v>21.3693</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.32</v>
       </c>
       <c r="I224" t="n">
-        <v>0.766</v>
+        <v>0.7494</v>
       </c>
       <c r="J224" t="n">
-        <v>14.554</v>
+        <v>14.2386</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.2</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5167</v>
+        <v>0.4881</v>
       </c>
       <c r="J225" t="n">
-        <v>9.817299999999999</v>
+        <v>9.273899999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4718</v>
+        <v>0.4417</v>
       </c>
       <c r="J226" t="n">
-        <v>8.9642</v>
+        <v>8.392300000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4396</v>
+        <v>0.3945</v>
       </c>
       <c r="J227" t="n">
-        <v>8.352399999999999</v>
+        <v>7.4955</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0612</v>
+        <v>-0.049</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.1628</v>
+        <v>-0.931</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2512</v>
+        <v>-0.2346</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.7728</v>
+        <v>-4.4574</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.54</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4677</v>
+        <v>-0.4626</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.8863</v>
+        <v>-8.789400000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5629</v>
+        <v>-0.5707</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.6951</v>
+        <v>-10.8433</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.29</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7487</v>
+        <v>0.7189</v>
       </c>
       <c r="J232" t="n">
-        <v>17.9688</v>
+        <v>17.2536</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J233" t="n">
-        <v>13.3368</v>
+        <v>12.4296</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.442</v>
+        <v>0.4036</v>
       </c>
       <c r="J234" t="n">
-        <v>10.608</v>
+        <v>9.686400000000001</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.13</v>
       </c>
       <c r="I235" t="n">
-        <v>0.395</v>
+        <v>0.3573</v>
       </c>
       <c r="J235" t="n">
-        <v>9.48</v>
+        <v>8.575200000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4693</v>
+        <v>-0.4275</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.2632</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.22</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4868</v>
+        <v>0.4296</v>
       </c>
       <c r="J237" t="n">
-        <v>11.6832</v>
+        <v>10.3104</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2871</v>
+        <v>0.2375</v>
       </c>
       <c r="J238" t="n">
-        <v>6.8904</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1951</v>
+        <v>-0.1751</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.6824</v>
+        <v>-4.2024</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3038</v>
+        <v>-0.2859</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.2912</v>
+        <v>-6.8616</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3133</v>
+        <v>-0.2958</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.5192</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.43</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5496</v>
+        <v>0.4799</v>
       </c>
       <c r="J242" t="n">
-        <v>10.992</v>
+        <v>9.598000000000001</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4107</v>
+        <v>0.3486</v>
       </c>
       <c r="J243" t="n">
-        <v>8.214</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.2</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2979</v>
+        <v>0.2461</v>
       </c>
       <c r="J244" t="n">
-        <v>5.958</v>
+        <v>4.922</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.17</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2613</v>
+        <v>0.2137</v>
       </c>
       <c r="J245" t="n">
-        <v>5.226</v>
+        <v>4.274</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.02</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0348</v>
+        <v>0.0228</v>
       </c>
       <c r="J246" t="n">
-        <v>0.696</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.48</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6857</v>
+        <v>0.7298</v>
       </c>
       <c r="J247" t="n">
-        <v>13.714</v>
+        <v>14.596</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="J248" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0418</v>
+        <v>-0.032</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.836</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1895</v>
+        <v>-0.169</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.79</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4359</v>
+        <v>-0.4293</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.718</v>
+        <v>-8.586</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.61</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0638</v>
+        <v>1.0553</v>
       </c>
       <c r="J252" t="n">
-        <v>22.3398</v>
+        <v>22.1613</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0948</v>
+        <v>-0.0796</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.9908</v>
+        <v>-1.6716</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1415</v>
+        <v>-0.123</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.9715</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2462</v>
+        <v>-0.2263</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.1702</v>
+        <v>-4.7523</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.42</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5851</v>
+        <v>-0.5988</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.2871</v>
+        <v>-12.5748</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.62</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2542</v>
+        <v>1.2714</v>
       </c>
       <c r="J257" t="n">
-        <v>26.3382</v>
+        <v>26.6994</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.6</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2279</v>
+        <v>1.2439</v>
       </c>
       <c r="J258" t="n">
-        <v>25.7859</v>
+        <v>26.1219</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4856</v>
       </c>
       <c r="J259" t="n">
-        <v>10.8696</v>
+        <v>10.1976</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.1</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3021</v>
+        <v>0.2702</v>
       </c>
       <c r="J260" t="n">
-        <v>6.3441</v>
+        <v>5.6742</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.767</v>
+        <v>-0.7451</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.107</v>
+        <v>-15.6471</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0595</v>
+        <v>1.041</v>
       </c>
       <c r="J262" t="n">
-        <v>37.0825</v>
+        <v>36.435</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.523</v>
+        <v>0.4635</v>
       </c>
       <c r="J263" t="n">
-        <v>18.305</v>
+        <v>16.2225</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1271</v>
+        <v>-0.1082</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.4485</v>
+        <v>-3.787</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.73</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3235</v>
+        <v>-0.3073</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.3225</v>
+        <v>-10.7555</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3875</v>
+        <v>-0.3766</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.5625</v>
+        <v>-13.181</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>2.04</v>
       </c>
       <c r="I267" t="n">
-        <v>1.7989</v>
+        <v>1.8698</v>
       </c>
       <c r="J267" t="n">
-        <v>62.9615</v>
+        <v>65.443</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4894</v>
       </c>
       <c r="J268" t="n">
-        <v>18.3295</v>
+        <v>17.129</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3855</v>
+        <v>0.3513</v>
       </c>
       <c r="J269" t="n">
-        <v>13.4925</v>
+        <v>12.2955</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.83</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5557</v>
+        <v>-0.5183</v>
       </c>
       <c r="J270" t="n">
-        <v>-19.4495</v>
+        <v>-18.1405</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5793</v>
+        <v>-0.543</v>
       </c>
       <c r="J271" t="n">
-        <v>-20.2755</v>
+        <v>-19.005</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9953</v>
+        <v>0.9912</v>
       </c>
       <c r="J272" t="n">
-        <v>33.8402</v>
+        <v>33.7008</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5944</v>
+        <v>0.5588</v>
       </c>
       <c r="J273" t="n">
-        <v>20.2096</v>
+        <v>18.9992</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4617</v>
+        <v>0.4247</v>
       </c>
       <c r="J274" t="n">
-        <v>15.6978</v>
+        <v>14.4398</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.15</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4392</v>
+        <v>0.4023</v>
       </c>
       <c r="J275" t="n">
-        <v>14.9328</v>
+        <v>13.6782</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5709</v>
+        <v>-0.5331</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.4106</v>
+        <v>-18.1254</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8262</v>
+        <v>0.7791</v>
       </c>
       <c r="J277" t="n">
-        <v>28.0908</v>
+        <v>26.4894</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.04</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1312</v>
+        <v>0.099</v>
       </c>
       <c r="J278" t="n">
-        <v>4.4608</v>
+        <v>3.366</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.93</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1083</v>
+        <v>-0.0914</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.6822</v>
+        <v>-3.1076</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.7</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3439</v>
+        <v>-0.3285</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.6926</v>
+        <v>-11.169</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.68</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3622</v>
+        <v>-0.3482</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.3148</v>
+        <v>-11.8388</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.37</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9056</v>
+        <v>0.8882</v>
       </c>
       <c r="J282" t="n">
-        <v>21.7344</v>
+        <v>21.3168</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8659</v>
+        <v>0.8449</v>
       </c>
       <c r="J283" t="n">
-        <v>20.7816</v>
+        <v>20.2776</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.29</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7439</v>
+        <v>0.7144</v>
       </c>
       <c r="J284" t="n">
-        <v>17.8536</v>
+        <v>17.1456</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3704</v>
+        <v>-0.3284</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.8896</v>
+        <v>-7.8816</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5695</v>
+        <v>-0.5314</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.668</v>
+        <v>-12.7536</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3284</v>
+        <v>0.2759</v>
       </c>
       <c r="J287" t="n">
-        <v>7.8816</v>
+        <v>6.6216</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.31</v>
+        <v>0.2587</v>
       </c>
       <c r="J288" t="n">
-        <v>7.44</v>
+        <v>6.2088</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0251</v>
+        <v>-0.0181</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.6024</v>
+        <v>-0.4344</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1235</v>
+        <v>-0.105</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.964</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2423</v>
+        <v>-0.2221</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.8152</v>
+        <v>-5.3304</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.54</v>
       </c>
       <c r="I292" t="n">
-        <v>1.169</v>
+        <v>1.1834</v>
       </c>
       <c r="J292" t="n">
-        <v>28.056</v>
+        <v>28.4016</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.25</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="J293" t="n">
-        <v>15.7872</v>
+        <v>14.9856</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.506</v>
+        <v>0.4693</v>
       </c>
       <c r="J294" t="n">
-        <v>12.144</v>
+        <v>11.2632</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0859</v>
+        <v>-0.065</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.0616</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.548</v>
+        <v>-0.5093</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.152</v>
+        <v>-12.2232</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.39</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7442</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>17.8608</v>
+        <v>16.584</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0241</v>
+        <v>-0.0177</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.5784</v>
+        <v>-0.4248</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.98</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0416</v>
+        <v>-0.0319</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.9984</v>
+        <v>-0.7655999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1096</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.6304</v>
+        <v>-2.2152</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.59</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.444</v>
+        <v>-0.4382</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.656</v>
+        <v>-10.5168</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.75</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4093</v>
+        <v>1.4351</v>
       </c>
       <c r="J302" t="n">
-        <v>28.186</v>
+        <v>28.702</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.56</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1648</v>
+        <v>1.1787</v>
       </c>
       <c r="J303" t="n">
-        <v>23.296</v>
+        <v>23.574</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7195</v>
+        <v>0.6958</v>
       </c>
       <c r="J304" t="n">
-        <v>14.39</v>
+        <v>13.916</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.23</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5971</v>
+        <v>0.5689</v>
       </c>
       <c r="J305" t="n">
-        <v>11.942</v>
+        <v>11.378</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9014</v>
+        <v>-0.8946</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.028</v>
+        <v>-17.892</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.78</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2498</v>
+        <v>1.2593</v>
       </c>
       <c r="J307" t="n">
-        <v>24.996</v>
+        <v>25.186</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.85</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1937</v>
+        <v>-0.1739</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.874</v>
+        <v>-3.478</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.74</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3023</v>
+        <v>-0.2843</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.046</v>
+        <v>-5.686</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.64</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3941</v>
+        <v>-0.3826</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.882</v>
+        <v>-7.652</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4647</v>
+        <v>-0.4606</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.294</v>
+        <v>-9.212</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.18</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3304</v>
+        <v>0.322</v>
       </c>
       <c r="J312" t="n">
-        <v>7.5992</v>
+        <v>7.406</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0669</v>
+        <v>-0.055</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.5387</v>
+        <v>-1.265</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0805</v>
+        <v>-0.0672</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.8515</v>
+        <v>-1.5456</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2142</v>
+        <v>-0.1942</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.9266</v>
+        <v>-4.4666</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3852</v>
+        <v>-0.3728</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.8596</v>
+        <v>-8.574400000000001</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4199</v>
+        <v>0.3557</v>
       </c>
       <c r="J317" t="n">
-        <v>9.6577</v>
+        <v>8.181100000000001</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.25</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3626</v>
+        <v>0.3027</v>
       </c>
       <c r="J318" t="n">
-        <v>8.3398</v>
+        <v>6.9621</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3392</v>
+        <v>0.2812</v>
       </c>
       <c r="J319" t="n">
-        <v>7.8016</v>
+        <v>6.4676</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0595</v>
       </c>
       <c r="J320" t="n">
-        <v>1.8653</v>
+        <v>1.3685</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1702</v>
+        <v>-0.1501</v>
       </c>
       <c r="J321" t="n">
-        <v>-3.9146</v>
+        <v>-3.4523</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.75</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3782</v>
+        <v>1.4024</v>
       </c>
       <c r="J322" t="n">
-        <v>23.4294</v>
+        <v>23.8408</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.53</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1037</v>
+        <v>1.1201</v>
       </c>
       <c r="J323" t="n">
-        <v>18.7629</v>
+        <v>19.0417</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.4</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9105</v>
+        <v>0.9061</v>
       </c>
       <c r="J324" t="n">
-        <v>15.4785</v>
+        <v>15.4037</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.39</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8922</v>
+        <v>0.8863</v>
       </c>
       <c r="J325" t="n">
-        <v>15.1674</v>
+        <v>15.0671</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5952</v>
+        <v>0.5705</v>
       </c>
       <c r="J326" t="n">
-        <v>10.1184</v>
+        <v>9.698499999999999</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.04</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2164</v>
+        <v>0.1912</v>
       </c>
       <c r="J327" t="n">
-        <v>3.6788</v>
+        <v>3.2504</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.82</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2012</v>
+        <v>-0.1859</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.4204</v>
+        <v>-3.1603</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.7</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3174</v>
+        <v>-0.3038</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.3958</v>
+        <v>-5.1646</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.63</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3789</v>
+        <v>-0.3669</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.4413</v>
+        <v>-6.2373</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.3</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6919</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.3356</v>
+        <v>-11.7623</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.56</v>
       </c>
       <c r="I332" t="n">
-        <v>1.1822</v>
+        <v>1.1965</v>
       </c>
       <c r="J332" t="n">
-        <v>24.8262</v>
+        <v>25.1265</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1145</v>
+        <v>1.1264</v>
       </c>
       <c r="J333" t="n">
-        <v>23.4045</v>
+        <v>23.6544</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.28</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7096</v>
+        <v>0.681</v>
       </c>
       <c r="J334" t="n">
-        <v>14.9016</v>
+        <v>14.301</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.9</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3829</v>
+        <v>-0.3423</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.040900000000001</v>
+        <v>-7.1883</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5581</v>
+        <v>-0.5212</v>
       </c>
       <c r="J336" t="n">
-        <v>-11.7201</v>
+        <v>-10.9452</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.22</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4986</v>
+        <v>0.443</v>
       </c>
       <c r="J337" t="n">
-        <v>10.4706</v>
+        <v>9.303000000000001</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0649</v>
+        <v>-0.0534</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.3629</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1605</v>
+        <v>-0.1421</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.3705</v>
+        <v>-2.9841</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2225</v>
+        <v>-0.2028</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.6725</v>
+        <v>-4.2588</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.59</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4366</v>
+        <v>-0.4291</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.1686</v>
+        <v>-9.011100000000001</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.7</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3357</v>
+        <v>1.3568</v>
       </c>
       <c r="J342" t="n">
-        <v>21.3712</v>
+        <v>21.7088</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.51</v>
       </c>
       <c r="I343" t="n">
-        <v>1.0908</v>
+        <v>1.1033</v>
       </c>
       <c r="J343" t="n">
-        <v>17.4528</v>
+        <v>17.6528</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.22</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5685</v>
+        <v>0.5409</v>
       </c>
       <c r="J344" t="n">
-        <v>9.096</v>
+        <v>8.654400000000001</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.19</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4728</v>
       </c>
       <c r="J345" t="n">
-        <v>8.039999999999999</v>
+        <v>7.5648</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.14</v>
       </c>
       <c r="I346" t="n">
-        <v>0.3862</v>
+        <v>0.3544</v>
       </c>
       <c r="J346" t="n">
-        <v>6.1792</v>
+        <v>5.6704</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.2033</v>
+        <v>-0.1878</v>
       </c>
       <c r="J347" t="n">
-        <v>-3.2528</v>
+        <v>-3.0048</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2139</v>
+        <v>-0.1988</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.4224</v>
+        <v>-3.1808</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.7</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3129</v>
+        <v>-0.3008</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.0064</v>
+        <v>-4.8128</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.67</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3399</v>
+        <v>-0.3284</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.4384</v>
+        <v>-5.2544</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.3</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6627</v>
+        <v>-0.6863</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.6032</v>
+        <v>-10.9808</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.5</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0756</v>
+        <v>1.0873</v>
       </c>
       <c r="J352" t="n">
-        <v>19.3608</v>
+        <v>19.5714</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.47</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0338</v>
+        <v>1.0406</v>
       </c>
       <c r="J353" t="n">
-        <v>18.6084</v>
+        <v>18.7308</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.41</v>
       </c>
       <c r="I354" t="n">
-        <v>0.9372</v>
+        <v>0.9307</v>
       </c>
       <c r="J354" t="n">
-        <v>16.8696</v>
+        <v>16.7526</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.36</v>
       </c>
       <c r="I355" t="n">
-        <v>0.8468</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J355" t="n">
-        <v>15.2424</v>
+        <v>14.9976</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.09</v>
       </c>
       <c r="I356" t="n">
-        <v>0.2569</v>
+        <v>0.2256</v>
       </c>
       <c r="J356" t="n">
-        <v>4.6242</v>
+        <v>4.0608</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.25</v>
       </c>
       <c r="I357" t="n">
-        <v>0.591</v>
+        <v>0.5461</v>
       </c>
       <c r="J357" t="n">
-        <v>10.638</v>
+        <v>9.829800000000001</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.82</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.215</v>
+        <v>-0.1979</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.87</v>
+        <v>-3.5622</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.75</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.281</v>
+        <v>-0.2636</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.058</v>
+        <v>-4.7448</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.61</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4088</v>
+        <v>-0.398</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.3584</v>
+        <v>-7.164</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.453</v>
+        <v>-0.4466</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.154</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.27</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7133</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J362" t="n">
-        <v>16.4059</v>
+        <v>15.6607</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.26</v>
       </c>
       <c r="I363" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6585</v>
       </c>
       <c r="J363" t="n">
-        <v>15.916</v>
+        <v>15.1455</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.08</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2723</v>
+        <v>0.2376</v>
       </c>
       <c r="J364" t="n">
-        <v>6.2629</v>
+        <v>5.4648</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.08</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2723</v>
+        <v>0.2376</v>
       </c>
       <c r="J365" t="n">
-        <v>6.2629</v>
+        <v>5.4648</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5844</v>
+        <v>-0.546</v>
       </c>
       <c r="J366" t="n">
-        <v>-13.4412</v>
+        <v>-12.558</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.25</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.4739</v>
       </c>
       <c r="J367" t="n">
-        <v>12.2314</v>
+        <v>10.8997</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.03</v>
       </c>
       <c r="I368" t="n">
-        <v>0.108</v>
+        <v>0.0795</v>
       </c>
       <c r="J368" t="n">
-        <v>2.484</v>
+        <v>1.8285</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0503</v>
+        <v>0.0337</v>
       </c>
       <c r="J369" t="n">
-        <v>1.1569</v>
+        <v>0.7751</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.79</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2574</v>
+        <v>-0.2377</v>
       </c>
       <c r="J370" t="n">
-        <v>-5.9202</v>
+        <v>-5.4671</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.66</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3794</v>
+        <v>-0.3668</v>
       </c>
       <c r="J371" t="n">
-        <v>-8.7262</v>
+        <v>-8.436400000000001</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7844</v>
       </c>
       <c r="J372" t="n">
-        <v>17.82</v>
+        <v>17.2568</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>0.7689</v>
+        <v>0.7405</v>
       </c>
       <c r="J373" t="n">
-        <v>16.9158</v>
+        <v>16.291</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.17</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4878</v>
+        <v>0.4494</v>
       </c>
       <c r="J374" t="n">
-        <v>10.7316</v>
+        <v>9.886799999999999</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.98</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1219</v>
+        <v>-0.0948</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.6818</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.87</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4447</v>
+        <v>-0.4026</v>
       </c>
       <c r="J376" t="n">
-        <v>-9.7834</v>
+        <v>-8.857200000000001</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.24</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5419</v>
+        <v>0.4882</v>
       </c>
       <c r="J377" t="n">
-        <v>11.9218</v>
+        <v>10.7404</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I378" t="n">
-        <v>0.1981</v>
+        <v>0.1579</v>
       </c>
       <c r="J378" t="n">
-        <v>4.3582</v>
+        <v>3.4738</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2302</v>
+        <v>-0.2109</v>
       </c>
       <c r="J379" t="n">
-        <v>-5.0644</v>
+        <v>-4.6398</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.74</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2978</v>
+        <v>-0.2798</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.5516</v>
+        <v>-6.1556</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5124</v>
+        <v>-0.514</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.2728</v>
+        <v>-11.308</v>
       </c>
     </row>
   </sheetData>
